--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C09892-FDD7-4528-B477-F08E532425E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD40288-8275-4FBA-A01C-A537F2564267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1790,10 +1790,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNS_05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2378,6 +2374,12 @@
   </si>
   <si>
     <t>中海石油化学</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>ENG_02</t>
   </si>
 </sst>
 </file>
@@ -4119,10 +4121,10 @@
         <v>324</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4133,7 +4135,7 @@
         <v>1.95</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4186,7 +4188,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
       <c r="B12" s="340" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C12" s="340"/>
       <c r="D12" s="340"/>
@@ -4206,7 +4208,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v>Low Growth Asset Play</v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4215,7 +4217,7 @@
         <v>357</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4225,11 +4227,11 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -4238,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4250,7 +4252,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4263,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>1.5407194269481685</v>
+        <v>1.7528561419286872</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>316</v>
@@ -4274,11 +4276,11 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20182066703946511</v>
+        <v>0.25280122918191261</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4289,7 +4291,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
       <c r="B25" s="340" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C25" s="340"/>
       <c r="D25" s="340"/>
@@ -4343,7 +4345,7 @@
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4369,7 +4371,7 @@
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -4382,7 +4384,7 @@
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -4404,7 +4406,7 @@
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -4422,11 +4424,11 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>27545.047874644533</v>
+        <v>28697.547874644533</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
@@ -4441,7 +4443,7 @@
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
@@ -4452,11 +4454,11 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-25213.952125355467</v>
+        <v>-24061.452125355467</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -4474,7 +4476,7 @@
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -4492,11 +4494,11 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-225806.47450420776</v>
+        <v>-226094.59950420776</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4518,7 +4520,7 @@
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
@@ -4532,7 +4534,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
       <c r="B54" s="340" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C54" s="340"/>
       <c r="D54" s="340"/>
@@ -4545,11 +4547,11 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>572742.03839346452</v>
+        <v>575049.21170235414</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4558,20 +4560,20 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>546774.39908131293</v>
+        <v>547638.77408131293</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.0823671959654366E-2</v>
+        <v>6.4575015354156703E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4580,12 +4582,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0</v>
+        <v>5.1282051282051287E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4599,7 +4601,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
       <c r="B63" s="340" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C63" s="340"/>
       <c r="D63" s="340"/>
@@ -4666,13 +4668,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
       <c r="B73" s="340" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C73" s="340"/>
       <c r="D73" s="340"/>
@@ -4681,7 +4683,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="B74" s="340" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C74" s="340"/>
       <c r="D74" s="340"/>
@@ -4702,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4825770040165753</v>
+        <v>1.5740159992575697</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4711,7 +4713,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4724,7 +4726,7 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="340" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C81" s="340"/>
       <c r="D81" s="340"/>
@@ -4760,7 +4762,7 @@
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -4769,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.45967982646420824</v>
+        <v>0.48726061605206072</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4778,7 +4780,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4796,7 +4798,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4818,7 +4820,7 @@
       </c>
       <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="94" spans="2:6">
@@ -4827,11 +4829,11 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>9855306.4750236981</v>
+        <v>9778473.1416903641</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="95" spans="2:6">
@@ -4840,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1378105151895226</v>
+        <v>2.2484124794342271</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4862,7 +4864,7 @@
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4871,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1405553145336226E-2</v>
+        <v>1.20898863340564E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4880,7 +4882,7 @@
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
       <c r="B101" s="340" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C101" s="340"/>
       <c r="D101" s="340"/>
@@ -4893,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,11 +4904,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.6893987527114966</v>
+        <v>1.7907626778741865</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4915,7 +4917,7 @@
     </row>
     <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4925,7 +4927,7 @@
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
       <c r="B108" s="341" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C108" s="341"/>
       <c r="D108" s="341"/>
@@ -4956,15 +4958,15 @@
       </c>
       <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.54 HKD</v>
+        <v>3.6 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4978,15 +4980,15 @@
       </c>
       <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.51 HKD</v>
+        <v>3.5 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5004,11 +5006,11 @@
       </c>
       <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.33 HKD</v>
+        <v>3.45 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5022,15 +5024,15 @@
       </c>
       <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.17 HKD</v>
+        <v>3.4 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5048,11 +5050,11 @@
       </c>
       <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>3.17 HKD</v>
+        <v>3.35 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5065,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>3.3849605810051271</v>
+        <v>3.4520249438173267</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5074,7 +5076,7 @@
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
       <c r="B119" s="345" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C119" s="345"/>
       <c r="D119" s="345"/>
@@ -5083,7 +5085,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5093,7 +5095,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="343" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C123" s="343"/>
       <c r="D123" s="343"/>
@@ -5102,7 +5104,7 @@
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
       <c r="B124" s="340" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C124" s="340"/>
       <c r="D124" s="340"/>
@@ -5138,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5147,14 +5149,14 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="2:4">
@@ -5164,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0</v>
+        <v>0.18161128812016392</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5174,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>1.5407194269481685</v>
+        <v>1.5712448538085233</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5183,11 +5185,11 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>1.5407194269481685</v>
+        <v>1.7528561419286872</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="134" spans="2:4">
@@ -5196,19 +5198,19 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54483386436049175</v>
+        <v>0.4922237902515445</v>
       </c>
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5218,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>0</v>
+        <v>0.21064814814814814</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5228,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>1.9588892251187078</v>
+        <v>1.9976996202646566</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5237,11 +5239,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>1.9588892251187078</v>
+        <v>2.2083477684128048</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="140" spans="2:4">
@@ -5250,19 +5252,19 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.42129629629629628</v>
+        <v>0.36027467809350067</v>
       </c>
     </row>
     <row r="142" spans="2:4">
       <c r="B142" s="234" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C142" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5272,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>0</v>
+        <v>0.25770969872478805</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5282,20 +5284,20 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>2.6870908437842354</v>
+        <v>2.7403286972080334</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="80" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>2.6870908437842354</v>
+        <v>2.9980383959328214</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5304,12 +5306,12 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.20616775897983042</v>
+        <v>0.13151311339670591</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
       <c r="A148" s="247" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B148" s="36"/>
       <c r="C148" s="36"/>
@@ -5319,7 +5321,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="B150" s="347" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C150" s="340"/>
       <c r="D150" s="340"/>
@@ -5328,12 +5330,12 @@
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="344" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C153" s="344"/>
       <c r="D153" s="344"/>
@@ -5342,27 +5344,27 @@
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="238" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="238" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="B156" s="238" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="B158" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
       <c r="B159" s="341" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C159" s="341"/>
       <c r="D159" s="341"/>
@@ -5371,12 +5373,12 @@
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
       <c r="B162" s="346" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C162" s="346"/>
       <c r="D162" s="346"/>
@@ -5385,7 +5387,7 @@
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
       <c r="B163" s="346" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C163" s="346"/>
       <c r="D163" s="346"/>
@@ -5394,22 +5396,22 @@
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="238" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -5476,7 +5478,7 @@
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="104">
         <v>45657</v>
@@ -5990,7 +5992,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" s="181">
         <v>1522553</v>
@@ -6026,7 +6028,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C23" s="181">
         <v>-379005</v>
@@ -6062,7 +6064,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C24" s="181">
         <v>-1061021</v>
@@ -6101,16 +6103,46 @@
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
+      <c r="C25" s="39">
+        <f>0.1208*Exchange_Rate</f>
+        <v>0.12804800000000002</v>
+      </c>
+      <c r="D25" s="39">
+        <f>0.207*Exchange_Rate</f>
+        <v>0.21942</v>
+      </c>
+      <c r="E25" s="39">
+        <f>0.178*Exchange_Rate</f>
+        <v>0.18868000000000001</v>
+      </c>
+      <c r="F25" s="39">
+        <f>0.155*Exchange_Rate</f>
+        <v>0.1643</v>
+      </c>
+      <c r="G25" s="39">
+        <f>0.08*Exchange_Rate</f>
+        <v>8.48E-2</v>
+      </c>
+      <c r="H25" s="39">
+        <f>0.076*Exchange_Rate</f>
+        <v>8.0560000000000007E-2</v>
+      </c>
+      <c r="I25" s="39">
+        <f>0.15*Exchange_Rate</f>
+        <v>0.159</v>
+      </c>
+      <c r="J25" s="39">
+        <f>0.005*Exchange_Rate</f>
+        <v>5.3E-3</v>
+      </c>
+      <c r="K25" s="39">
+        <f>0.05*Exchange_Rate</f>
+        <v>5.3000000000000005E-2</v>
+      </c>
+      <c r="L25" s="39">
+        <f>0.08*Exchange_Rate</f>
+        <v>8.48E-2</v>
+      </c>
       <c r="M25" s="39"/>
     </row>
     <row r="27" spans="2:13">
@@ -7423,7 +7455,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7476,43 +7508,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0</v>
+        <v>0.12804800000000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0</v>
+        <v>0.21942</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>0.18868000000000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>0.1643</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>8.48E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>8.0560000000000007E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>5.3E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>5.3000000000000005E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>8.48E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8803,7 +8835,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8830,11 +8862,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.9931186550976139</v>
+        <v>4.2327057744034713</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.6893987527114966</v>
+        <v>1.7907626778741865</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9025,7 +9057,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>9855306.4750236981</v>
+        <v>9778473.1416903641</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9092,11 +9124,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-915012.66666666663</v>
+        <v>-964204.44</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-918168.26248815109</v>
+        <v>-956584.92915481783</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>361</v>
@@ -9108,11 +9140,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>12.777575028105257</v>
+        <v>12.125688821760663</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>12.733660569269437</v>
+        <v>12.222273886679407</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>328</v>
@@ -9125,7 +9157,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1836336.5249763022</v>
+        <v>1913169.8583096357</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>362</v>
@@ -9240,11 +9272,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2119124</v>
+        <v>-2246271.44</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.45967982646420824</v>
+        <v>-0.48726061605206072</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9257,11 +9289,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>9855306.4750236981</v>
+        <v>10365181.530191787</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1378105151895226</v>
+        <v>2.2484124794342271</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9274,11 +9306,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>52579.6</v>
+        <v>55734.376000000004</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1405553145336226E-2</v>
+        <v>1.20898863340564E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9291,11 +9323,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>7788762.0750236977</v>
+        <v>8174644.4661917873</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.6895362418706508</v>
+        <v>1.7732417497162227</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9332,7 +9364,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
         <v>57</v>
@@ -9875,24 +9907,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-25213.952125355467</v>
+        <v>-24061.452125355467</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>2383.0383934644778</v>
+        <v>4690.2117023541432</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>22034.654678691666</v>
+        <v>24386.916047488732</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>20053.210923741812</v>
+        <v>22122.109509395399</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>7980.0191567487709</v>
+        <v>10429.324014928243</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9930,24 +9962,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>903225.89801683102</v>
+        <v>904378.39801683102</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>968690.03839346452</v>
+        <v>970997.21170235414</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1337806.6546786916</v>
+        <v>1340158.9160474888</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>1918186.2109237418</v>
+        <v>1920255.1095093954</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>1921133.0191567487</v>
+        <v>1923582.3240149282</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9985,7 +10017,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-225806.47450420776</v>
+        <v>-226094.59950420776</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10097,26 +10129,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>546774.39908131293</v>
+        <v>547638.77408131293</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>572742.03839346452</v>
+        <v>575049.21170235414</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1047919.6546786916</v>
+        <v>1050271.9160474888</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>1289995.2109237418</v>
+        <v>1292064.1095093954</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>777125.01915674866</v>
+        <v>779574.32401492819</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10205,26 +10237,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>546774.39908131293</v>
+        <v>547638.77408131293</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>572742.03839346452</v>
+        <v>575049.21170235414</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1047919.6546786916</v>
+        <v>1050271.9160474888</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>1289995.2109237418</v>
+        <v>1292064.1095093954</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>777125.01915674866</v>
+        <v>779574.32401492819</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11066,19 +11098,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.32630871328482591</v>
+        <v>0.32553337557563827</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21668826282645734</v>
+        <v>0.21630792925286765</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.24608507626205953</v>
+        <v>0.24581994218497374</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.5206151734558232</v>
+        <v>0.51995227212965289</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11204,24 +11236,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>27545.047874644533</v>
+        <v>28697.547874644533</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>55142.038393464478</v>
+        <v>57449.211702354143</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>56219.654678691666</v>
+        <v>58571.916047488732</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>49447.210923741812</v>
+        <v>51516.109509395399</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>58539.019156748771</v>
+        <v>60988.324014928243</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11316,24 +11348,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-25213.952125355467</v>
+        <v>-24061.452125355467</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>2383.0383934644778</v>
+        <v>4690.2117023541432</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>22034.654678691666</v>
+        <v>24386.916047488732</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>20053.210923741812</v>
+        <v>22122.109509395399</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>7980.0191567487709</v>
+        <v>10429.324014928243</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12290,7 +12322,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12402,26 +12434,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.11057955544446E-3</v>
+        <v>2.0141074543808726E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.9947654727350405E-4</v>
+        <v>3.9260267015976392E-4</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.6963002045516575E-3</v>
+        <v>1.8773850229540099E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>1.4043795144791673E-3</v>
+        <v>1.5492699663013669E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>5.9561235944543178E-4</v>
+        <v>7.7842348018662493E-4</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12459,26 +12491,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>7.5606160621890642E-2</v>
+        <v>7.570263272295423E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>8.1085955126407289E-2</v>
+        <v>8.1279081249293547E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10298875725865367</v>
+        <v>0.10316984207705603</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13433566473827621</v>
+        <v>0.13448055519009841</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.14338945156300464</v>
+        <v>0.14357226268374584</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12516,7 +12548,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>1.890154015547266E-2</v>
+        <v>1.8925658180738558E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12631,26 +12663,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>4.5768741941131924E-2</v>
+        <v>4.5841096016929615E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>4.7942410248381091E-2</v>
+        <v>4.813553637126735E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0672302357620296E-2</v>
+        <v>8.0853387176022667E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0341783911156992E-2</v>
+        <v>9.0486674362979191E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8003026954212049E-2</v>
+        <v>5.8185838074953249E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12738,26 +12770,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>4.5768741941131924E-2</v>
+        <v>4.5841096016929615E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>4.7942410248381091E-2</v>
+        <v>4.813553637126735E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0672302357620296E-2</v>
+        <v>8.0853387176022667E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0341783911156992E-2</v>
+        <v>9.0486674362979191E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8003026954212049E-2</v>
+        <v>5.8185838074953249E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12806,49 +12838,48 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C90" s="114">
-        <f>G90</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0</v>
+        <v>0.12804800000000002</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0</v>
+        <v>0.21942</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0</v>
+        <v>0.18868000000000001</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0</v>
+        <v>0.1643</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0</v>
+        <v>8.48E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>0</v>
+        <v>8.0560000000000007E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>0</v>
+        <v>5.3E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>0</v>
+        <v>5.3000000000000005E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>0</v>
+        <v>8.48E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -12863,48 +12894,48 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>0</v>
+        <v>461000</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>0</v>
+        <v>590301.28000000014</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1011526.2</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>869814.80000000016</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>757423</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>390928</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>371381.60000000003</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>732990</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>24433</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>244330.00000000003</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>390928</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12918,48 +12949,48 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0</v>
+        <v>0.84179576359133257</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0</v>
+        <v>1.0265230661781002</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.96310887165934944</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.67319786502720369</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.9715853596859817</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.89702916225909413</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1.099500552145968</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.57960413999568261</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>6.2161783974252961E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>-0.5894941540362002</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.6488808478500826</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12973,48 +13004,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0</v>
+        <v>5.1282051282051287E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0</v>
+        <v>6.5665641025641042E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.11252307692307693</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>9.6758974358974362E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>8.4256410256410258E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>4.3487179487179485E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>4.1312820512820515E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>8.1538461538461546E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>2.7179487179487178E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>2.7179487179487184E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>4.3487179487179485E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13110,26 +13141,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-6.7580069766386086E-2</v>
+        <v>-6.8608656011202029E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.27591178067048849</v>
+        <v>-0.27546114115622788</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.30256684827567215</v>
+        <v>-0.30209329509875127</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-1.5338907840438676E-3</v>
+        <v>-1.7296969638336268E-3</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.5824005913929731</v>
+        <v>1.5856929643058288</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13663,7 +13694,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13715,25 +13746,25 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>2.6583573370495825</v>
+        <v>2.6476916566717676</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.4730375493083954</v>
+        <v>1.4697384328899867</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.6608410495305728</v>
+        <v>1.6581816523125246</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.7815125334515232</v>
+        <v>3.7696315918477148</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13829,24 +13860,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>7.5606160621890642E-2</v>
+        <v>7.570263272295423E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>8.1085955126407289E-2</v>
+        <v>8.1279081249293547E-2</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10298875725865367</v>
+        <v>0.10316984207705603</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13433566473827621</v>
+        <v>0.13448055519009841</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.14338945156300464</v>
+        <v>0.14357226268374584</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14115,50 +14146,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.11860616032132601</v>
+        <v>0.12592127994060556</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.12423905388144568</v>
+        <v>0.13222389683394697</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.22731445871555134</v>
+        <v>0.24149419327773064</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.27982542536306765</v>
+        <v>0.29709066292406927</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.16857375686697368</v>
+        <v>0.17925136300560171</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>9.4534273318872014E-2</v>
+        <v>0.10020632971800433</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.326963123644252E-2</v>
+        <v>7.7665809110629078E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.27432516268980478</v>
+        <v>0.2907846724511931</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>8.5261388286334061E-2</v>
+        <v>9.0377071583514115E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-8.9907592190889368E-2</v>
+        <v>-9.5302047722342742E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.13068655097613882</v>
+        <v>0.13852774403470716</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14172,50 +14203,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0823671959654366E-2</v>
+        <v>6.4575015354156703E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.37123353238183E-2</v>
+        <v>6.7807126581511265E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11657151729002634</v>
+        <v>0.12384317603986186</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.14350021813490649</v>
+        <v>0.15235418611490731</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.6448080444601894E-2</v>
+        <v>9.1923775900308577E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.8479114522498472E-2</v>
+        <v>5.1387861393848377E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.757416986484232E-2</v>
+        <v>3.9828620056732864E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.14067957061015629</v>
+        <v>0.1491203448467657</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.37237888647867E-2</v>
+        <v>4.6347216196673903E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.6106457533789419E-2</v>
+        <v>-4.8872844985816795E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7018744090327598E-2</v>
+        <v>7.1039868735747261E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14224,7 +14255,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15015,11 +15046,11 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>546774.39908131293</v>
+        <v>547638.77408131293</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
         <v>251</v>
@@ -15047,11 +15078,11 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>6834679.9885164117</v>
+        <v>6845484.6760164117</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E6" s="348" t="s">
         <v>250</v>
@@ -15069,7 +15100,7 @@
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E7" s="348"/>
       <c r="F7" s="348"/>
@@ -15081,11 +15112,11 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>9855306.4750236981</v>
+        <v>9778473.1416903641</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E8" s="348"/>
       <c r="F8" s="348"/>
@@ -15101,7 +15132,7 @@
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E9" s="348"/>
       <c r="F9" s="348"/>
@@ -15113,11 +15144,11 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>14623442.06354011</v>
+        <v>14557413.417706775</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H10" s="121"/>
     </row>
@@ -15127,11 +15158,11 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="H11" s="121"/>
     </row>
@@ -15141,7 +15172,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15174,7 +15205,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15184,7 +15215,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -15194,7 +15225,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.5749449798714292</v>
+        <v>3.4488765062257274</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15229,11 +15260,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>572240.34612452588</v>
+        <v>558591.54956293921</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15241,7 +15272,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>529852.17233752389</v>
+        <v>517214.39774346218</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15251,11 +15282,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>598892.36636337009</v>
+        <v>569763.38055419805</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15263,7 +15294,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>513453.67486571509</v>
+        <v>488480.26453549211</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15273,11 +15304,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>626785.70100379828</v>
+        <v>581158.64816528198</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15285,7 +15316,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>497562.69766724313</v>
+        <v>461342.47206129803</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15295,11 +15326,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>655978.16410379822</v>
+        <v>592781.82112858759</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15307,7 +15338,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>482163.53339890245</v>
+        <v>435712.33472455922</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15317,11 +15348,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>686530.26240364404</v>
+        <v>604637.45755115931</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15329,7 +15360,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>467240.96084709343</v>
+        <v>411506.09390652814</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15339,11 +15370,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>718505.32073722617</v>
+        <v>616730.20670218254</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15351,7 +15382,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>452780.22988250316</v>
+        <v>388644.64424505428</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15361,11 +15392,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>751969.61328439775</v>
+        <v>629064.81083622621</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15373,7 +15404,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>438767.04688042717</v>
+        <v>367053.27512032911</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15383,11 +15414,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>786992.50093638164</v>
+        <v>641646.10705295065</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15395,7 +15426,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>425187.560592319</v>
+        <v>346661.42650253297</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15405,11 +15436,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>823646.57505895442</v>
+        <v>654479.02919400972</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15417,7 +15448,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>412028.34845460573</v>
+        <v>327402.45836350339</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15427,11 +15458,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>862007.80795138143</v>
+        <v>667568.60977788991</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15439,7 +15470,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>399276.403321233</v>
+        <v>309213.43289886427</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15449,19 +15480,19 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>902155.71031295741</v>
+        <v>0</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <v>0</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>386919.12060682842</v>
+        <v>0</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15471,19 +15502,19 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>944173.49604353146</v>
+        <v>0</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <v>0</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>374944.28582777269</v>
+        <v>0</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15493,19 +15524,19 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>988148.25471959403</v>
+        <v>0</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <v>0</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>363340.06252886512</v>
+        <v>0</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15515,19 +15546,19 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>1034171.1321034164</v>
+        <v>0</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <v>0</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>352094.98058364849</v>
+        <v>0</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15537,19 +15568,19 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>1082337.5190593805</v>
+        <v>0</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0.31524170496588994</v>
+        <v>0</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>341197.9248568305</v>
+        <v>0</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15889,7 +15920,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>7153004.3265565736</v>
+        <v>6982394.3695367398</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15897,11 +15928,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.31524170496588994</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>2254925.2795320814</v>
+        <v>3234199.6032085824</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15912,7 +15943,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>8691734.2821835913</v>
+        <v>7287430.4033102058</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15933,7 +15964,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>8691734.2821835913</v>
+        <v>7287430.4033102058</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15941,7 +15972,7 @@
       </c>
       <c r="C55" s="132">
         <f>C77</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D55" s="132">
         <f>C76</f>
@@ -15949,11 +15980,11 @@
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -15963,19 +15994,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>6834679.9885164108</v>
+        <v>6845484.6760164108</v>
       </c>
       <c r="C56" s="124">
-        <v>6834679.9885164108</v>
+        <v>6955111.1823613569</v>
       </c>
       <c r="D56" s="124">
-        <v>7055202.5426627398</v>
+        <v>7066355.8459411301</v>
       </c>
       <c r="E56" s="124">
-        <v>7282329.6510735676</v>
+        <v>7179254.1201073788</v>
       </c>
       <c r="F56" s="124">
-        <v>7516351.1429258529</v>
+        <v>7179254.1201073788</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15984,19 +16015,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>6834679.988516409</v>
+        <v>6845484.676016409</v>
       </c>
       <c r="C57" s="124">
-        <v>6834679.988516409</v>
+        <v>7061230.3512272798</v>
       </c>
       <c r="D57" s="124">
-        <v>7275928.1632333808</v>
+        <v>7287430.4033102058</v>
       </c>
       <c r="E57" s="124">
-        <v>7761401.3523080619</v>
+        <v>7524695.7799897753</v>
       </c>
       <c r="F57" s="124">
-        <v>8296392.3208651114</v>
+        <v>7524695.7799897753</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16005,19 +16036,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>6834679.9885164071</v>
+        <v>6845484.6760164071</v>
       </c>
       <c r="C58" s="124">
-        <v>6834679.9885164071</v>
+        <v>7189317.0636369651</v>
       </c>
       <c r="D58" s="124">
-        <v>7549137.3201691713</v>
+        <v>7561071.4662851654</v>
       </c>
       <c r="E58" s="124">
-        <v>8385932.0684122788</v>
+        <v>7963395.6280424176</v>
       </c>
       <c r="F58" s="124">
-        <v>9369369.0560005996</v>
+        <v>7963395.6280424176</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16026,19 +16057,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>6834679.9885164071</v>
+        <v>6845484.6760164071</v>
       </c>
       <c r="C59" s="124">
-        <v>6834679.9885164071</v>
+        <v>7316450.0839890596</v>
       </c>
       <c r="D59" s="124">
-        <v>7827493.6372053726</v>
+        <v>7839867.8263115697</v>
       </c>
       <c r="E59" s="124">
-        <v>9058130.7502612546</v>
+        <v>8422602.6695664581</v>
       </c>
       <c r="F59" s="124">
-        <v>10593343.860637248</v>
+        <v>8422602.6695664581</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16047,19 +16078,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>6834679.988516408</v>
+        <v>6845484.6760164062</v>
       </c>
       <c r="C60" s="124">
-        <v>6834679.988516408</v>
+        <v>7431557.6000728682</v>
       </c>
       <c r="D60" s="124">
-        <v>8086380.4580437485</v>
+        <v>8099163.9115488231</v>
       </c>
       <c r="E60" s="124">
-        <v>9720269.3195986785</v>
+        <v>8861869.696615696</v>
       </c>
       <c r="F60" s="124">
-        <v>11876032.241067521</v>
+        <v>8861869.696615696</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16068,19 +16099,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>6834679.988516408</v>
+        <v>6845484.6760164071</v>
       </c>
       <c r="C61" s="124">
-        <v>6834679.988516408</v>
+        <v>7530343.1967899622</v>
       </c>
       <c r="D61" s="124">
-        <v>8314754.6472975221</v>
+        <v>8327899.1289344318</v>
       </c>
       <c r="E61" s="124">
-        <v>10340367.957803952</v>
+        <v>9260821.8524683584</v>
       </c>
       <c r="F61" s="124">
-        <v>13158557.616912102</v>
+        <v>9260821.8524683584</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16108,7 +16139,7 @@
       </c>
       <c r="C64" s="133">
         <f>C55</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D64" s="133">
         <f>D55</f>
@@ -16116,11 +16147,11 @@
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -16130,23 +16161,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16157,23 +16188,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1721132458872252</v>
+        <v>3.3472577489737922</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872252</v>
+        <v>3.3724647113871637</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.2199489409298132</v>
+        <v>3.3980437446614711</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.2692172941642661</v>
+        <v>3.4240030007604356</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.3199811752602062</v>
+        <v>3.4240030007604356</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16184,23 +16215,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.3968652144235798</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2678286850883032</v>
+        <v>3.4488765062257274</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.3731374028919219</v>
+        <v>3.5034321025989041</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.4891875045311949</v>
+        <v>3.5034321025989041</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16211,23 +16242,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872243</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872243</v>
+        <v>3.4263168229169128</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3270931442934639</v>
+        <v>3.5117961432655234</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.5086104432615999</v>
+        <v>3.6043045188539584</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7219373386169852</v>
+        <v>3.6043045188539584</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16238,23 +16269,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872243</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872243</v>
+        <v>3.4555491442993906</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.387474124127781</v>
+        <v>3.5759011631414426</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.6544236063524846</v>
+        <v>3.7098922550829134</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.987441634633611</v>
+        <v>3.7098922550829134</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16265,23 +16296,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.4820163822709387</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.4436317859148473</v>
+        <v>3.6355223888142167</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.7980545324560473</v>
+        <v>3.810895085597489</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>4.2656820642280309</v>
+        <v>3.810895085597489</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16291,23 +16322,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1721132458872248</v>
+        <v>3.5047306409520931</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.4931706556011322</v>
+        <v>3.6881166036577619</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.9325661676415735</v>
+        <v>3.902628119264262</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>4.5438871349101513</v>
+        <v>3.902628119264262</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16334,15 +16365,15 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>4.5438871349101513</v>
+        <v>3.6043045188539584</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16356,15 +16387,15 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.5086104432615999</v>
+        <v>3.5034321025989041</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16383,11 +16414,11 @@
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.3270931442934639</v>
+        <v>3.4488765062257274</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16402,15 +16433,15 @@
       </c>
       <c r="C77" s="143">
         <f>Scenarios!C32</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.1721132458872243</v>
+        <v>3.3968652144235798</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16429,11 +16460,11 @@
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1721132458872248</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16554,7 +16585,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16563,7 +16594,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16583,7 +16614,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>3.3849605810051271</v>
+        <v>3.5520249438173268</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16596,11 +16627,11 @@
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 15-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="350"/>
       <c r="H7" s="276">
@@ -16617,11 +16648,11 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>572742.03839346452</v>
+        <v>575049.21170235414</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E8" s="350"/>
       <c r="F8" s="350"/>
@@ -16639,11 +16670,11 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>546774.39908131293</v>
+        <v>547638.77408131293</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E9" s="350"/>
       <c r="F9" s="350"/>
@@ -16723,7 +16754,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-9.6719316018011758E-2</v>
+        <v>-9.6456300478413137E-2</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16750,7 +16781,7 @@
         <v>134</v>
       </c>
       <c r="C18" s="151">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
         <v>340</v>
@@ -16789,7 +16820,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.1721132458872257</v>
+        <v>3.3472577489737918</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16813,7 +16844,7 @@
       </c>
       <c r="C25" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="164"/>
       <c r="E25" s="349"/>
@@ -16836,7 +16867,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.3270931442934639</v>
+        <v>3.4488765062257274</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16871,7 +16902,7 @@
       </c>
       <c r="C31" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D31" s="164"/>
       <c r="E31" s="349"/>
@@ -16882,7 +16913,7 @@
         <v>135</v>
       </c>
       <c r="C32" s="165">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="349"/>
@@ -16894,7 +16925,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.1721132458872243</v>
+        <v>3.3968652144235798</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16929,7 +16960,7 @@
       </c>
       <c r="C37" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37" s="164"/>
       <c r="E37" s="349"/>
@@ -16940,7 +16971,7 @@
         <v>135</v>
       </c>
       <c r="C38" s="165">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="349"/>
@@ -16952,7 +16983,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.5086104432615999</v>
+        <v>3.5034321025989041</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16979,7 +17010,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.3324006244058428</v>
+        <v>3.449385367139933</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17005,7 +17036,7 @@
         <v>134</v>
       </c>
       <c r="C46" s="151">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -17030,7 +17061,7 @@
       </c>
       <c r="C49" s="167">
         <f>C46</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D49" s="164"/>
       <c r="E49" s="349"/>
@@ -17053,7 +17084,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.1721132458872248</v>
+        <v>3.3472577489737914</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17088,7 +17119,7 @@
       </c>
       <c r="C55" s="167">
         <f>C46</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D55" s="164"/>
       <c r="E55" s="349"/>
@@ -17099,7 +17130,7 @@
         <v>135</v>
       </c>
       <c r="C56" s="165">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="349"/>
@@ -17111,7 +17142,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>4.5438871349101513</v>
+        <v>3.6043045188539584</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17137,7 +17168,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.3849605810051271</v>
+        <v>3.4520249438173267</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17174,11 +17205,11 @@
       </c>
       <c r="C64" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17186,7 +17217,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>4.6574870890079501E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -17199,7 +17230,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.5749449798714292</v>
+        <v>3.4488765062257274</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17255,14 +17286,14 @@
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
         <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.49913025615469986</v>
+        <v>0.51368161545070767</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17295,7 +17326,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17353,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>0.18161128812016392</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17334,7 +17365,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.5407194269481685</v>
+        <v>1.5712448538085233</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17344,7 +17375,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.5407194269481685</v>
+        <v>1.7528561419286872</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17355,7 +17386,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.54483386436049175</v>
+        <v>0.4922237902515445</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17385,7 +17416,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20182066703946511</v>
+        <v>0.25280122918191261</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17393,12 +17424,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17411,7 +17442,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>0.21064814814814814</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17423,7 +17454,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.9588892251187078</v>
+        <v>1.9976996202646566</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17433,7 +17464,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.9588892251187078</v>
+        <v>2.2083477684128048</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17444,19 +17475,19 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.42129629629629628</v>
+        <v>0.36027467809350067</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17471,7 +17502,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>0.25770969872478805</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17483,7 +17514,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.6870908437842354</v>
+        <v>2.7403286972080334</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17491,21 +17522,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.6870908437842354</v>
+        <v>2.9980383959328214</v>
       </c>
       <c r="D99" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.20616775897983042</v>
+        <v>0.13151311339670591</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD40288-8275-4FBA-A01C-A537F2564267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE2E5B1-0D59-432E-92AA-7FA746B3F863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v>Low Growth Asset Play</v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>1.7528561419286872</v>
+        <v>1.582657938626912</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>316</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25280122918191261</v>
+        <v>0.20890029037251456</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>349</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>28697.547874644533</v>
+        <v>57395.095749289067</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-24061.452125355467</v>
+        <v>4636.0957492890666</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-226094.59950420776</v>
+        <v>-233268.98647286888</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>348</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>353</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>575049.21170235414</v>
+        <v>632498.42340470827</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>547638.77408131293</v>
+        <v>569161.93498729635</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.4575015354156703E-2</v>
+        <v>6.7112926312535084E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.5740159992575697</v>
+        <v>1.6358775788680426</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>354</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>9778473.1416903641</v>
+        <v>7865303.2833807282</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2484124794342271</v>
+        <v>1.8085079133153084</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.6 HKD</v>
+        <v>3.24 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.5 HKD</v>
+        <v>3.13 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.45 HKD</v>
+        <v>3.07 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.4 HKD</v>
+        <v>3.02 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>3.35 HKD</v>
+        <v>2.97 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>3.4520249438173267</v>
+        <v>3.0780994911633259</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>1.5712448538085233</v>
+        <v>1.401046650506748</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>1.7528561419286872</v>
+        <v>1.582657938626912</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4922237902515445</v>
+        <v>0.48583275388906688</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>1.9976996202646566</v>
+        <v>1.7813075759047026</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>2.2083477684128048</v>
+        <v>1.9919557240528507</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.36027467809350067</v>
+        <v>0.35286181302085917</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>2.7403286972080334</v>
+        <v>2.4434946171532266</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>2.9980383959328214</v>
+        <v>2.7012043158780146</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.13151311339670591</v>
+        <v>0.12244411734166172</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>393</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>394</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>9778473.1416903641</v>
+        <v>7865303.2833807282</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9157,7 +9157,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1913169.8583096357</v>
+        <v>3826339.7166192713</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>362</v>
@@ -9169,8 +9169,8 @@
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
-        <v>2</v>
+        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))*2</f>
+        <v>4</v>
       </c>
       <c r="F76" s="283" t="s">
         <v>333</v>
@@ -9289,11 +9289,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>10365181.530191787</v>
+        <v>8337221.4803835722</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2484124794342271</v>
+        <v>1.8085079133153086</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9323,11 +9323,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>8174644.4661917873</v>
+        <v>6146684.4163835719</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.7732417497162227</v>
+        <v>1.3333371835973042</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9907,24 +9907,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-24061.452125355467</v>
+        <v>4636.0957492890666</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>4690.2117023541432</v>
+        <v>62139.423404708286</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>24386.916047488732</v>
+        <v>82958.832094977464</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>22122.109509395399</v>
+        <v>73638.219018790798</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>10429.324014928243</v>
+        <v>71417.648029856486</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9962,24 +9962,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>904378.39801683102</v>
+        <v>933075.94589147554</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>970997.21170235414</v>
+        <v>1028446.4234047083</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1340158.9160474888</v>
+        <v>1398730.8320949774</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>1920255.1095093954</v>
+        <v>1971771.2190187909</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>1923582.3240149282</v>
+        <v>1984570.6480298564</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-226094.59950420776</v>
+        <v>-233268.98647286888</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10129,26 +10129,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>547638.77408131293</v>
+        <v>569161.93498729635</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>575049.21170235414</v>
+        <v>632498.42340470827</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1050271.9160474888</v>
+        <v>1108843.8320949774</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>1292064.1095093954</v>
+        <v>1343580.2190187909</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>779574.32401492819</v>
+        <v>840562.64802985638</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10237,26 +10237,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>547638.77408131293</v>
+        <v>569161.93498729635</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>575049.21170235414</v>
+        <v>632498.42340470827</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1050271.9160474888</v>
+        <v>1108843.8320949774</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>1292064.1095093954</v>
+        <v>1343580.2190187909</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>779574.32401492819</v>
+        <v>840562.64802985638</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11098,19 +11098,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.32553337557563827</v>
+        <v>0.30734901965390304</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21630792925286765</v>
+        <v>0.20725002505722698</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.24581994218497374</v>
+        <v>0.23939744907875213</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.51995227212965289</v>
+        <v>0.50397349219736776</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11236,24 +11236,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>28697.547874644533</v>
+        <v>57395.095749289067</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>57449.211702354143</v>
+        <v>114898.42340470829</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>58571.916047488732</v>
+        <v>117143.83209497746</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>51516.109509395399</v>
+        <v>103032.2190187908</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>60988.324014928243</v>
+        <v>121976.64802985649</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11348,24 +11348,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-24061.452125355467</v>
+        <v>4636.0957492890666</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>4690.2117023541432</v>
+        <v>62139.423404708286</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>24386.916047488732</v>
+        <v>82958.832094977464</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>22122.109509395399</v>
+        <v>73638.219018790798</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>10429.324014928243</v>
+        <v>71417.648029856486</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12434,26 +12434,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.0141074543808726E-3</v>
+        <v>3.8807279623937656E-4</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>3.9260267015976392E-4</v>
+        <v>5.2014930453206498E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.8773850229540099E-3</v>
+        <v>6.3864438042753333E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>1.5492699663013669E-3</v>
+        <v>5.1570796649967705E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>7.7842348018662493E-4</v>
+        <v>5.3304676359244218E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12491,26 +12491,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>7.570263272295423E-2</v>
+        <v>7.8104812973574481E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>8.1279081249293547E-2</v>
+        <v>8.6087971624454432E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10316984207705603</v>
+        <v>0.10767890085837734</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13448055519009841</v>
+        <v>0.13808836488879381</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.14357226268374584</v>
+        <v>0.14812430683948363</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>1.8925658180738558E-2</v>
+        <v>1.952620324339362E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12663,26 +12663,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>4.5841096016929615E-2</v>
+        <v>4.7642731204894803E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>4.813553637126735E-2</v>
+        <v>5.2944426746428234E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0853387176022667E-2</v>
+        <v>8.5362445957343977E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0486674362979191E-2</v>
+        <v>9.4094484061674588E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8185838074953249E-2</v>
+        <v>6.2737882230691044E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12770,26 +12770,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>4.5841096016929615E-2</v>
+        <v>4.7642731204894803E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>4.813553637126735E-2</v>
+        <v>5.2944426746428234E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0853387176022667E-2</v>
+        <v>8.5362445957343977E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0486674362979191E-2</v>
+        <v>9.4094484061674588E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8185838074953249E-2</v>
+        <v>6.2737882230691044E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12949,24 +12949,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.84179576359133257</v>
+        <v>0.80996280963569622</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>1.0265230661781002</v>
+        <v>0.9332849824706867</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.96310887165934944</v>
+        <v>0.91223504223213125</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.67319786502720369</v>
+        <v>0.64738583352709733</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.9715853596859817</v>
+        <v>0.90109048001987424</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
@@ -13141,26 +13141,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-6.8608656011202029E-2</v>
+        <v>-9.2732567630995688E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.27546114115622788</v>
+        <v>-0.26472885289564119</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.30209329509875127</v>
+        <v>-0.2906221479431953</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-1.7296969638336268E-3</v>
+        <v>-6.4494700774557767E-3</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.5856929643058288</v>
+        <v>1.6676739007811947</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13752,19 +13752,19 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>2.6476916566717676</v>
+        <v>2.4072044192682269</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.4697384328899867</v>
+        <v>1.3921031576498697</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.6581816523125246</v>
+        <v>1.5946029642834716</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.7696315918477148</v>
+        <v>3.4961201367772632</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13860,24 +13860,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>7.570263272295423E-2</v>
+        <v>7.8104812973574481E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>8.1279081249293547E-2</v>
+        <v>8.6087971624454432E-2</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10316984207705603</v>
+        <v>0.10767890085837734</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13448055519009841</v>
+        <v>0.13808836488879381</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.14357226268374584</v>
+        <v>0.14812430683948363</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14146,26 +14146,26 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.12592127994060556</v>
+        <v>0.13087020630944343</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.13222389683394697</v>
+        <v>0.14543347696507392</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24149419327773064</v>
+        <v>0.25496192234721826</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29709066292406927</v>
+        <v>0.30893601565291073</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.17925136300560171</v>
+        <v>0.19327470865762428</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
@@ -14203,26 +14203,26 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4575015354156703E-2</v>
+        <v>6.7112926312535084E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.7807126581511265E-2</v>
+        <v>7.4581270238499447E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12384317603986186</v>
+        <v>0.13074970376780423</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15235418611490731</v>
+        <v>0.15842872597585167</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.1923775900308577E-2</v>
+        <v>9.9115235209038088E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>547638.77408131293</v>
+        <v>569161.93498729635</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>6845484.6760164117</v>
+        <v>7114524.1873412039</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>9778473.1416903641</v>
+        <v>7865303.2833807282</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>14557413.417706775</v>
+        <v>12913283.070721932</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.4488765062257274</v>
+        <v>3.0748273144719884</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>558591.54956293921</v>
+        <v>580545.17368704232</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>517214.39774346218</v>
+        <v>537541.82748800213</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>569763.38055419805</v>
+        <v>592156.07716078323</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>488480.26453549211</v>
+        <v>507678.39262755762</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>581158.64816528198</v>
+        <v>603999.19870399882</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>461342.47206129803</v>
+        <v>479474.03748158208</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>592781.82112858759</v>
+        <v>616079.18267807877</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>435712.33472455922</v>
+        <v>452836.59095482749</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>604637.45755115931</v>
+        <v>628400.76633164042</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>411506.09390652814</v>
+        <v>427679.00256844825</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>616730.20670218254</v>
+        <v>640968.78165827319</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>388644.64424505428</v>
+        <v>403919.0579813121</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>629064.81083622621</v>
+        <v>653788.15729143866</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>367053.27512032911</v>
+        <v>381479.11031568371</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>641646.10705295065</v>
+        <v>666863.92043726728</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>346661.42650253297</v>
+        <v>360285.82640925673</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>654479.02919400972</v>
+        <v>680201.1988460127</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>327402.45836350339</v>
+        <v>340269.94716429804</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>667568.60977788991</v>
+        <v>693805.22282293299</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>309213.43289886427</v>
+        <v>321366.06121072592</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>6982394.3695367398</v>
+        <v>7256814.6710880287</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15932,7 +15932,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3234199.6032085824</v>
+        <v>3361309.2998853745</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>7287430.4033102058</v>
+        <v>7573839.1540870694</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15964,7 +15964,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>7287430.4033102058</v>
+        <v>7573839.1540870694</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15994,19 +15994,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>6845484.6760164108</v>
+        <v>7114524.187341203</v>
       </c>
       <c r="C56" s="124">
-        <v>6955111.1823613569</v>
+        <v>7228459.2069750074</v>
       </c>
       <c r="D56" s="124">
-        <v>7066355.8459411301</v>
+        <v>7344075.9802509518</v>
       </c>
       <c r="E56" s="124">
-        <v>7179254.1201073788</v>
+        <v>7461411.3538993616</v>
       </c>
       <c r="F56" s="124">
-        <v>7179254.1201073788</v>
+        <v>7461411.3538993616</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16015,19 +16015,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>6845484.676016409</v>
+        <v>7114524.1873412021</v>
       </c>
       <c r="C57" s="124">
-        <v>7061230.3512272798</v>
+        <v>7338749.0446372405</v>
       </c>
       <c r="D57" s="124">
-        <v>7287430.4033102058</v>
+        <v>7573839.1540870694</v>
       </c>
       <c r="E57" s="124">
-        <v>7524695.7799897753</v>
+        <v>7820429.4747285768</v>
       </c>
       <c r="F57" s="124">
-        <v>7524695.7799897753</v>
+        <v>7820429.4747285768</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16036,19 +16036,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>6845484.6760164071</v>
+        <v>7114524.1873412021</v>
       </c>
       <c r="C58" s="124">
-        <v>7189317.0636369651</v>
+        <v>7471869.7886962304</v>
       </c>
       <c r="D58" s="124">
-        <v>7561071.4662851654</v>
+        <v>7858234.7890675925</v>
       </c>
       <c r="E58" s="124">
-        <v>7963395.6280424176</v>
+        <v>8276370.9935064297</v>
       </c>
       <c r="F58" s="124">
-        <v>7963395.6280424176</v>
+        <v>8276370.9935064297</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16057,19 +16057,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>6845484.6760164071</v>
+        <v>7114524.1873412011</v>
       </c>
       <c r="C59" s="124">
-        <v>7316450.0839890596</v>
+        <v>7603999.3589330409</v>
       </c>
       <c r="D59" s="124">
-        <v>7839867.8263115697</v>
+        <v>8147988.3332833685</v>
       </c>
       <c r="E59" s="124">
-        <v>8422602.6695664581</v>
+        <v>8753625.6742986385</v>
       </c>
       <c r="F59" s="124">
-        <v>8422602.6695664581</v>
+        <v>8753625.6742986385</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16078,19 +16078,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>6845484.6760164062</v>
+        <v>7114524.1873412021</v>
       </c>
       <c r="C60" s="124">
-        <v>7431557.6000728682</v>
+        <v>7723630.8015673673</v>
       </c>
       <c r="D60" s="124">
-        <v>8099163.9115488231</v>
+        <v>8417475.2078309935</v>
       </c>
       <c r="E60" s="124">
-        <v>8861869.696615696</v>
+        <v>9210156.6631988883</v>
       </c>
       <c r="F60" s="124">
-        <v>8861869.696615696</v>
+        <v>9210156.6631988883</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16099,19 +16099,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>6845484.6760164071</v>
+        <v>7114524.187341203</v>
       </c>
       <c r="C61" s="124">
-        <v>7530343.1967899622</v>
+        <v>7826298.8448787555</v>
       </c>
       <c r="D61" s="124">
-        <v>8327899.1289344318</v>
+        <v>8655200.1190104969</v>
       </c>
       <c r="E61" s="124">
-        <v>9260821.8524683584</v>
+        <v>9624788.3360079788</v>
       </c>
       <c r="F61" s="124">
-        <v>9260821.8524683584</v>
+        <v>9624788.3360079788</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16161,23 +16161,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16188,23 +16188,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.3472577489737922</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.3724647113871637</v>
+        <v>2.9954124025546811</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.3980437446614711</v>
+        <v>3.0219967365400393</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.4240030007604356</v>
+        <v>3.0489762367715612</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.4240030007604356</v>
+        <v>3.0489762367715612</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16215,23 +16215,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.3968652144235798</v>
+        <v>3.0207718880041314</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.4488765062257274</v>
+        <v>3.0748273144719884</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.5034321025989041</v>
+        <v>3.131527041127085</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.5034321025989041</v>
+        <v>3.131527041127085</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16242,23 +16242,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.4263168229169128</v>
+        <v>3.0513809961825542</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.5117961432655234</v>
+        <v>3.1402198032093755</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.6043045188539584</v>
+        <v>3.2363639196313208</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.6043045188539584</v>
+        <v>3.2363639196313208</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16269,23 +16269,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4555491442993906</v>
+        <v>3.0817621988834265</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5759011631414426</v>
+        <v>3.2068442623999878</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.7098922550829134</v>
+        <v>3.3461014384251904</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.7098922550829134</v>
+        <v>3.3461014384251904</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16296,23 +16296,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.4820163822709387</v>
+        <v>3.109269645562903</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.6355223888142167</v>
+        <v>3.2688087064391378</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.810895085597489</v>
+        <v>3.4510738566972656</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.810895085597489</v>
+        <v>3.4510738566972656</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16322,23 +16322,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.5047306409520931</v>
+        <v>3.1328766143069529</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6881166036577619</v>
+        <v>3.3234699658426679</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.902628119264262</v>
+        <v>3.5464121589049959</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.902628119264262</v>
+        <v>3.5464121589049959</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.6043045188539584</v>
+        <v>3.2363639196313208</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.5034321025989041</v>
+        <v>3.131527041127085</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.4488765062257274</v>
+        <v>3.0748273144719884</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.3968652144235798</v>
+        <v>3.0207718880041314</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>3.5520249438173268</v>
+        <v>3.178099491163326</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>575049.21170235414</v>
+        <v>632498.42340470827</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>547638.77408131293</v>
+        <v>569161.93498729635</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-9.6456300478413137E-2</v>
+        <v>-9.0443280496378065E-2</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.3472577489737918</v>
+        <v>2.9692147624653469</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.4488765062257274</v>
+        <v>3.0748273144719884</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.3968652144235798</v>
+        <v>3.0207718880041314</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.5034321025989041</v>
+        <v>3.131527041127085</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.449385367139933</v>
+        <v>3.0753561745094364</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.3472577489737914</v>
+        <v>2.9692147624653464</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.6043045188539584</v>
+        <v>3.2363639196313208</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.4520249438173267</v>
+        <v>3.0780994911633259</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.4488765062257274</v>
+        <v>3.0748273144719884</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17286,14 +17286,14 @@
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
         <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.51368161545070767</v>
+        <v>0.43316896917239917</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.5712448538085233</v>
+        <v>1.401046650506748</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.7528561419286872</v>
+        <v>1.582657938626912</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.4922237902515445</v>
+        <v>0.48583275388906688</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.25280122918191261</v>
+        <v>0.20890029037251456</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.9976996202646566</v>
+        <v>1.7813075759047026</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>2.2083477684128048</v>
+        <v>1.9919557240528507</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.36027467809350067</v>
+        <v>0.35286181302085917</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.7403286972080334</v>
+        <v>2.4434946171532266</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.9980383959328214</v>
+        <v>2.7012043158780146</v>
       </c>
       <c r="D99" t="s">
         <v>407</v>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.13151311339670591</v>
+        <v>0.12244411734166172</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE2E5B1-0D59-432E-92AA-7FA746B3F863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3273BCD3-9F5F-4D81-A7EC-EA2BE81259EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1414,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1579,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1790,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2370,16 +2358,52 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>中海石油化学</t>
+  </si>
+  <si>
     <t>3983.HK</t>
   </si>
   <si>
-    <t>中海石油化学</t>
-  </si>
-  <si>
-    <t>CNY</t>
+    <t/>
   </si>
   <si>
     <t>ENG_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3053,7 +3077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,29 +3778,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4066,13 +4097,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4086,10 +4116,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>288</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4137,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>3983.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>425</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4118,343 +4147,335 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>428</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>4610000000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>1.95</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>4610000000</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>8989.5</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
-        <v>358</v>
+      <c r="B15" s="4" t="s">
+        <v>429</v>
       </c>
       <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1.06</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>429</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1.06</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>430</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E19" s="339">
+      <c r="D24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>1.582657938626912</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E20" s="330">
+      <c r="D25" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C21" s="280">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.20890029037251456</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>928439.85014218651</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>57395.095749289067</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>351</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-52759</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>4636.0957492890666</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4483,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-130645.02443131036</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>57395.095749289067</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-52759</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>4636.0957492890666</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-130645.02443131036</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-233268.98647286888</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>632498.42340470827</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>632498.42340470827</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>569161.93498729635</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
-        <v>401</v>
-      </c>
-      <c r="C58" s="92">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>6.7112926312535084E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
-        <v>317</v>
-      </c>
-      <c r="C59" s="92">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.1282051282051287E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="311">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
-        <v>367</v>
-      </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
     <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
+        <v>372</v>
+      </c>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6358775788680426</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
-        <v>368</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>2119124</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.48726061605206072</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C88" s="337">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.23422582328431374</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
-        <v>416</v>
-      </c>
-      <c r="C89" s="337">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.10863424600069688</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
-        <v>418</v>
-      </c>
-      <c r="C90" s="338">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>2.2824569622635926</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>11691643</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>7865303.2833807282</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8085079133153084</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>52579.6</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4869,591 +4898,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.20898863340564E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>7865303.2833807282</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8085079133153084</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>2.9692147624653469</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>52579.6</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>417</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>1.7907626778741865</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.20898863340564E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
-        <v>369</v>
-      </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>2.9692147624653469</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>1.7907626778741865</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.03</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>3.24 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.03</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>3.13 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>3.07 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.01</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>3.02 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.97 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>3.0780994911633259</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
-        <v>413</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="B124" s="348" t="s">
+        <v>378</v>
+      </c>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.1</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
-        <v>421</v>
-      </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>3983.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>0.18161128812016392</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>1.401046650506748</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>1.582657938626912</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.48583275388906688</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
-        <v>424</v>
-      </c>
-      <c r="C136" s="337">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>0.21064814814814814</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>1.7813075759047026</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>1.9919557240528507</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.35286181302085917</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
-        <v>411</v>
-      </c>
-      <c r="C142" s="92">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>0.25770969872478805</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>2.4434946171532266</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
-        <v>412</v>
-      </c>
-      <c r="C145" s="239">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>2.7012043158780146</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.12244411734166172</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
+        <v>388</v>
+      </c>
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
-        <v>391</v>
-      </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
-        <v>399</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5477,7 +5603,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -5992,7 +6118,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>1522553</v>
@@ -6028,7 +6154,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-379005</v>
@@ -6064,7 +6190,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-1061021</v>
@@ -6150,7 +6276,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7455,7 +7581,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8835,7 +8961,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -9041,7 +9167,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -9108,7 +9234,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -9120,7 +9246,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9131,12 +9257,12 @@
         <v>-956584.92915481783</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9147,12 +9273,12 @@
         <v>12.222273886679407</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -9160,12 +9286,12 @@
         <v>3826339.7166192713</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9173,7 +9299,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9249,7 +9375,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9260,15 +9386,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9285,7 +9411,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9319,7 +9445,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9363,7 +9489,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -10190,7 +10316,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10215,7 +10341,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10543,7 +10669,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10603,7 +10729,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10727,7 +10853,7 @@
         <v>-676714.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10785,7 +10911,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11093,7 +11219,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11232,7 +11358,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11287,7 +11413,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11419,7 +11545,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11446,7 +11572,7 @@
         <v>2.4896608221132883E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11761,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11990,7 +12116,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>438</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12322,7 +12448,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>439</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13000,7 +13126,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13694,7 +13820,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13746,7 +13872,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14255,7 +14381,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15056,7 +15182,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15066,7 +15192,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15084,10 +15210,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15102,8 +15228,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15118,8 +15244,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15134,8 +15260,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15161,7 +15287,7 @@
         <v>1.06</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16480,7 +16606,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16552,7 +16678,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16629,11 +16755,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16654,8 +16780,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16676,8 +16802,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16687,8 +16813,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16701,8 +16827,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16720,8 +16846,8 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16738,8 +16864,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16756,8 +16882,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16773,7 +16899,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16783,21 +16909,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="351"/>
+      <c r="E18" s="353" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+        <v>310</v>
+      </c>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16811,8 +16937,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16826,8 +16952,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16847,8 +16973,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16858,8 +16984,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16873,8 +16999,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16884,8 +17010,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16905,8 +17031,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16916,8 +17042,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16931,8 +17057,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16942,8 +17068,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16963,8 +17089,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16974,8 +17100,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16989,8 +17115,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17001,8 +17127,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17064,8 +17190,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17075,8 +17201,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17090,8 +17216,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17101,12 +17227,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17122,8 +17248,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17133,8 +17259,8 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17148,8 +17274,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17159,8 +17285,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17175,16 +17301,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17193,10 +17319,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17209,7 +17335,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17221,7 +17347,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17237,20 +17363,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17260,19 +17386,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17282,14 +17408,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17312,7 +17438,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17335,15 +17461,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17394,12 +17520,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17412,7 +17538,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17424,15 +17550,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17480,17 +17606,17 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
@@ -17522,14 +17648,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>2.7012043158780146</v>
       </c>
       <c r="D99" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
@@ -17544,32 +17670,32 @@
     </row>
     <row r="101" spans="2:8" ht="14.65">
       <c r="E101" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F101" s="317"/>
     </row>
     <row r="102" spans="2:8" ht="13.9">
       <c r="E102" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F102" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="13.9">
       <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F103" s="318" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="13.9">
       <c r="E104" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F104" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3273BCD3-9F5F-4D81-A7EC-EA2BE81259EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F5B1A1-79CE-4DA8-8756-E9AB3311A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5569,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8696,7 +8696,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>1098684</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F5B1A1-79CE-4DA8-8756-E9AB3311A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42237F3-93ED-4E7D-BEC3-212E0D1CACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4229,8 +4229,7 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8989.5</v>
+        <v>1.08195318</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4267,13 +4266,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4322,7 +4321,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>1.582657938626912</v>
+        <v>1.2806485026105419</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20890029037251456</v>
+        <v>0.20462519829719406</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4372,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4399,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4425,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4460,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4482,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4552,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4574,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4596,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4646,7 +4645,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.7112926312535084E-2</v>
+        <v>6.6431576806824072E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4654,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.1282051282051287E-2</v>
+        <v>5.0761421319796961E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4673,22 +4672,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4745,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4797,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4816,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4953,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4998,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5147,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5166,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5204,7 +5203,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5239,7 +5238,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5249,7 +5248,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.18161128812016392</v>
+        <v>0.15889212827988333</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5258,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>1.401046650506748</v>
+        <v>1.1217563743306584</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5267,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>1.582657938626912</v>
+        <v>1.2806485026105419</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5293,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48583275388906688</v>
+        <v>0.5839483076206422</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5446,13 +5445,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5488,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5502,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5541,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5568,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13130,48 +13129,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.1282051282051287E-2</v>
+        <v>5.0761421319796961E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5665641025641042E-2</v>
+        <v>6.499898477157362E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11252307692307693</v>
+        <v>0.11138071065989848</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.6758974358974362E-2</v>
+        <v>9.5776649746192904E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4256410256410258E-2</v>
+        <v>8.3401015228426398E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3487179487179485E-2</v>
+        <v>4.3045685279187819E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1312820512820515E-2</v>
+        <v>4.0893401015228432E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1538461538461546E-2</v>
+        <v>8.0710659898477158E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7179487179487178E-3</v>
+        <v>2.6903553299492387E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7179487179487184E-2</v>
+        <v>2.6903553299492389E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3487179487179485E-2</v>
+        <v>4.3045685279187819E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14329,50 +14328,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7112926312535084E-2</v>
+        <v>6.6431576806824072E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.4581270238499447E-2</v>
+        <v>7.3824099982271019E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13074970376780423</v>
+        <v>0.129422295607725</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15842872597585167</v>
+        <v>0.15682031251416789</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.9115235209038088E-2</v>
+        <v>9.810898916630674E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.1387861393848377E-2</v>
+        <v>5.0866157217261086E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9828620056732864E-2</v>
+        <v>3.9424268584075675E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.1491203448467657</v>
+        <v>0.14760643271634169</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.6347216196673903E-2</v>
+        <v>4.5876686083002091E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.8872844985816795E-2</v>
+        <v>-4.8376673970732358E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.1039868735747261E-2</v>
+        <v>7.0318651794267592E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14386,43 +14385,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12805261694198788</v>
+        <v>0.1267525903740489</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.26409677957617222</v>
+        <v>0.26141559399671865</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20009255242227042</v>
+        <v>0.19806115595097834</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18259469380944435</v>
+        <v>0.18074094057280024</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6674119806440852E-2</v>
+        <v>8.5794179503837387E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3985538684020242E-2</v>
+        <v>8.313289362123831E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1700083430669114</v>
+        <v>0.16828237004085139</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1959730797040992E-2</v>
+        <v>1.1838312210269002E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.6327381945603204E-2</v>
+        <v>-2.6060098880165607E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3780632960676347E-2</v>
+        <v>9.2828545316405525E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16691,7 +16690,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-1.95</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16931,7 +16930,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17470,7 +17469,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17479,7 +17478,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.18161128812016392</v>
+        <v>0.15889212827988333</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17491,7 +17490,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.401046650506748</v>
+        <v>1.1217563743306584</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17501,7 +17500,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.582657938626912</v>
+        <v>1.2806485026105419</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17512,7 +17511,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48583275388906688</v>
+        <v>0.5839483076206422</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17529,7 +17528,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17542,7 +17541,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20890029037251456</v>
+        <v>0.20462519829719406</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42237F3-93ED-4E7D-BEC3-212E0D1CACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D367985E-BD22-4E4A-A788-430D7641934A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4229,7 +4229,8 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <v>1.08195318</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>9081.7000000000007</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4266,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4372,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4399,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4425,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4460,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4482,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4552,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4574,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4596,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4672,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4745,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4797,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4816,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4953,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4998,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5147,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5166,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5445,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5488,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5502,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5541,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5568,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D367985E-BD22-4E4A-A788-430D7641934A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD974B5-5B60-4346-B2B0-42CD7241C5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9081.7000000000007</v>
+        <v>8989.5</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.06</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>1.2806485026105419</v>
+        <v>1.3048682598278565</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20462519829719406</v>
+        <v>0.21694243716728789</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6431576806824072E-2</v>
+        <v>6.8561956439422506E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0761421319796961E-2</v>
+        <v>5.1282051282051287E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6358775788680426</v>
+        <v>1.6711976882109234</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.48726061605206072</v>
+        <v>0.49778102323885459</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8085079133153084</v>
+        <v>1.8475552711805359</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.20898863340564E-2</v>
+        <v>1.2350918157450758E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.7907626778741865</v>
+        <v>1.8294268997002676</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>3.24 HKD</v>
+        <v>3.31 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.13 HKD</v>
+        <v>3.2 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.07 HKD</v>
+        <v>3.14 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.02 HKD</v>
+        <v>3.09 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.97 HKD</v>
+        <v>3.03 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>3.0780994911633259</v>
+        <v>3.1445585049676374</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1217563743306584</v>
+        <v>1.1459761315479731</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>1.2806485026105419</v>
+        <v>1.3048682598278565</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5839483076206422</v>
+        <v>0.58503928046926712</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>1.7813075759047026</v>
+        <v>1.8197676533377531</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>1.9919557240528507</v>
+        <v>2.0304158014859013</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35286181302085917</v>
+        <v>0.35430814905229513</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>2.4434946171532266</v>
+        <v>2.4962519250174937</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7012043158780146</v>
+        <v>2.7539616237422817</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12244411734166172</v>
+        <v>0.12421358375374725</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6231,43 +6231,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.12804800000000002</v>
+        <v>0.13081267470399999</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.21942</v>
+        <v>0.22415748065999996</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.18868000000000001</v>
+        <v>0.19275377563999999</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.1643</v>
+        <v>0.16784738889999998</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.0560000000000007E-2</v>
+        <v>8.2299364879999989E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.159</v>
+        <v>0.16243295699999999</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.3E-3</v>
+        <v>5.4144318999999998E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.3000000000000005E-2</v>
+        <v>5.4144318999999996E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7486,11 +7486,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
       <c r="E62" s="183">
@@ -7634,43 +7634,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.12804800000000002</v>
+        <v>0.13081267470399999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.21942</v>
+        <v>0.22415748065999996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.18868000000000001</v>
+        <v>0.19275377563999999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.1643</v>
+        <v>0.16784738889999998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.0560000000000007E-2</v>
+        <v>8.2299364879999989E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.159</v>
+        <v>0.16243295699999999</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.3E-3</v>
+        <v>5.4144318999999998E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.3000000000000005E-2</v>
+        <v>5.4144318999999996E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.2327057744034713</v>
+        <v>4.3240938053291229</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7907626778741865</v>
+        <v>1.8294268997002676</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-964204.44</v>
+        <v>-965266.53586545342</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>12.125688821760663</v>
+        <v>12.112346761837474</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
@@ -9398,11 +9398,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2246271.44</v>
+        <v>-2294770.51713112</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.48726061605206072</v>
+        <v>-0.49778102323885459</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9415,11 +9415,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8337221.4803835722</v>
+        <v>8517229.8001422696</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8085079133153086</v>
+        <v>1.8475552711805356</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9432,11 +9432,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>55734.376000000004</v>
+        <v>56937.732705847993</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.20898863340564E-2</v>
+        <v>1.2350918157450758E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9449,11 +9449,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6146684.4163835719</v>
+        <v>6279397.0157169979</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.3333371835973042</v>
+        <v>1.3621251660991318</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12969,43 +12969,43 @@
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.12804800000000002</v>
+        <v>0.13081267470399999</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.21942</v>
+        <v>0.22415748065999996</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.18868000000000001</v>
+        <v>0.19275377563999999</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.1643</v>
+        <v>0.16784738889999998</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.0560000000000007E-2</v>
+        <v>8.2299364879999989E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.159</v>
+        <v>0.16243295699999999</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.3E-3</v>
+        <v>5.4144318999999998E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.3000000000000005E-2</v>
+        <v>5.4144318999999996E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.48E-2</v>
+        <v>8.6630910399999997E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13025,43 +13025,43 @@
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>590301.28000000014</v>
+        <v>603046.43038544001</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1011526.2</v>
+        <v>1033365.9858425999</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>869814.80000000016</v>
+        <v>888594.90570039989</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>757423</v>
+        <v>773776.46282899985</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>390928</v>
+        <v>399368.49694400001</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>371381.60000000003</v>
+        <v>379400.07209679997</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>732990</v>
+        <v>748815.93177000002</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24433</v>
+        <v>24960.531059000001</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>244330.00000000003</v>
+        <v>249605.31058999998</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>390928</v>
+        <v>399368.49694400001</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13080,43 +13080,43 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.9332849824706867</v>
+        <v>0.95343546809060864</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91223504223213125</v>
+        <v>0.93193104018103734</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64738583352709733</v>
+        <v>0.66136349219947266</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.90109048001987424</v>
+        <v>0.9205458565671546</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.89702916225909413</v>
+        <v>0.91639685120111614</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.099500552145968</v>
+        <v>1.1232397855861775</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.57960413999568261</v>
+        <v>0.59211832923862062</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.2161783974252961E-2</v>
+        <v>6.3503914360585667E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.5894941540362002</v>
+        <v>-0.60222187782587089</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.6488808478500826</v>
+        <v>0.66289078526387424</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13130,48 +13130,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0761421319796961E-2</v>
+        <v>5.1282051282051287E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.499898477157362E-2</v>
+        <v>6.70834229251282E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11138071065989848</v>
+        <v>0.11495255418461536</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.5776649746192904E-2</v>
+        <v>9.8848090071794861E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3401015228426398E-2</v>
+        <v>8.6075584051282045E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3045685279187819E-2</v>
+        <v>4.4426107897435896E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.0893401015228432E-2</v>
+        <v>4.2204802502564101E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.0710659898477158E-2</v>
+        <v>8.3298952307692298E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6903553299492387E-3</v>
+        <v>2.7766317435897435E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6903553299492389E-2</v>
+        <v>2.7766317435897435E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3045685279187819E-2</v>
+        <v>4.4426107897435896E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14272,50 +14272,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13087020630944343</v>
+        <v>0.13369581505687389</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14543347696507392</v>
+        <v>0.14857352019011535</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.25496192234721826</v>
+        <v>0.26046678597020778</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.30893601565291073</v>
+        <v>0.315606229850947</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19327470865762428</v>
+        <v>0.19744768830548054</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10020632971800433</v>
+        <v>0.10236987702020389</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.7665809110629078E-2</v>
+        <v>7.9342685733566162E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.2907846724511931</v>
+        <v>0.29706298236807371</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.0377071583514115E-2</v>
+        <v>9.2328396115162692E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.5302047722342742E-2</v>
+        <v>-9.7359707042108445E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.13852774403470716</v>
+        <v>0.14151868610123641</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14329,50 +14329,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6431576806824072E-2</v>
+        <v>6.8561956439422506E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.3824099982271019E-2</v>
+        <v>7.619154881544378E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.129422295607725</v>
+        <v>0.13357271075395272</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15682031251416789</v>
+        <v>0.16184934864151129</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.810898916630674E-2</v>
+        <v>0.10125522477204131</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.0866157217261086E-2</v>
+        <v>5.2497372830873794E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9424268584075675E-2</v>
+        <v>4.0688556786444188E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.14760643271634169</v>
+        <v>0.15233999095798653</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.5876686083002091E-2</v>
+        <v>4.7347895443673176E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.8376673970732358E-2</v>
+        <v>-4.9928054893388946E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.0318651794267592E-2</v>
+        <v>7.2573685180121236E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14386,43 +14386,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1267525903740489</v>
+        <v>0.12805261694198788</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.26141559399671865</v>
+        <v>0.26409677957617222</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19806115595097834</v>
+        <v>0.20009255242227042</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18074094057280024</v>
+        <v>0.18259469380944435</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5794179503837387E-2</v>
+        <v>8.6674119806440852E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.313289362123831E-2</v>
+        <v>8.3985538684020242E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16828237004085139</v>
+        <v>0.1700083430669114</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1838312210269002E-2</v>
+        <v>1.1959730797040992E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.6060098880165607E-2</v>
+        <v>-2.6327381945603204E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2828545316405525E-2</v>
+        <v>9.3780632960676347E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.0748273144719884</v>
+        <v>3.1412156789563142</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16287,23 +16287,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16314,23 +16314,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.9954124025546811</v>
+        <v>3.0600861256693785</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0219967365400393</v>
+        <v>3.0872444400034498</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0489762367715612</v>
+        <v>3.1148064525882813</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0489762367715612</v>
+        <v>3.1148064525882813</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16341,23 +16341,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0207718880041314</v>
+        <v>3.0859931458552441</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0748273144719884</v>
+        <v>3.1412156789563142</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.131527041127085</v>
+        <v>3.1991396051303962</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.131527041127085</v>
+        <v>3.1991396051303962</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16368,23 +16368,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0513809961825542</v>
+        <v>3.1172631329782261</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1402198032093755</v>
+        <v>3.2080200519827478</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2363639196313208</v>
+        <v>3.3062400087661996</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2363639196313208</v>
+        <v>3.3062400087661996</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16395,23 +16395,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0817621988834265</v>
+        <v>3.1483002939336915</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2068442623999878</v>
+        <v>3.2760829948434833</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.3461014384251904</v>
+        <v>3.4183468620462709</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.3461014384251904</v>
+        <v>3.4183468620462709</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16422,23 +16422,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.109269645562903</v>
+        <v>3.1764016518183915</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.2688087064391378</v>
+        <v>3.3393853085173206</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.4510738566972656</v>
+        <v>3.5255857318788117</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.4510738566972656</v>
+        <v>3.5255857318788117</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16448,23 +16448,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1328766143069529</v>
+        <v>3.2005183168429361</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3234699658426679</v>
+        <v>3.3952267550472546</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.5464121589049959</v>
+        <v>3.6229824761741654</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.5464121589049959</v>
+        <v>3.6229824761741654</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.2363639196313208</v>
+        <v>3.3062400087661996</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.131527041127085</v>
+        <v>3.1991396051303962</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.0748273144719884</v>
+        <v>3.1412156789563142</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0207718880041314</v>
+        <v>3.0859931458552441</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-1.97</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>3.178099491163326</v>
+        <v>3.2445585049676375</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.9692147624653469</v>
+        <v>3.0333228543100557</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.0748273144719884</v>
+        <v>3.1412156789563142</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.0207718880041314</v>
+        <v>3.0859931458552441</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.131527041127085</v>
+        <v>3.1991396051303962</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.0753561745094364</v>
+        <v>3.1417559575709166</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.9692147624653464</v>
+        <v>3.0333228543100552</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.2363639196313208</v>
+        <v>3.3062400087661996</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.0780994911633259</v>
+        <v>3.1445585049676374</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.0748273144719884</v>
+        <v>3.1412156789563142</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239917</v>
+        <v>0.43316896917239905</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1217563743306584</v>
+        <v>1.1459761315479731</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.2806485026105419</v>
+        <v>1.3048682598278565</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5839483076206422</v>
+        <v>0.58503928046926712</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20462519829719406</v>
+        <v>0.21694243716728789</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.7813075759047026</v>
+        <v>1.8197676533377531</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.9919557240528507</v>
+        <v>2.0304158014859013</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35286181302085917</v>
+        <v>0.35430814905229513</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4434946171532266</v>
+        <v>2.4962519250174937</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7012043158780146</v>
+        <v>2.7539616237422817</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12244411734166172</v>
+        <v>0.12421358375374725</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD974B5-5B60-4346-B2B0-42CD7241C5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C071115-99C9-4DAC-A2DB-20459A986109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>1.3048682598278565</v>
+        <v>1.3047948694461962</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21694243716728789</v>
+        <v>0.21691823243350972</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8561956439422506E-2</v>
+        <v>6.8557565607875542E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6711976882109234</v>
+        <v>1.6710906616919665</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49778102323885459</v>
+        <v>0.49774914444288937</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8475552711805359</v>
+        <v>1.847436950403377</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2350918157450758E-2</v>
+        <v>1.235012718234013E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.8294268997002676</v>
+        <v>1.8293097398967673</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>3.1445585049676374</v>
+        <v>3.1443571217603616</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1459761315479731</v>
+        <v>1.1459027411663127</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>1.3048682598278565</v>
+        <v>1.3047948694461962</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58503928046926712</v>
+        <v>0.58503604427867617</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>1.8197676533377531</v>
+        <v>1.8196511121298389</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>2.0304158014859013</v>
+        <v>2.030299260277987</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35430814905229513</v>
+        <v>0.35430385873557257</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>2.4962519250174937</v>
+        <v>2.4960920605347581</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7539616237422817</v>
+        <v>2.7538017592595461</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12421358375374725</v>
+        <v>0.12420833492417171</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5542,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5569,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6231,43 +6231,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13081267470399999</v>
+        <v>0.130804297224</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22415748065999996</v>
+        <v>0.22414312520999999</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19275377563999999</v>
+        <v>0.19274143133999999</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16784738889999998</v>
+        <v>0.16783663964999998</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2299364879999989E-2</v>
+        <v>8.2294094279999994E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16243295699999999</v>
+        <v>0.16242255449999998</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4144318999999998E-3</v>
+        <v>5.4140851500000002E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4144318999999996E-2</v>
+        <v>5.4140851500000003E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7634,43 +7634,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13081267470399999</v>
+        <v>0.130804297224</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22415748065999996</v>
+        <v>0.22414312520999999</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19275377563999999</v>
+        <v>0.19274143133999999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16784738889999998</v>
+        <v>0.16783663964999998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2299364879999989E-2</v>
+        <v>8.2294094279999994E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16243295699999999</v>
+        <v>0.16242255449999998</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4144318999999998E-3</v>
+        <v>5.4140851500000002E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4144318999999996E-2</v>
+        <v>5.4140851500000003E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3240938053291229</v>
+        <v>4.3238168825503926</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8294268997002676</v>
+        <v>1.8293097398967673</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965266.53586545342</v>
+        <v>-965263.31751688663</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>12.112346761837474</v>
+        <v>12.112387146417653</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
@@ -9398,11 +9398,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2294770.51713112</v>
+        <v>-2294623.55588172</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49778102323885459</v>
+        <v>-0.49774914444288937</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9415,11 +9415,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8517229.8001422696</v>
+        <v>8516684.3413595688</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8475552711805356</v>
+        <v>1.8474369504033772</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9432,11 +9432,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>56937.732705847993</v>
+        <v>56934.086310587998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2350918157450758E-2</v>
+        <v>1.235012718234013E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9449,11 +9449,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6279397.0157169979</v>
+        <v>6278994.8717884365</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.3621251660991318</v>
+        <v>1.3620379331428278</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12969,43 +12969,43 @@
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.13081267470399999</v>
+        <v>0.130804297224</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22415748065999996</v>
+        <v>0.22414312520999999</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19275377563999999</v>
+        <v>0.19274143133999999</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16784738889999998</v>
+        <v>0.16783663964999998</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2299364879999989E-2</v>
+        <v>8.2294094279999994E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16243295699999999</v>
+        <v>0.16242255449999998</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4144318999999998E-3</v>
+        <v>5.4140851500000002E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4144318999999996E-2</v>
+        <v>5.4140851500000003E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6630910399999997E-2</v>
+        <v>8.6625362400000003E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13025,43 +13025,43 @@
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603046.43038544001</v>
+        <v>603007.8102026399</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1033365.9858425999</v>
+        <v>1033299.8072180999</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>888594.90570039989</v>
+        <v>888537.99847739993</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>773776.46282899985</v>
+        <v>773726.90878649987</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399368.49694400001</v>
+        <v>399342.92066400003</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379400.07209679997</v>
+        <v>379375.77463079995</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>748815.93177000002</v>
+        <v>748767.97624499991</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24960.531059000001</v>
+        <v>24958.932541500002</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249605.31058999998</v>
+        <v>249589.32541500003</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399368.49694400001</v>
+        <v>399342.92066400003</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13080,43 +13080,43 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95343546809060864</v>
+        <v>0.95337440836085929</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93193104018103734</v>
+        <v>0.93187135763369899</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66136349219947266</v>
+        <v>0.66132113728668485</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.9205458565671546</v>
+        <v>0.920486903147542</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91639685120111614</v>
+        <v>0.91633816349130237</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.1232397855861775</v>
+        <v>1.1231678512811858</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59211832923862062</v>
+        <v>0.59208040891115954</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3503914360585667E-2</v>
+        <v>6.3499847455190744E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60222187782587089</v>
+        <v>-0.60218331044890638</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66289078526387424</v>
+        <v>0.66284833254047959</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13135,43 +13135,43 @@
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.70834229251282E-2</v>
+        <v>6.7079126781538462E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11495255418461536</v>
+        <v>0.11494519241538462</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8848090071794861E-2</v>
+        <v>9.8841759661538464E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6075584051282045E-2</v>
+        <v>8.6070071615384602E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4426107897435896E-2</v>
+        <v>4.4423262769230774E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2204802502564101E-2</v>
+        <v>4.2202099630769228E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3298952307692298E-2</v>
+        <v>8.3293617692307684E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7766317435897435E-3</v>
+        <v>2.7764539230769234E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7766317435897435E-2</v>
+        <v>2.7764539230769235E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4426107897435896E-2</v>
+        <v>4.4423262769230774E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14272,50 +14272,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13369581505687389</v>
+        <v>0.13368725293535733</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14857352019011535</v>
+        <v>0.14856400527348559</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.26046678597020778</v>
+        <v>0.26045010520670325</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.315606229850947</v>
+        <v>0.31558601785784746</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19744768830548054</v>
+        <v>0.19743504339883394</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10236987702020389</v>
+        <v>0.10236332106834924</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9342685733566162E-2</v>
+        <v>7.9337604484639918E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29706298236807371</v>
+        <v>0.29704395791804122</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2328396115162692E-2</v>
+        <v>9.2322483237885028E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.7359707042108445E-2</v>
+        <v>-9.735347195059002E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14151868610123641</v>
+        <v>0.14150962298892622</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14329,50 +14329,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8561956439422506E-2</v>
+        <v>6.8557565607875542E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.619154881544378E-2</v>
+        <v>7.6186669371018256E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13357271075395272</v>
+        <v>0.13356415651625808</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16184934864151129</v>
+        <v>0.16183898351684486</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10125522477204131</v>
+        <v>0.10124874020453023</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2497372830873794E-2</v>
+        <v>5.2494010804281663E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0688556786444188E-2</v>
+        <v>4.0685951017764059E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15233999095798653</v>
+        <v>0.15233023482976474</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.7347895443673176E-2</v>
+        <v>4.7344863198915399E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9928054893388946E-2</v>
+        <v>-4.9924857410558986E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2573685180121236E-2</v>
+        <v>7.2569037430218572E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1412156789563142</v>
+        <v>3.1410145098296547</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16287,23 +16287,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16314,23 +16314,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0600861256693785</v>
+        <v>3.0598901522258717</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0872444400034498</v>
+        <v>3.087046727292432</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1148064525882813</v>
+        <v>3.1146069747561871</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1148064525882813</v>
+        <v>3.1146069747561871</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16341,23 +16341,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0859931458552441</v>
+        <v>3.085795513279364</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1412156789563142</v>
+        <v>3.1410145098296551</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1991396051303962</v>
+        <v>3.1989347264508661</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1991396051303962</v>
+        <v>3.1989347264508661</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16368,23 +16368,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1172631329782261</v>
+        <v>3.1170634978158818</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2080200519827478</v>
+        <v>3.2078146045833584</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3062400087661996</v>
+        <v>3.3060282711833446</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3062400087661996</v>
+        <v>3.3060282711833446</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16395,23 +16395,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1483002939336915</v>
+        <v>3.1480986710954912</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2760829948434833</v>
+        <v>3.2758731885702783</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4183468620462709</v>
+        <v>3.4181279449380115</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4183468620462709</v>
+        <v>3.4181279449380115</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16422,23 +16422,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1764016518183915</v>
+        <v>3.1761982293184672</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3393853085173206</v>
+        <v>3.3391714482495929</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5255857318788117</v>
+        <v>3.5253599469996022</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5255857318788117</v>
+        <v>3.5253599469996022</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16448,23 +16448,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2005183168429361</v>
+        <v>3.200313349868217</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3952267550472546</v>
+        <v>3.3950093185924137</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6229824761741654</v>
+        <v>3.6227504538315052</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6229824761741654</v>
+        <v>3.6227504538315052</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3062400087661996</v>
+        <v>3.3060282711833446</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.1991396051303962</v>
+        <v>3.1989347264508661</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1412156789563142</v>
+        <v>3.1410145098296551</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0859931458552441</v>
+        <v>3.085795513279364</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>3.2445585049676375</v>
+        <v>3.2443571217603617</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.0333228543100557</v>
+        <v>3.0331285948347944</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.1412156789563142</v>
+        <v>3.1410145098296551</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.0859931458552441</v>
+        <v>3.085795513279364</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.1991396051303962</v>
+        <v>3.1989347264508661</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1417559575709166</v>
+        <v>3.1415547538438391</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.0333228543100552</v>
+        <v>3.0331285948347939</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.3062400087661996</v>
+        <v>3.3060282711833446</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1445585049676374</v>
+        <v>3.1443571217603616</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.1412156789563142</v>
+        <v>3.1410145098296547</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239905</v>
+        <v>0.43316896917239917</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1459761315479731</v>
+        <v>1.1459027411663127</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3048682598278565</v>
+        <v>1.3047948694461962</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.58503928046926712</v>
+        <v>0.58503604427867617</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21694243716728789</v>
+        <v>0.21691823243350972</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8197676533377531</v>
+        <v>1.8196511121298389</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>2.0304158014859013</v>
+        <v>2.030299260277987</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35430814905229513</v>
+        <v>0.35430385873557257</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4962519250174937</v>
+        <v>2.4960920605347581</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7539616237422817</v>
+        <v>2.7538017592595461</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12421358375374725</v>
+        <v>0.12420833492417171</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C071115-99C9-4DAC-A2DB-20459A986109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A679EE63-4CA5-4954-9AB9-7FF31299D78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2377,6 +2377,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4097,7 +4109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4119,7 +4131,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4162,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4197,10 +4209,10 @@
         <v>427</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4257,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4313,7 +4325,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>1.3047948694461962</v>
+        <v>1.3066492491416455</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,10 +4365,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21691823243350972</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.21752951885117988</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4646,7 +4662,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8557565607875542E-2</v>
+        <v>6.8668510239619146E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4712,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4724,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4777,7 +4793,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6710906616919665</v>
+        <v>1.6737949370907166</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4860,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49774914444288937</v>
+        <v>0.49855463680600437</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4915,7 +4931,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.847436950403377</v>
+        <v>1.8504266016594371</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4962,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.235012718234013E-2</v>
+        <v>1.2370113019061173E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4984,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4997,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.8293097398967673</v>
+        <v>1.8322700564371563</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5083,7 +5099,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.14 HKD</v>
+        <v>3.15 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5127,7 +5143,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>3.03 HKD</v>
+        <v>3.04 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5156,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>3.1443571217603616</v>
+        <v>3.1494455396446743</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5275,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1459027411663127</v>
+        <v>1.1477571208617621</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5284,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>1.3047948694461962</v>
+        <v>1.3066492491416455</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5310,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58503604427867617</v>
+        <v>0.58511768732185665</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5311,7 +5327,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5321,30 +5337,30 @@
         <v>0.21064814814814814</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>1.8196511121298389</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>1.8225957984054828</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>2.030299260277987</v>
+        <v>2.0332439465536307</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>426</v>
       </c>
@@ -5357,21 +5373,21 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35430385873557257</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.35441209541187224</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5380,7 +5396,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5390,30 +5406,30 @@
         <v>0.25770969872478805</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>2.4960920605347581</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>2.5001314107071093</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7538017592595461</v>
+        <v>2.7578411094318973</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>426</v>
       </c>
@@ -5426,127 +5442,196 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12420833492417171</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>0.1243407530891798</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>0.24126031259386493</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>2.257397822774434</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>2.4986581353682991</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.20579126339785159</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6231,43 +6316,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.130804297224</v>
+        <v>0.13101597385600003</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22414312520999999</v>
+        <v>0.22450584924000003</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19274143133999999</v>
+        <v>0.19305333896000001</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16783663964999998</v>
+        <v>0.16810824460000001</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2294094279999994E-2</v>
+        <v>8.2427268320000011E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16242255449999998</v>
+        <v>0.16268539800000001</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4140851500000002E-3</v>
+        <v>5.4228466000000013E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4140851500000003E-2</v>
+        <v>5.422846600000001E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -6276,7 +6361,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7634,43 +7719,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.130804297224</v>
+        <v>0.13101597385600003</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22414312520999999</v>
+        <v>0.22450584924000003</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19274143133999999</v>
+        <v>0.19305333896000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16783663964999998</v>
+        <v>0.16810824460000001</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2294094279999994E-2</v>
+        <v>8.2427268320000011E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16242255449999998</v>
+        <v>0.16268539800000001</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4140851500000002E-3</v>
+        <v>5.4228466000000013E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4140851500000003E-2</v>
+        <v>5.422846600000001E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8988,11 +9073,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3238168825503926</v>
+        <v>4.3308139844385343</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8293097398967673</v>
+        <v>1.8322700564371563</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9250,7 +9335,7 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965263.31751688663</v>
+        <v>-965344.6366230133</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9266,7 +9351,7 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>12.112387146417653</v>
+        <v>12.111366818072273</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
@@ -9398,11 +9483,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2294623.55588172</v>
+        <v>-2298336.8756756806</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49774914444288937</v>
+        <v>-0.49855463680600448</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9415,11 +9500,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8516684.3413595688</v>
+        <v>8530466.6336500049</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8474369504033772</v>
+        <v>1.8504266016594371</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9432,11 +9517,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>56934.086310587998</v>
+        <v>57026.221017872005</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.235012718234013E-2</v>
+        <v>1.2370113019061173E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9449,11 +9534,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6278994.8717884365</v>
+        <v>6289155.9789921967</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>1.3620379331428278</v>
+        <v>1.3642420778724937</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12116,7 +12201,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12448,7 +12533,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12969,43 +13054,43 @@
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.130804297224</v>
+        <v>0.13101597385600003</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22414312520999999</v>
+        <v>0.22450584924000003</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19274143133999999</v>
+        <v>0.19305333896000001</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16783663964999998</v>
+        <v>0.16810824460000001</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2294094279999994E-2</v>
+        <v>8.2427268320000011E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16242255449999998</v>
+        <v>0.16268539800000001</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4140851500000002E-3</v>
+        <v>5.4228466000000013E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4140851500000003E-2</v>
+        <v>5.422846600000001E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6625362400000003E-2</v>
+        <v>8.6765545600000021E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13025,43 +13110,43 @@
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603007.8102026399</v>
+        <v>603983.63947616017</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1033299.8072180999</v>
+        <v>1034971.9649964002</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>888537.99847739993</v>
+        <v>889975.89260560006</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>773726.90878649987</v>
+        <v>774979.00760600006</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399342.92066400003</v>
+        <v>399989.16521600005</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379375.77463079995</v>
+        <v>379989.70695520006</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>748767.97624499991</v>
+        <v>749979.68478000013</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24958.932541500002</v>
+        <v>24999.322826000003</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249589.32541500003</v>
+        <v>249993.22826000006</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399342.92066400003</v>
+        <v>399989.16521600005</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13080,43 +13165,43 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95337440836085929</v>
+        <v>0.9549172252872119</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93187135763369899</v>
+        <v>0.93337937682440941</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66132113728668485</v>
+        <v>0.66239133325105393</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.920486903147542</v>
+        <v>0.92197649922040448</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91633816349130237</v>
+        <v>0.91782104578444879</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.1231678512811858</v>
+        <v>1.1249854397929973</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59208040891115954</v>
+        <v>0.59303855470217193</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3499847455190744E-2</v>
+        <v>6.3602607334851374E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60218331044890638</v>
+        <v>-0.60315780545944997</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66284833254047959</v>
+        <v>0.66392099991866771</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13135,43 +13220,43 @@
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7079126781538462E-2</v>
+        <v>6.7187678900512832E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11494519241538462</v>
+        <v>0.11513120473846156</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8841759661538464E-2</v>
+        <v>9.9001712287179494E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6070071615384602E-2</v>
+        <v>8.6209356205128207E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4423262769230774E-2</v>
+        <v>4.4495151589743605E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2202099630769228E-2</v>
+        <v>4.2270394010256417E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3293617692307684E-2</v>
+        <v>8.3428409230769232E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7764539230769234E-3</v>
+        <v>2.7809469743589753E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7764539230769235E-2</v>
+        <v>2.7809469743589749E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4423262769230774E-2</v>
+        <v>4.4495151589743605E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14272,50 +14357,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13368725293535733</v>
+        <v>0.13390359496725734</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14856400527348559</v>
+        <v>0.14880442190306217</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.26045010520670325</v>
+        <v>0.26087158372265595</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31558601785784746</v>
+        <v>0.31609672115111964</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19743504339883394</v>
+        <v>0.19775454654905442</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10236332106834924</v>
+        <v>0.10252897253014318</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9337604484639918E-2</v>
+        <v>7.946599412675924E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29704395791804122</v>
+        <v>0.29752465515737098</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2322483237885028E-2</v>
+        <v>9.2471885915965307E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.735347195059002E-2</v>
+        <v>-9.7511016125310213E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14150962298892622</v>
+        <v>0.14173862372533624</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14329,50 +14414,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8557565607875542E-2</v>
+        <v>6.8668510239619146E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6186669371018256E-2</v>
+        <v>7.6309959950288289E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13356415651625808</v>
+        <v>0.13378029934495178</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16183898351684486</v>
+        <v>0.16210088264159983</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10124874020453023</v>
+        <v>0.10141258797387406</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2494010804281663E-2</v>
+        <v>5.25789602718683E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0685951017764059E-2</v>
+        <v>4.0751791859876534E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15233023482976474</v>
+        <v>0.15257674623454923</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.7344863198915399E-2</v>
+        <v>4.7421479956905287E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9924857410558986E-2</v>
+        <v>-5.0005649295030881E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2569037430218572E-2</v>
+        <v>7.2686473705300639E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15284,7 +15369,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15298,7 +15383,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15351,7 +15436,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1410145098296547</v>
+        <v>3.1460975184663309</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16287,23 +16372,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16314,23 +16399,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0598901522258717</v>
+        <v>3.0648418797719783</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.087046727292432</v>
+        <v>3.0920424015013679</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1146069747561871</v>
+        <v>3.1196472488787652</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1146069747561871</v>
+        <v>3.1196472488787652</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16341,23 +16426,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.085795513279364</v>
+        <v>3.0907891626865633</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1410145098296551</v>
+        <v>3.1460975184663313</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1989347264508661</v>
+        <v>3.2041114656196368</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1989347264508661</v>
+        <v>3.2041114656196368</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16368,23 +16453,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1170634978158818</v>
+        <v>3.1221077472553169</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2078146045833584</v>
+        <v>3.2130057137899306</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3060282711833446</v>
+        <v>3.3113783165915818</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3060282711833446</v>
+        <v>3.3113783165915818</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16395,23 +16480,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1480986710954912</v>
+        <v>3.1531931438157574</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2758731885702783</v>
+        <v>3.2811744349217515</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4181279449380115</v>
+        <v>3.423659397852671</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4181279449380115</v>
+        <v>3.423659397852671</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16422,23 +16507,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1761982293184672</v>
+        <v>3.181338174702641</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3391714482495929</v>
+        <v>3.3445751282573353</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5253599469996022</v>
+        <v>3.5310649302150297</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5253599469996022</v>
+        <v>3.5310649302150297</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16448,23 +16533,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.200313349868217</v>
+        <v>3.2054923200215044</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3950093185924137</v>
+        <v>3.400503359334345</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6227504538315052</v>
+        <v>3.6286130411540793</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6227504538315052</v>
+        <v>3.6286130411540793</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16499,7 +16584,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3060282711833446</v>
+        <v>3.3113783165915818</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16521,7 +16606,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.1989347264508661</v>
+        <v>3.2041114656196368</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16544,7 +16629,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1410145098296551</v>
+        <v>3.1460975184663313</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16567,7 +16652,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.085795513279364</v>
+        <v>3.0907891626865633</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16590,7 +16675,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16658,7 +16743,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16740,7 +16825,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>3.2443571217603617</v>
+        <v>3.2494455396446744</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16946,7 +17031,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.0331285948347944</v>
+        <v>3.0380370149632103</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16993,7 +17078,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.1410145098296551</v>
+        <v>3.1460975184663313</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17051,7 +17136,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.085795513279364</v>
+        <v>3.0907891626865633</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17194,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.1989347264508661</v>
+        <v>3.2041114656196368</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17221,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1415547538438391</v>
+        <v>3.1466386367410388</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17210,7 +17295,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.0331285948347939</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17268,7 +17353,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.3060282711833446</v>
+        <v>3.3113783165915818</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17379,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1443571217603616</v>
+        <v>3.1494455396446743</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17356,7 +17441,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.1410145098296547</v>
+        <v>3.1460975184663309</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17419,7 +17504,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239917</v>
+        <v>0.43316896917239911</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17491,7 +17576,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1459027411663127</v>
+        <v>1.1477571208617621</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17501,7 +17586,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3047948694461962</v>
+        <v>1.3066492491416455</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17512,7 +17597,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.58503604427867617</v>
+        <v>0.58511768732185665</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17542,7 +17627,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21691823243350972</v>
+        <v>0.21752951885117988</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17580,7 +17665,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8196511121298389</v>
+        <v>1.8225957984054828</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17590,7 +17675,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>2.030299260277987</v>
+        <v>2.0332439465536307</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17601,7 +17686,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35430385873557257</v>
+        <v>0.35441209541187224</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17640,7 +17725,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4960920605347581</v>
+        <v>2.5001314107071093</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17652,7 +17737,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7538017592595461</v>
+        <v>2.7578411094318973</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17662,39 +17747,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12420833492417171</v>
+        <v>0.1243407530891798</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>0.24126031259386493</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>2.257397822774434</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>2.4986581353682991</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.20579126339785159</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A679EE63-4CA5-4954-9AB9-7FF31299D78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3766DD2-A479-474C-A648-74CF36828318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2382,13 +2359,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3089,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3603,14 +3628,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3668,9 +3687,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3678,7 +3694,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3770,9 +3785,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3787,9 +3799,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3797,6 +3806,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4109,10 +4145,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4127,11 +4163,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>435</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4159,10 +4195,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>436</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,9 +4212,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4199,20 +4235,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4228,17 +4264,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4252,14 +4288,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4269,34 +4305,34 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4304,286 +4340,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>1.3066492491416455</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>3.1494455396446734</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21752951885117988</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>0.21752951885117966</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>3983.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>1.3066492491416453</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>2.0332439465536307</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>2.7578411094318964</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>2.4986581353682982</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>928439.85014218651</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>57395.095749289067</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>57395.095749289067</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-52759</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>4636.0957492890666</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-130645.02443131036</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-233268.98647286888</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4591,1080 +4679,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-130645.02443131036</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>632498.42340470827</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-233268.98647286888</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>569161.93498729635</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>632498.42340470827</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>569161.93498729635</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8668510239619146E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+        <v>6.8668510239619132E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.1282051282051287E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6737949370907166</v>
-      </c>
-      <c r="D82" s="1" t="str">
+        <v>1.6737949370907161</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>2119124</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49855463680600437</v>
-      </c>
-      <c r="D92" s="1" t="str">
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.49855463680600426</v>
+      </c>
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.23422582328431374</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.10863424600069688</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>2.2824569622635926</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>11691643</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>7865303.2833807282</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8504266016594371</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>52579.6</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2370113019061173E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>7865303.2833807282</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8504266016594366</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>3.0380370149632103</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>52579.6</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>1.8322700564371563</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2370113019061171E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>3.0380370149632099</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>1.8322700564371559</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.03</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>3.31 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.03</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>3.2 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>3.15 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.01</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>3.09 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>3.04 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>3.1494455396446743</v>
-      </c>
-      <c r="D122" s="236" t="str">
+        <v>3.1494455396446734</v>
+      </c>
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0.1</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>3983.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>0.15889212827988333</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1477571208617621</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+        <v>1.1477571208617618</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>1.3066492491416455</v>
-      </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+        <v>1.3066492491416453</v>
+      </c>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.58511768732185665</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>0.21064814814814814</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>1.8225957984054828</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+        <v>1.8225957984054824</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>2.0332439465536307</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35441209541187224</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+        <v>0.35441209541187202</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>0.25770969872478805</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>2.5001314107071093</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+        <v>2.5001314107071084</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7578411094318973</v>
-      </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+        <v>2.7578411094318964</v>
+      </c>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.1243407530891798</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>0.24126031259386493</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>2.257397822774434</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+        <v>2.2573978227744331</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>2.4986581353682991</v>
-      </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>2.4986581353682982</v>
+      </c>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20579126339785159</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+        <v>0.2057912633978517</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5678,17 +5795,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6203,7 +6320,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>1522553</v>
@@ -6239,7 +6356,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-379005</v>
@@ -6275,7 +6392,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-1061021</v>
@@ -6316,43 +6433,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13101597385600003</v>
+        <v>0.131015973856</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22450584924000003</v>
+        <v>0.22450584923999997</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19305333896000001</v>
+        <v>0.19305333895999999</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16810824460000001</v>
+        <v>0.16810824459999998</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2427268320000011E-2</v>
+        <v>8.2427268319999997E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16268539800000001</v>
+        <v>0.16268539799999998</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4228466000000013E-3</v>
+        <v>5.4228465999999996E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.422846600000001E-2</v>
+        <v>5.4228466000000003E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -6361,7 +6478,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7666,7 +7783,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7719,43 +7836,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13101597385600003</v>
+        <v>0.131015973856</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22450584924000003</v>
+        <v>0.22450584923999997</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19305333896000001</v>
+        <v>0.19305333895999999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16810824460000001</v>
+        <v>0.16810824459999998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2427268320000011E-2</v>
+        <v>8.2427268319999997E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16268539800000001</v>
+        <v>0.16268539799999998</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4228466000000013E-3</v>
+        <v>5.4228465999999996E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.422846600000001E-2</v>
+        <v>5.4228466000000003E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8114,11 +8231,11 @@
         <f t="shared" si="40"/>
         <v>365962</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8148,11 +8265,11 @@
         <f t="shared" si="40"/>
         <v>1110767</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8284,15 +8401,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8350,7 +8467,7 @@
         <f>23621+80349</f>
         <v>103970</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8361,7 +8478,7 @@
         <f>11000000+679928</f>
         <v>11679928</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8372,7 +8489,7 @@
       <c r="C5" s="19">
         <v>1830485</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8383,7 +8500,7 @@
         <f>11715</f>
         <v>11715</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8394,7 +8511,7 @@
       <c r="C6" s="19">
         <v>1124718</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8404,7 +8521,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8415,7 +8532,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8425,7 +8542,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8436,7 +8553,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8446,7 +8563,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8458,7 +8575,7 @@
         <f>12783+436808</f>
         <v>449591</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8468,7 +8585,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8479,10 +8596,10 @@
       <c r="C10" s="19">
         <v>156022</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8491,10 +8608,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8552,7 +8669,7 @@
       <c r="C15" s="19">
         <v>208252</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8561,7 +8678,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8572,7 +8689,7 @@
       <c r="C16" s="19">
         <v>600</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8581,7 +8698,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8592,7 +8709,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8601,7 +8718,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8612,7 +8729,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8621,7 +8738,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8633,7 +8750,7 @@
         <f>7177198+126839+332968+94332</f>
         <v>7731337</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8643,7 +8760,7 @@
         <f>333906+127404</f>
         <v>461310</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8654,7 +8771,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8663,7 +8780,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8674,7 +8791,7 @@
       <c r="C21" s="19">
         <v>129691</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8683,7 +8800,7 @@
       <c r="G21" s="19">
         <v>64486</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8694,10 +8811,10 @@
       <c r="C22" s="19">
         <v>123890</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8706,10 +8823,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9042,13 +9159,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9064,7 +9181,7 @@
         <f>H29</f>
         <v>7788128.25</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9073,29 +9190,29 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3308139844385343</v>
+        <v>4.3308139844385334</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8322700564371563</v>
-      </c>
-      <c r="F47" s="283"/>
+        <v>1.8322700564371559</v>
+      </c>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9109,7 +9226,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>2.1930131935295925</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9120,22 +9237,22 @@
         <f>G29/G32</f>
         <v>0.764590497713594</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9149,7 +9266,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>8.1486059516858542E-2</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9163,22 +9280,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9200,22 +9317,22 @@
         <f>G39/G32</f>
         <v>0.32112222153227726</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9229,7 +9346,7 @@
         <f>G28/G29</f>
         <v>5.968423878019654E-2</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9248,13 +9365,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9282,7 +9399,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9292,7 +9409,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9302,7 +9419,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9312,26 +9429,26 @@
         <f>SUM(C66:C69)</f>
         <v>11691643</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9342,65 +9459,65 @@
         <v>-956584.92915481783</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>12.111366818072273</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>12.222273886679407</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>3826339.7166192713</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))*2</f>
         <v>4</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9414,7 +9531,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9428,7 +9545,7 @@
         <f>G19*H19</f>
         <v>46131</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9442,7 +9559,7 @@
         <f>G9*H9+G21*H21</f>
         <v>6448.6</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9456,11 +9573,11 @@
         <f>SUM(D79:D81)</f>
         <v>52579.6</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9471,76 +9588,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2298336.8756756806</v>
+        <v>-2298336.8756756801</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49855463680600448</v>
-      </c>
-      <c r="E86" s="269" t="str">
+        <v>-0.49855463680600437</v>
+      </c>
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8530466.6336500049</v>
+        <v>8530466.633650003</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8504266016594371</v>
-      </c>
-      <c r="E87" s="269" t="str">
+        <v>1.8504266016594368</v>
+      </c>
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>57026.221017872005</v>
+        <v>57026.221017871998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2370113019061173E-2</v>
-      </c>
-      <c r="E88" s="269" t="str">
+        <v>1.2370113019061171E-2</v>
+      </c>
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6289155.9789921967</v>
-      </c>
-      <c r="D89" s="271">
+        <v>6289155.9789921949</v>
+      </c>
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>1.3642420778724937</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9559,22 +9676,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9661,7 +9778,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9675,7 +9792,7 @@
         <v>11946459</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9731,7 +9848,7 @@
         <f>C25</f>
         <v>-10341304.899857813</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10333174</v>
@@ -9786,7 +9903,7 @@
         <f>C4+C5</f>
         <v>1605154.1001421865</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>1613285</v>
@@ -9841,7 +9958,7 @@
         <f>C35</f>
         <v>-676714.25</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-646978</v>
@@ -9897,7 +10014,7 @@
         <v>928439.85014218651</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9953,7 +10070,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10008,7 +10125,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -10064,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10120,7 +10237,7 @@
         <f>C50</f>
         <v>4636.0957492890666</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>62139.423404708286</v>
@@ -10175,7 +10292,7 @@
         <f>SUM(C8:C12)</f>
         <v>933075.94589147554</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1028446.4234047083</v>
@@ -10230,7 +10347,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-233268.98647286888</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-316092</v>
@@ -10286,7 +10403,7 @@
         <v>-130645.02443131036</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10343,7 +10460,7 @@
         <v>569161.93498729635</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10400,8 +10517,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10425,8 +10542,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10451,7 +10568,7 @@
         <v>569161.93498729635</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10547,7 +10664,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10571,7 +10688,7 @@
         <v>-10241839</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10628,7 +10745,7 @@
         <v>-99465.899857813085</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10685,7 +10802,7 @@
         <v>-10341304.899857813</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10734,14 +10851,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10753,8 +10870,8 @@
         <v>0.85731169378306993</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10813,8 +10930,8 @@
         <v>8.3259733999683991E-3</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10871,7 +10988,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.86563766718303836</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.86495705547560164</v>
@@ -10919,14 +11036,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10937,8 +11054,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-676714.25</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10995,8 +11112,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11054,7 +11171,7 @@
         <v>-676714.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11103,14 +11220,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11123,7 +11240,7 @@
         <v>5.664559263962652E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11181,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11237,7 +11354,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>5.664559263962652E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>5.4156465945264617E-2</v>
@@ -11285,26 +11402,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11383,7 +11500,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11394,7 +11511,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-52759</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-52759</v>
@@ -11443,111 +11560,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>57395.095749289067</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>114898.42340470829</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>117143.83209497746</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>103032.2190187908</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>121976.64802985649</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>175374.64499999999</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>351080</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>357941</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>314822</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>372708</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11561,7 +11678,7 @@
         <f>C47+C48</f>
         <v>4636.0957492890666</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>62139.423404708286</v>
@@ -11609,14 +11726,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11629,8 +11746,8 @@
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11656,8 +11773,8 @@
         <f>G54</f>
         <v>2.4896608221132883E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11683,7 +11800,7 @@
         <f>-C8/C47</f>
         <v>17.597752992706202</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>18.315491195814932</v>
@@ -11731,14 +11848,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11752,7 +11869,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11807,7 +11924,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11862,7 +11979,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11917,7 +12034,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11968,11 +12085,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12028,7 +12145,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>202593</v>
@@ -12076,14 +12193,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12097,7 +12214,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12122,7 +12239,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12147,7 +12264,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12173,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12201,7 +12318,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12223,7 +12340,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12247,7 +12364,7 @@
         <v>0.86563766718303836</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12304,7 +12421,7 @@
         <v>0.13436233281696161</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12361,7 +12478,7 @@
         <v>5.664559263962652E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12418,7 +12535,7 @@
         <v>7.7716740177335097E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12475,7 +12592,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12532,8 +12649,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>443</v>
+      <c r="E78" s="296" t="s">
+        <v>453</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12591,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12648,7 +12765,7 @@
         <v>3.8807279623937656E-4</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12705,7 +12822,7 @@
         <v>7.8104812973574481E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12762,7 +12879,7 @@
         <v>1.952620324339362E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12815,12 +12932,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.0935878525286059E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12877,7 +12994,7 @@
         <v>4.7642731204894803E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12929,26 +13046,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12958,7 +13075,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12984,7 +13101,7 @@
         <v>4.7642731204894803E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13033,14 +13150,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13051,46 +13168,46 @@
       <c r="C90" s="114">
         <v>0.1</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.13101597385600003</v>
+        <v>0.131015973856</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22450584924000003</v>
+        <v>0.22450584923999997</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19305333896000001</v>
+        <v>0.19305333895999999</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16810824460000001</v>
+        <v>0.16810824459999998</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2427268320000011E-2</v>
+        <v>8.2427268319999997E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16268539800000001</v>
+        <v>0.16268539799999998</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4228466000000013E-3</v>
+        <v>5.4228465999999996E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.422846600000001E-2</v>
+        <v>5.4228466000000003E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6765545600000021E-2</v>
+        <v>8.6765545599999994E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13107,46 +13224,46 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>461000</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603983.63947616017</v>
+        <v>603983.63947616005</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034971.9649964002</v>
+        <v>1034971.9649963998</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889975.89260560006</v>
+        <v>889975.89260559995</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774979.00760600006</v>
+        <v>774979.00760599994</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399989.16521600005</v>
+        <v>399989.16521599994</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379989.70695520006</v>
+        <v>379989.70695519994</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749979.68478000013</v>
+        <v>749979.68478000001</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24999.322826000003</v>
+        <v>24999.322825999996</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249993.22826000006</v>
+        <v>249993.22826000003</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399989.16521600005</v>
+        <v>399989.16521599994</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13162,14 +13279,14 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.80996280963569622</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.9549172252872119</v>
+        <v>0.95491722528721168</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93337937682440941</v>
+        <v>0.93337937682440919</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13177,31 +13294,31 @@
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.92197649922040448</v>
+        <v>0.92197649922040426</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91782104578444879</v>
+        <v>0.91782104578444845</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.1249854397929973</v>
+        <v>1.124985439792997</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59303855470217193</v>
+        <v>0.59303855470217182</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3602607334851374E-2</v>
+        <v>6.3602607334851347E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60315780545944997</v>
+        <v>-0.60315780545944986</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66392099991866771</v>
+        <v>0.66392099991866749</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13211,52 +13328,52 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>5.1282051282051287E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7187678900512832E-2</v>
+        <v>6.7187678900512818E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11513120473846156</v>
+        <v>0.11513120473846153</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.9001712287179494E-2</v>
+        <v>9.900171228717948E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6209356205128207E-2</v>
+        <v>8.6209356205128193E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4495151589743605E-2</v>
+        <v>4.4495151589743591E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2270394010256417E-2</v>
+        <v>4.227039401025641E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3428409230769232E-2</v>
+        <v>8.3428409230769218E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7809469743589753E-3</v>
+        <v>2.7809469743589744E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7809469743589749E-2</v>
+        <v>2.7809469743589745E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4495151589743605E-2</v>
+        <v>4.4495151589743591E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13265,7 +13382,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13274,7 +13391,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13298,7 +13415,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13355,7 +13472,7 @@
         <v>-9.2732567630995688E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13433,7 +13550,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13448,7 +13565,7 @@
         <v>24075995</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13505,7 +13622,7 @@
         <v>103970</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13562,7 +13679,7 @@
         <v>1124718</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13619,7 +13736,7 @@
         <v>4569034</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13676,7 +13793,7 @@
         <v>19506961</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13725,7 +13842,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13734,7 +13851,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13760,7 +13877,7 @@
         <v>8.7029972647124972E-3</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13817,7 +13934,7 @@
         <v>9.4146558406972308E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13874,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13893,63 +14010,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3226606227451485</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.65019430537408307</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.1911040666425015</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.7903285844398347</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6212457823006146</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.5133869677398846</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.3115161389526857</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>15.801640747079396</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-4.710466049773947</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.6060025550358761</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13957,58 +14074,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.4072044192682269</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.3921031576498697</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.5946029642834716</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4961201367772632</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.8985688487688246</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.3827126502118285</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.5849400500854394</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.3222093600132299</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-2.6897368713115899</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.2473106321529053</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14017,7 +14134,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14073,7 +14190,7 @@
         <f>C81</f>
         <v>7.8104812973574481E-2</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>8.6087971624454432E-2</v>
@@ -14127,7 +14244,7 @@
         <f>C4/C101</f>
         <v>0.49619793491400876</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.49619793491400876</v>
@@ -14182,7 +14299,7 @@
         <v>1.2342258232843137</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14239,7 +14356,7 @@
         <v>4.7595309702120517E-2</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14335,7 +14452,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14357,50 +14474,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13390359496725734</v>
+        <v>0.13390359496725732</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14880442190306217</v>
+        <v>0.14880442190306215</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.26087158372265595</v>
+        <v>0.2608715837226559</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31609672115111964</v>
+        <v>0.31609672115111953</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19775454654905442</v>
+        <v>0.19775454654905439</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10252897253014318</v>
+        <v>0.10252897253014316</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.946599412675924E-2</v>
+        <v>7.9465994126759226E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29752465515737098</v>
+        <v>0.29752465515737092</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2471885915965307E-2</v>
+        <v>9.2471885915965293E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.7511016125310213E-2</v>
+        <v>-9.7511016125310185E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14173862372533624</v>
+        <v>0.14173862372533622</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14414,50 +14531,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8668510239619146E-2</v>
+        <v>6.8668510239619132E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6309959950288289E-2</v>
+        <v>7.6309959950288275E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13378029934495178</v>
+        <v>0.13378029934495175</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16210088264159983</v>
+        <v>0.16210088264159978</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10141258797387406</v>
+        <v>0.10141258797387405</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.25789602718683E-2</v>
+        <v>5.2578960271868286E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0751791859876534E-2</v>
+        <v>4.0751791859876527E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15257674623454923</v>
+        <v>0.1525767462345492</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.7421479956905287E-2</v>
+        <v>4.742147995690528E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-5.0005649295030881E-2</v>
+        <v>-5.0005649295030867E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2686473705300639E-2</v>
+        <v>7.2686473705300625E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14466,7 +14583,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15217,13 +15334,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15267,7 +15384,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15277,7 +15394,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15295,10 +15412,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15313,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15329,8 +15446,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15345,8 +15462,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15369,7 +15486,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15383,7 +15500,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15410,7 +15527,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15420,7 +15537,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15430,13 +15547,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1460975184663309</v>
+        <v>3.1460975184663305</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16372,23 +16489,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16399,23 +16516,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0648418797719783</v>
+        <v>3.0648418797719779</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0920424015013679</v>
+        <v>3.0920424015013674</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1196472488787652</v>
+        <v>3.1196472488787648</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1196472488787652</v>
+        <v>3.1196472488787648</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16426,23 +16543,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0907891626865633</v>
+        <v>3.0907891626865629</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1460975184663313</v>
+        <v>3.1460975184663305</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2041114656196368</v>
+        <v>3.2041114656196363</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2041114656196368</v>
+        <v>3.2041114656196363</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16453,23 +16570,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1221077472553169</v>
+        <v>3.1221077472553165</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2130057137899306</v>
+        <v>3.2130057137899297</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3113783165915818</v>
+        <v>3.3113783165915809</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3113783165915818</v>
+        <v>3.3113783165915809</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16480,23 +16597,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1531931438157574</v>
+        <v>3.1531931438157565</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2811744349217515</v>
+        <v>3.2811744349217511</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.423659397852671</v>
+        <v>3.4236593978526701</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.423659397852671</v>
+        <v>3.4236593978526701</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16507,23 +16624,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.181338174702641</v>
+        <v>3.1813381747026401</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3445751282573353</v>
+        <v>3.3445751282573348</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5310649302150297</v>
+        <v>3.5310649302150288</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5310649302150297</v>
+        <v>3.5310649302150288</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16533,23 +16650,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2054923200215044</v>
+        <v>3.2054923200215035</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.400503359334345</v>
+        <v>3.4005033593343446</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6286130411540793</v>
+        <v>3.6286130411540785</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6286130411540793</v>
+        <v>3.6286130411540785</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16584,7 +16701,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3113783165915818</v>
+        <v>3.3113783165915809</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16606,7 +16723,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.2041114656196368</v>
+        <v>3.2041114656196363</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16629,7 +16746,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1460975184663313</v>
+        <v>3.1460975184663305</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16652,7 +16769,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0907891626865633</v>
+        <v>3.0907891626865629</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16675,7 +16792,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16691,7 +16808,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16744,12 +16861,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16762,19 +16879,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-1.95</v>
       </c>
@@ -16791,19 +16908,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -16817,15 +16934,15 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>3.2494455396446744</v>
+        <v>3.2494455396446735</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16840,15 +16957,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16865,12 +16982,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16887,37 +17004,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16931,12 +17048,12 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16949,12 +17066,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16967,8 +17084,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16984,7 +17101,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16994,25 +17111,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17022,23 +17139,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.0380370149632103</v>
+        <v>3.0380370149632099</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17058,8 +17175,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17069,8 +17186,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17078,14 +17195,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.1460975184663313</v>
+        <v>3.1460975184663305</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17095,8 +17212,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17116,8 +17233,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17127,8 +17244,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17136,14 +17253,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.0907891626865633</v>
+        <v>3.0907891626865629</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17153,8 +17270,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17174,8 +17291,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17185,8 +17302,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17194,14 +17311,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.2041114656196368</v>
+        <v>3.2041114656196363</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17212,8 +17329,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17221,7 +17338,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1466386367410388</v>
+        <v>3.1466386367410379</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17275,8 +17392,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17286,8 +17403,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17295,14 +17412,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.0380370149632099</v>
+        <v>3.0380370149632094</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17312,12 +17429,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17333,8 +17450,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17344,8 +17461,8 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17353,14 +17470,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.3113783165915818</v>
+        <v>3.3113783165915809</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17370,8 +17487,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17379,23 +17496,23 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1494455396446743</v>
+        <v>3.1494455396446734</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17404,10 +17521,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17419,8 +17536,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17431,8 +17548,8 @@
         <v>0.02</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17441,29 +17558,29 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.1460975184663309</v>
+        <v>3.1460975184663305</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17471,40 +17588,40 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239911</v>
+        <v>0.43316896917239922</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17522,10 +17639,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17546,15 +17663,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17576,7 +17693,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1477571208617621</v>
+        <v>1.1477571208617618</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17586,7 +17703,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3066492491416455</v>
+        <v>1.3066492491416453</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17595,7 +17712,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.58511768732185665</v>
       </c>
@@ -17605,14 +17722,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>1.95</v>
       </c>
@@ -17623,11 +17740,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21752951885117988</v>
+        <v>0.21752951885117966</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17635,15 +17752,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17665,7 +17782,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8225957984054828</v>
+        <v>1.8225957984054824</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17684,28 +17801,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.35441209541187224</v>
+        <v>0.35441209541187202</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17717,7 +17834,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17725,27 +17842,27 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.5001314107071093</v>
+        <v>2.5001314107071084</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7578411094318973</v>
+        <v>2.7578411094318964</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.1243407530891798</v>
       </c>
@@ -17755,15 +17872,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17783,60 +17900,60 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>2.257397822774434</v>
+        <v>2.2573978227744331</v>
       </c>
       <c r="D104" s="117"/>
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>2.4986581353682991</v>
+        <v>2.4986581353682982</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.20579126339785159</v>
+        <v>0.2057912633978517</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3766DD2-A479-474C-A648-74CF36828318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BEB5C6-1B88-48AF-A13C-391267AA8BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,29 +3833,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4315,13 +4315,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>3.1494455396446734</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21752951885117966</v>
+        <v>0.21725217049313983</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>1.3066492491416453</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D29" s="339" t="str">
         <f>D144</f>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>2.0332439465536307</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4461,7 +4461,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>2.7578411094318964</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D31" s="148" t="str">
         <f>D160</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>2.4986581353682982</v>
+        <v>2.4970028993594653</v>
       </c>
       <c r="D32" s="148" t="str">
         <f>D168</f>
@@ -4517,22 +4517,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4544,13 +4544,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4570,13 +4570,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4605,13 +4605,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4719,7 +4719,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4741,22 +4741,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8668510239619132E-2</v>
+        <v>6.8618159083223565E-2</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4817,22 +4817,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4876,22 +4876,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6737949370907161</v>
+        <v>1.6725676276535739</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4928,13 +4928,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4947,13 +4947,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49855463680600426</v>
+        <v>0.49818907182721034</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8504266016594366</v>
+        <v>1.8490697771281694</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2370113019061171E-2</v>
+        <v>1.2361042638866811E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5084,13 +5084,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>1.8322700564371559</v>
+        <v>1.8309265451850745</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5129,13 +5129,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.15 HKD</v>
+        <v>3.14 HKD</v>
       </c>
       <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>3.1494455396446734</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5278,13 +5278,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,22 +5297,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1477571208617618</v>
+        <v>1.1469155284332238</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>1.3066492491416453</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D144" s="336" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58511768732185665</v>
+        <v>0.58508066712991391</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>0.21064814814814814</v>
+        <v>0.20504008238649371</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>1.8225957984054824</v>
+        <v>1.7442777766579685</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>2.0332439465536307</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35441209541187202</v>
+        <v>0.38060581781059921</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>2.5001314107071084</v>
+        <v>2.4982981903965071</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7578411094318964</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D160" s="336" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1243407530891798</v>
+        <v>0.12428070944437752</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>2.2573978227744331</v>
+        <v>2.2557425867656002</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>2.4986581353682982</v>
+        <v>2.4970028993594653</v>
       </c>
       <c r="D168" s="336" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.2057912633978517</v>
+        <v>0.20573499246785421</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5645,13 +5645,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5688,13 +5688,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5702,22 +5702,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,17 +5741,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5768,6 +5757,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6433,43 +6433,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.131015973856</v>
+        <v>0.130919906448</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22450584923999997</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19305333895999999</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16810824459999998</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2427268319999997E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16268539799999998</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4228465999999996E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4228466000000003E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7836,43 +7836,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.131015973856</v>
+        <v>0.130919906448</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22450584923999997</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19305333895999999</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16810824459999998</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2427268319999997E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16268539799999998</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4228465999999996E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4228466000000003E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9190,11 +9190,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3308139844385334</v>
+        <v>4.32763841689688</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8322700564371559</v>
+        <v>1.8309265451850745</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965344.6366230133</v>
+        <v>-965307.73072710668</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C74" s="285">
         <f>-$C$66/C73</f>
-        <v>12.111366818072273</v>
+        <v>12.111829862994474</v>
       </c>
       <c r="D74" s="285">
         <f>-$C$66/D73</f>
@@ -9600,11 +9600,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2298336.8756756801</v>
+        <v>-2296651.6211234396</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49855463680600437</v>
+        <v>-0.49818907182721034</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9617,11 +9617,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8530466.633650003</v>
+        <v>8524211.6725608613</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8504266016594368</v>
+        <v>1.8490697771281694</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9634,11 +9634,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>57026.221017871998</v>
+        <v>56984.406565175988</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2370113019061171E-2</v>
+        <v>1.2361042638866809E-2</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6289155.9789921949</v>
+        <v>6284544.458002598</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>1.3642420778724937</v>
+        <v>1.3632417479398258</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -13171,43 +13171,43 @@
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.131015973856</v>
+        <v>0.130919906448</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22450584923999997</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19305333895999999</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16810824459999998</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2427268319999997E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16268539799999998</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4228465999999996E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4228466000000003E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6765545599999994E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13227,43 +13227,43 @@
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603983.63947616005</v>
+        <v>603540.76872528007</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034971.9649963998</v>
+        <v>1034213.0722361997</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889975.89260559995</v>
+        <v>889323.31815479998</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774979.00760599994</v>
+        <v>774410.75457299978</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399989.16521599994</v>
+        <v>399695.87332800002</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379989.70695519994</v>
+        <v>379711.0796616</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749979.68478000001</v>
+        <v>749429.76248999988</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24999.322825999996</v>
+        <v>24980.992083000001</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249993.22826000003</v>
+        <v>249809.92082999999</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399989.16521599994</v>
+        <v>399695.87332800002</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13282,43 +13282,43 @@
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95491722528721168</v>
+        <v>0.95421703263140079</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93337937682440919</v>
+        <v>0.93269497678697</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66239133325105393</v>
+        <v>0.66190563508315692</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.92197649922040426</v>
+        <v>0.92130046033819613</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91782104578444845</v>
+        <v>0.91714805388673326</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.124985439792997</v>
+        <v>1.1241605446900729</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59303855470217182</v>
+        <v>0.59260370943012186</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3602607334851347E-2</v>
+        <v>6.3555970749640631E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60315780545944986</v>
+        <v>-0.60271554025101692</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66392099991866749</v>
+        <v>0.66343418012332667</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13337,43 +13337,43 @@
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7187678900512818E-2</v>
+        <v>6.7138413563076926E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11513120473846153</v>
+        <v>0.11504678483076922</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.900171228717948E-2</v>
+        <v>9.8929119323076908E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6209356205128193E-2</v>
+        <v>8.6146143230769218E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4495151589743591E-2</v>
+        <v>4.4462525538461535E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.227039401025641E-2</v>
+        <v>4.2239399261538461E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3428409230769218E-2</v>
+        <v>8.3367235384615379E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7809469743589744E-3</v>
+        <v>2.7789078461538459E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7809469743589745E-2</v>
+        <v>2.7789078461538462E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4495151589743591E-2</v>
+        <v>4.4462525538461535E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14474,50 +14474,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13390359496725732</v>
+        <v>0.13380541021228592</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14880442190306215</v>
+        <v>0.14869531112297604</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.2608715837226559</v>
+        <v>0.2606802997430655</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31609672115111953</v>
+        <v>0.31586494336262128</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19775454654905439</v>
+        <v>0.19760954311055715</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10252897253014316</v>
+        <v>0.10245379320394359</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9465994126759226E-2</v>
+        <v>7.9407725719822117E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29752465515737092</v>
+        <v>0.29730649532849024</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2471885915965293E-2</v>
+        <v>9.2404080944316694E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.7511016125310185E-2</v>
+        <v>-9.743951621354445E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14173862372533622</v>
+        <v>0.14163469393880693</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14531,50 +14531,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8668510239619132E-2</v>
+        <v>6.8618159083223565E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6309959950288275E-2</v>
+        <v>7.6254005704090286E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13378029934495175</v>
+        <v>0.13368220499644384</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16210088264159978</v>
+        <v>0.16198202223724167</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10141258797387405</v>
+        <v>0.10133822723618316</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2578960271868286E-2</v>
+        <v>5.2540406771253122E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0751791859876527E-2</v>
+        <v>4.0721910625549806E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.1525767462345492</v>
+        <v>0.15246486939922577</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.742147995690528E-2</v>
+        <v>4.7386708176572666E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-5.0005649295030867E-2</v>
+        <v>-4.9968982673612543E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2686473705300625E-2</v>
+        <v>7.2633176378875355E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1460975184663305</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16489,23 +16489,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16516,23 +16516,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0648418797719779</v>
+        <v>3.0625945857462646</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0920424015013674</v>
+        <v>3.0897751627044796</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1196472488787648</v>
+        <v>3.1173597688390902</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1196472488787648</v>
+        <v>3.1173597688390902</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16543,23 +16543,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0907891626865629</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1460975184663305</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2041114656196363</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2041114656196363</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16570,23 +16570,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1221077472553165</v>
+        <v>3.1198184630562369</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2130057137899297</v>
+        <v>3.2106497786949295</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3113783165915809</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3113783165915809</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16597,23 +16597,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1531931438157565</v>
+        <v>3.1508810662626585</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2811744349217511</v>
+        <v>3.2787685151405088</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4236593978526701</v>
+        <v>3.4211490010319889</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4236593978526701</v>
+        <v>3.4211490010319889</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16624,23 +16624,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1813381747026401</v>
+        <v>3.1790054598174224</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3445751282573348</v>
+        <v>3.3421227199442374</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5310649302150288</v>
+        <v>3.5284757783326914</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5310649302150288</v>
+        <v>3.5284757783326914</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16650,23 +16650,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2054923200215035</v>
+        <v>3.2031418941193395</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.4005033593343446</v>
+        <v>3.398009941669216</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6286130411540785</v>
+        <v>3.625952362160219</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6286130411540785</v>
+        <v>3.625952362160219</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3113783165915809</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16723,7 +16723,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.2041114656196363</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1460975184663305</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0907891626865629</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>3.2494455396446735</v>
+        <v>3.2471362100207655</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.0380370149632099</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.1460975184663305</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17253,7 +17253,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.0907891626865629</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.2041114656196363</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1466386367410379</v>
+        <v>3.1443313652775093</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.0380370149632094</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.3113783165915809</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1494455396446734</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.1460975184663305</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239922</v>
+        <v>0.43316896917239905</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1477571208617618</v>
+        <v>1.1469155284332238</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3066492491416453</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.58511768732185665</v>
+        <v>0.58508066712991391</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21752951885117966</v>
+        <v>0.21725217049313983</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.21064814814814814</v>
+        <v>0.20504008238649371</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8225957984054824</v>
+        <v>1.7442777766579685</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>2.0332439465536307</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.35441209541187202</v>
+        <v>0.38060581781059921</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.5001314107071084</v>
+        <v>2.4982981903965071</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7578411094318964</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>0.1243407530891798</v>
+        <v>0.12428070944437752</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>2.2573978227744331</v>
+        <v>2.2557425867656002</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>2.4986581353682982</v>
+        <v>2.4970028993594653</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17920,7 +17920,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.2057912633978517</v>
+        <v>0.20573499246785421</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BEB5C6-1B88-48AF-A13C-391267AA8BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA4E52-EE7A-4A79-9EF3-CAE82156F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3114,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3748,7 +3748,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3812,9 +3811,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3833,29 +3829,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4163,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4197,7 +4203,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>446</v>
       </c>
     </row>
@@ -4305,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4350,7 +4356,7 @@
       <c r="D22" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>443</v>
       </c>
     </row>
@@ -4381,7 +4387,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4391,14 +4397,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
-        <v>3.1471362100207654</v>
+        <v>3.1471362100207658</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.21725217049313983</v>
       </c>
@@ -4411,18 +4417,18 @@
       <c r="B28" s="45" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>3983.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>433</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4430,18 +4436,18 @@
       <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
-        <v>1.3058076567131072</v>
-      </c>
-      <c r="D29" s="339" t="str">
+        <v>1.3058076567131074</v>
+      </c>
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4449,18 +4455,18 @@
       <c r="B30" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
-        <v>1.9493178590444622</v>
-      </c>
-      <c r="D30" s="148" t="str">
+        <v>1.9493178590444624</v>
+      </c>
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4468,18 +4474,18 @@
       <c r="B31" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
-        <v>2.7560078891212951</v>
-      </c>
-      <c r="D31" s="148" t="str">
+        <v>2.7560078891212956</v>
+      </c>
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4487,18 +4493,18 @@
       <c r="B32" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>2.4970028993594653</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4526,13 +4532,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4639,7 +4645,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>57395.095749289067</v>
       </c>
@@ -4647,14 +4653,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-52759</v>
       </c>
@@ -4662,8 +4668,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4722,10 +4728,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4790,7 +4796,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8618159083223565E-2</v>
+        <v>6.8618159083223579E-2</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4826,13 +4832,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4870,7 +4876,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4907,7 +4913,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6725676276535739</v>
+        <v>1.6725676276535744</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4980,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49818907182721034</v>
+        <v>0.49818907182721045</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -4982,28 +4988,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.23422582328431374</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.10863424600069688</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>2.2824569622635926</v>
       </c>
@@ -5045,7 +5051,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8490697771281694</v>
+        <v>1.8490697771281697</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5098,7 +5104,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5106,12 +5112,12 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>1.8309265451850745</v>
+        <v>1.8309265451850749</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5270,7 +5276,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>3.1471362100207654</v>
+        <v>3.1471362100207658</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5278,13 +5284,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,13 +5303,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5367,7 +5373,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5389,7 +5395,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>1.1469155284332238</v>
+        <v>1.146915528433224</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5398,9 +5404,9 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>1.3058076567131072</v>
-      </c>
-      <c r="D144" s="336" t="str">
+        <v>1.3058076567131074</v>
+      </c>
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5409,11 +5415,11 @@
       <c r="B145" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5424,7 +5430,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58508066712991391</v>
+        <v>0.5850806671299138</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5436,7 +5442,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5458,7 +5464,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>1.7442777766579685</v>
+        <v>1.7442777766579687</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5467,9 +5473,9 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>1.9493178590444622</v>
-      </c>
-      <c r="D152" s="336" t="str">
+        <v>1.9493178590444624</v>
+      </c>
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5478,11 +5484,11 @@
       <c r="B153" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5527,7 +5533,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>2.4982981903965071</v>
+        <v>2.4982981903965076</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5536,9 +5542,9 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>2.7560078891212951</v>
-      </c>
-      <c r="D160" s="336" t="str">
+        <v>2.7560078891212956</v>
+      </c>
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5547,11 +5553,11 @@
       <c r="B161" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5607,7 +5613,7 @@
         <f>Scenarios!C105</f>
         <v>2.4970028993594653</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5616,11 +5622,11 @@
       <c r="B169" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5631,7 +5637,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20573499246785421</v>
+        <v>0.20573499246785443</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5645,7 +5651,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5659,13 +5665,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5702,22 +5708,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,6 +5747,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5757,17 +5774,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6433,43 +6439,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.130919906448</v>
+        <v>0.13091990644800003</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22434123041999995</v>
+        <v>0.22434123042000001</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19291178267999998</v>
+        <v>0.19291178268</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16798497929999998</v>
+        <v>0.1679849793</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2366828560000008E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16256610899999999</v>
+        <v>0.16256610900000001</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4188703000000006E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4188703000000005E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7836,43 +7842,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.130919906448</v>
+        <v>0.13091990644800003</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22434123041999995</v>
+        <v>0.22434123042000001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19291178267999998</v>
+        <v>0.19291178268</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16798497929999998</v>
+        <v>0.1679849793</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2366828560000008E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16256610899999999</v>
+        <v>0.16256610900000001</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4188703000000006E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4188703000000005E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8231,11 +8237,11 @@
         <f t="shared" si="40"/>
         <v>365962</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8265,11 +8271,11 @@
         <f t="shared" si="40"/>
         <v>1110767</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9190,11 +9196,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.32763841689688</v>
+        <v>4.3276384168968809</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8309265451850745</v>
+        <v>1.8309265451850749</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9496,7 +9502,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))*2</f>
         <v>4</v>
       </c>
@@ -9600,11 +9606,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2296651.6211234396</v>
+        <v>-2296651.6211234401</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49818907182721034</v>
+        <v>-0.49818907182721045</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9617,11 +9623,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>8524211.6725608613</v>
+        <v>8524211.6725608632</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8490697771281694</v>
+        <v>1.8490697771281699</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9634,11 +9640,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>56984.406565175988</v>
+        <v>56984.406565176003</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2361042638866809E-2</v>
+        <v>1.2361042638866811E-2</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9651,11 +9657,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6284544.458002598</v>
+        <v>6284544.458002599</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>1.3632417479398258</v>
+        <v>1.3632417479398262</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -11567,104 +11573,104 @@
         <v>57395.095749289067</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>114898.42340470829</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>117143.83209497746</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>103032.2190187908</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>121976.64802985649</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>175374.64499999999</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>351080</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>357941</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>314822</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>372708</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13171,43 +13177,43 @@
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.130919906448</v>
+        <v>0.13091990644800003</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22434123041999995</v>
+        <v>0.22434123042000001</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19291178267999998</v>
+        <v>0.19291178268</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16798497929999998</v>
+        <v>0.1679849793</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2366828560000008E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16256610899999999</v>
+        <v>0.16256610900000001</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4188703000000006E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4188703000000005E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.670192480000001E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13227,43 +13233,43 @@
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603540.76872528007</v>
+        <v>603540.76872528018</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034213.0722361997</v>
+        <v>1034213.0722362001</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889323.31815479998</v>
+        <v>889323.3181548001</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774410.75457299978</v>
+        <v>774410.75457300013</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800002</v>
+        <v>399695.87332800007</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379711.0796616</v>
+        <v>379711.07966160006</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749429.76248999988</v>
+        <v>749429.76248999999</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24980.992083000001</v>
+        <v>24980.992083000005</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249809.92082999999</v>
+        <v>249809.92083000002</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800002</v>
+        <v>399695.87332800007</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13282,23 +13288,23 @@
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95421703263140079</v>
+        <v>0.9542170326314009</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93269497678697</v>
+        <v>0.93269497678697022</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66190563508315692</v>
+        <v>0.66190563508315703</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.92130046033819613</v>
+        <v>0.92130046033819624</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91714805388673326</v>
+        <v>0.91714805388673337</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
@@ -13306,19 +13312,19 @@
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59260370943012186</v>
+        <v>0.59260370943012197</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3555970749640631E-2</v>
+        <v>6.3555970749640645E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60271554025101692</v>
+        <v>-0.60271554025101703</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66343418012332667</v>
+        <v>0.66343418012332678</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13337,43 +13343,43 @@
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7138413563076926E-2</v>
+        <v>6.713841356307694E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11504678483076922</v>
+        <v>0.11504678483076924</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8929119323076908E-2</v>
+        <v>9.8929119323076922E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6146143230769218E-2</v>
+        <v>8.6146143230769232E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461535E-2</v>
+        <v>4.4462525538461542E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2239399261538461E-2</v>
+        <v>4.2239399261538468E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3367235384615379E-2</v>
+        <v>8.3367235384615393E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538459E-3</v>
+        <v>2.7789078461538464E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538462E-2</v>
+        <v>2.7789078461538465E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461535E-2</v>
+        <v>4.4462525538461542E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14026,47 +14032,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3226606227451485</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.65019430537408307</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.1911040666425015</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.7903285844398347</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6212457823006146</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.5133869677398846</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.3115161389526857</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>15.801640747079396</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-4.710466049773947</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.6060025550358761</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14078,47 +14084,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.4072044192682269</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.3921031576498697</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.5946029642834716</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4961201367772632</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.8985688487688246</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.3827126502118285</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.5849400500854394</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.3222093600132299</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-2.6897368713115899</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.2473106321529053</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -14474,50 +14480,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13380541021228592</v>
+        <v>0.13380541021228595</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14869531112297604</v>
+        <v>0.14869531112297607</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.2606802997430655</v>
+        <v>0.26068029974306556</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31586494336262128</v>
+        <v>0.31586494336262133</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19760954311055715</v>
+        <v>0.19760954311055717</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10245379320394359</v>
+        <v>0.1024537932039436</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9407725719822117E-2</v>
+        <v>7.9407725719822131E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29730649532849024</v>
+        <v>0.29730649532849029</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2404080944316694E-2</v>
+        <v>9.2404080944316722E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.743951621354445E-2</v>
+        <v>-9.7439516213544478E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14163469393880693</v>
+        <v>0.14163469393880695</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14531,50 +14537,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8618159083223565E-2</v>
+        <v>6.8618159083223579E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6254005704090286E-2</v>
+        <v>7.62540057040903E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13368220499644384</v>
+        <v>0.13368220499644387</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16198202223724167</v>
+        <v>0.1619820222372417</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10133822723618316</v>
+        <v>0.10133822723618317</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2540406771253122E-2</v>
+        <v>5.2540406771253129E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0721910625549806E-2</v>
+        <v>4.0721910625549813E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15246486939922577</v>
+        <v>0.15246486939922579</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.7386708176572666E-2</v>
+        <v>4.738670817657268E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9968982673612543E-2</v>
+        <v>-4.9968982673612557E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2633176378875355E-2</v>
+        <v>7.2633176378875369E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15412,10 +15418,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15430,8 +15436,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15446,8 +15452,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15462,8 +15468,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15486,7 +15492,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15500,7 +15506,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15553,7 +15559,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.14379064377755</v>
+        <v>3.1437906437775509</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16489,23 +16495,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16516,23 +16522,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0625945857462646</v>
+        <v>3.0625945857462655</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0897751627044796</v>
+        <v>3.0897751627044805</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390902</v>
+        <v>3.1173597688390906</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390902</v>
+        <v>3.1173597688390906</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16543,23 +16549,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0885228428265115</v>
+        <v>3.0885228428265123</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.14379064377755</v>
+        <v>3.1437906437775509</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283843</v>
+        <v>3.2017620522283852</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283843</v>
+        <v>3.2017620522283852</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16570,23 +16576,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1198184630562369</v>
+        <v>3.1198184630562373</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2106497786949295</v>
+        <v>3.21064977869493</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267449</v>
+        <v>3.3089502498267458</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267449</v>
+        <v>3.3089502498267458</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16597,23 +16603,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1508810662626585</v>
+        <v>3.150881066262659</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2787685151405088</v>
+        <v>3.2787685151405097</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319889</v>
+        <v>3.4211490010319894</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319889</v>
+        <v>3.4211490010319894</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16624,23 +16630,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1790054598174224</v>
+        <v>3.1790054598174233</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3421227199442374</v>
+        <v>3.3421227199442383</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326914</v>
+        <v>3.5284757783326923</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326914</v>
+        <v>3.5284757783326923</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16650,23 +16656,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2031418941193395</v>
+        <v>3.2031418941193404</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.398009941669216</v>
+        <v>3.3980099416692164</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.625952362160219</v>
+        <v>3.6259523621602194</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.625952362160219</v>
+        <v>3.6259523621602194</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16701,7 +16707,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3089502498267449</v>
+        <v>3.3089502498267458</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16723,7 +16729,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.2017620522283843</v>
+        <v>3.2017620522283852</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16746,7 +16752,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.14379064377755</v>
+        <v>3.1437906437775509</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16769,7 +16775,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0885228428265115</v>
+        <v>3.0885228428265123</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16792,7 +16798,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16942,7 +16948,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>3.2471362100207655</v>
+        <v>3.2471362100207659</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16957,11 +16963,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16982,8 +16988,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -17004,8 +17010,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -17015,8 +17021,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -17029,8 +17035,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17048,8 +17054,8 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17066,8 +17072,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17084,8 +17090,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17111,21 +17117,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17139,8 +17145,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17148,14 +17154,14 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.0358093755934008</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17175,8 +17181,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17186,8 +17192,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17195,14 +17201,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>3.14379064377755</v>
+        <v>3.1437906437775509</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17212,8 +17218,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17233,8 +17239,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17244,8 +17250,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17253,14 +17259,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>3.0885228428265115</v>
+        <v>3.0885228428265123</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17270,8 +17276,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17291,8 +17297,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17302,8 +17308,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17311,14 +17317,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>3.2017620522283843</v>
+        <v>3.2017620522283852</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17329,8 +17335,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17338,7 +17344,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1443313652775093</v>
+        <v>3.1443313652775102</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17392,8 +17398,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17403,8 +17409,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17412,14 +17418,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>3.0358093755933995</v>
+        <v>3.0358093755934004</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17429,8 +17435,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17450,8 +17456,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17461,8 +17467,8 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17470,14 +17476,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>3.3089502498267449</v>
+        <v>3.3089502498267458</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17487,8 +17493,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17496,7 +17502,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1471362100207654</v>
+        <v>3.1471362100207658</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17505,7 +17511,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17558,7 +17564,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>3.14379064377755</v>
+        <v>3.1437906437775509</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17619,9 +17625,9 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239905</v>
+        <v>0.43316896917239917</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17693,7 +17699,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1469155284332238</v>
+        <v>1.146915528433224</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17703,7 +17709,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3058076567131072</v>
+        <v>1.3058076567131074</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17712,9 +17718,9 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
-        <v>0.58508066712991391</v>
+        <v>0.5850806671299138</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17782,7 +17788,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.7442777766579685</v>
+        <v>1.7442777766579687</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17792,7 +17798,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.9493178590444622</v>
+        <v>1.9493178590444624</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17801,7 +17807,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.38060581781059921</v>
       </c>
@@ -17811,7 +17817,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17822,7 +17828,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17834,7 +17840,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17842,11 +17848,11 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4982981903965071</v>
+        <v>2.4982981903965076</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17854,7 +17860,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7560078891212951</v>
+        <v>2.7560078891212956</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17862,7 +17868,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.12428070944437752</v>
       </c>
@@ -17918,41 +17924,41 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
-        <v>0.20573499246785421</v>
+        <v>0.20573499246785443</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA4E52-EE7A-4A79-9EF3-CAE82156F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F5D679-AFEE-43BD-8EC3-155FB31BFFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4912,7 +4912,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6725676276535744</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4966,7 +4966,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>2119124</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5037,7 +5037,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>7865303.2833807282</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5068,7 +5068,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>52579.6</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5103,7 +5103,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>3.0358093755934008</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5162,111 +5162,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.03</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>3.31 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.03</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>3.2 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.02</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>3.14 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.01</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>3.09 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>3.04 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-2296651.6211234401</v>
       </c>
       <c r="D86" s="248">
@@ -9622,7 +9622,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>8524211.6725608632</v>
       </c>
       <c r="D87" s="248">
@@ -9639,7 +9639,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>56984.406565176003</v>
       </c>
       <c r="D88" s="248">
@@ -15597,7 +15597,7 @@
         <v>580545.17368704232</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E21" s="125">
@@ -15619,7 +15619,7 @@
         <v>592156.07716078323</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E22" s="125">
@@ -15641,7 +15641,7 @@
         <v>603999.19870399882</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E23" s="125">
@@ -15663,7 +15663,7 @@
         <v>616079.18267807877</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E24" s="125">
@@ -15685,7 +15685,7 @@
         <v>628400.76633164042</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E25" s="125">
@@ -15707,7 +15707,7 @@
         <v>640968.78165827319</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E26" s="125">
@@ -15729,7 +15729,7 @@
         <v>653788.15729143866</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E27" s="125">
@@ -15751,7 +15751,7 @@
         <v>666863.92043726728</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E28" s="125">
@@ -15773,7 +15773,7 @@
         <v>680201.1988460127</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E29" s="125">
@@ -15795,7 +15795,7 @@
         <v>693805.22282293299</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>0.02</v>
       </c>
       <c r="E30" s="125">
@@ -15817,7 +15817,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15839,7 +15839,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15861,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15883,7 +15883,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15905,7 +15905,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15927,7 +15927,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15971,7 +15971,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15993,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -16015,7 +16015,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -16037,7 +16037,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16059,7 +16059,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16103,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16125,7 +16125,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16147,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16191,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16235,7 +16235,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16936,7 +16936,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17153,7 +17153,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>3.0358093755934008</v>
       </c>
       <c r="D22" t="str">
@@ -17200,7 +17200,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>3.1437906437775509</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17258,7 +17258,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>3.0885228428265123</v>
       </c>
       <c r="D33" t="str">
@@ -17316,7 +17316,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>3.2017620522283852</v>
       </c>
       <c r="D39" t="str">
@@ -17417,7 +17417,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>3.0358093755934004</v>
       </c>
       <c r="D51" t="str">
@@ -17475,7 +17475,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>3.3089502498267458</v>
       </c>
       <c r="D57" t="str">
@@ -17563,7 +17563,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>3.1437906437775509</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F5D679-AFEE-43BD-8EC3-155FB31BFFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5266BF49-9E1B-4CCD-A8E8-EC93CF80187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5266BF49-9E1B-4CCD-A8E8-EC93CF80187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEBD5CB-36F0-45B7-8BA4-116A6B9F29F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2410,28 +2405,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>中海石油化学</t>
+  </si>
+  <si>
+    <t>3983.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ENG_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>中海石油化学</t>
-  </si>
-  <si>
-    <t>3983.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>ENG_02</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2447,7 +2472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2466,6 +2491,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3114,7 +3140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3620,9 +3646,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3839,29 +3862,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3880,7 +3910,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3927,8 +3971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4169,15 +4213,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>445</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4192,7 +4236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4201,10 +4245,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>446</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4218,9 +4262,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4241,20 +4285,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4270,17 +4314,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4294,7 +4338,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4321,73 +4365,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>443</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>450</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>450</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4397,14 +4445,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>3.1471362100207658</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.21725217049313983</v>
       </c>
@@ -4415,96 +4463,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>3983.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>1.3058076567131074</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>428</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>1.9493178590444624</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>2.7560078891212956</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>2.4970028993594653</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4513,8 +4561,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4523,22 +4571,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4550,13 +4598,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4576,13 +4624,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4611,13 +4659,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4633,19 +4681,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>57395.095749289067</v>
       </c>
@@ -4653,14 +4701,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-52759</v>
       </c>
@@ -4668,8 +4716,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4703,13 +4751,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4725,13 +4773,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4747,22 +4795,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4791,26 +4839,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>6.8618159083223579E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>5.1282051282051287E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.80996280963569622</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4823,22 +4879,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4847,7 +4903,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4856,7 +4912,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4867,7 +4923,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4876,42 +4932,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6725676276535744</v>
       </c>
@@ -4921,8 +4977,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4934,13 +4990,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4953,13 +5009,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4976,9 +5032,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.49818907182721045</v>
       </c>
@@ -4988,28 +5044,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.23422582328431374</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.10863424600069688</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>2.2824569622635926</v>
       </c>
@@ -5047,9 +5103,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.8490697771281697</v>
       </c>
@@ -5078,9 +5134,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.2361042638866811E-2</v>
       </c>
@@ -5090,20 +5146,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>3.0358093755934008</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5112,10 +5168,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>1.8309265451850749</v>
       </c>
@@ -5125,8 +5181,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5135,49 +5191,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.03</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>3.31 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5195,11 +5251,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>3.2 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5217,11 +5273,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>3.14 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5239,11 +5295,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>3.09 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5261,11 +5317,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>3.04 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5284,17 +5340,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5303,22 +5359,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5329,7 +5385,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5338,7 +5394,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5358,22 +5414,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>3983.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5406,20 +5462,20 @@
         <f>Scenarios!C83</f>
         <v>1.3058076567131074</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5435,14 +5491,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5475,20 +5531,20 @@
         <f>Scenarios!C93</f>
         <v>1.9493178590444624</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5504,12 +5560,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5538,26 +5594,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>2.7560078891212956</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5573,12 +5629,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5607,26 +5663,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>2.4970028993594653</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5641,8 +5697,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5651,113 +5707,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5774,6 +5819,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5786,7 +5842,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6326,7 +6382,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>1522553</v>
@@ -6362,7 +6418,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-379005</v>
@@ -6398,7 +6454,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-1061021</v>
@@ -6484,7 +6540,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7789,7 +7845,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8237,11 +8293,11 @@
         <f t="shared" si="40"/>
         <v>365962</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8271,11 +8327,11 @@
         <f t="shared" si="40"/>
         <v>1110767</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8378,17 +8434,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8473,7 +8529,7 @@
         <f>23621+80349</f>
         <v>103970</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8484,7 +8540,7 @@
         <f>11000000+679928</f>
         <v>11679928</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8495,7 +8551,7 @@
       <c r="C5" s="19">
         <v>1830485</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8506,7 +8562,7 @@
         <f>11715</f>
         <v>11715</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8517,7 +8573,7 @@
       <c r="C6" s="19">
         <v>1124718</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8527,7 +8583,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8538,7 +8594,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8548,7 +8604,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8559,7 +8615,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8569,7 +8625,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8581,7 +8637,7 @@
         <f>12783+436808</f>
         <v>449591</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8591,7 +8647,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8602,10 +8658,10 @@
       <c r="C10" s="19">
         <v>156022</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8614,10 +8670,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8675,7 +8731,7 @@
       <c r="C15" s="19">
         <v>208252</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8684,7 +8740,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8695,7 +8751,7 @@
       <c r="C16" s="19">
         <v>600</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8704,7 +8760,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8715,7 +8771,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8724,7 +8780,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8735,7 +8791,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8744,7 +8800,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8756,7 +8812,7 @@
         <f>7177198+126839+332968+94332</f>
         <v>7731337</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8766,7 +8822,7 @@
         <f>333906+127404</f>
         <v>461310</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8777,7 +8833,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8786,7 +8842,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8797,7 +8853,7 @@
       <c r="C21" s="19">
         <v>129691</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8806,7 +8862,7 @@
       <c r="G21" s="19">
         <v>64486</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8817,10 +8873,10 @@
       <c r="C22" s="19">
         <v>123890</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8829,10 +8885,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9165,13 +9221,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9187,7 +9243,7 @@
         <f>H29</f>
         <v>7788128.25</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9202,23 +9258,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>1.8309265451850749</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9232,7 +9288,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>2.1930131935295925</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9243,22 +9299,22 @@
         <f>G29/G32</f>
         <v>0.764590497713594</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9272,7 +9328,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>8.1486059516858542E-2</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9286,22 +9342,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9323,22 +9379,22 @@
         <f>G39/G32</f>
         <v>0.32112222153227726</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9352,7 +9408,7 @@
         <f>G28/G29</f>
         <v>5.968423878019654E-2</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9371,13 +9427,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9405,7 +9461,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9415,7 +9471,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9425,7 +9481,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9435,26 +9491,26 @@
         <f>SUM(C66:C69)</f>
         <v>11691643</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9465,65 +9521,65 @@
         <v>-956584.92915481783</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>12.111829862994474</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>12.222273886679407</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>3826339.7166192713</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))*2</f>
         <v>4</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9537,7 +9593,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9551,7 +9607,7 @@
         <f>G19*H19</f>
         <v>46131</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9565,7 +9621,7 @@
         <f>G9*H9+G21*H21</f>
         <v>6448.6</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9579,11 +9635,11 @@
         <f>SUM(D79:D81)</f>
         <v>52579.6</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9594,76 +9650,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-2296651.6211234401</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.49818907182721045</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>8524211.6725608632</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>1.8490697771281699</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>56984.406565176003</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.2361042638866811E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>6284544.458002599</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>1.3632417479398262</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9784,7 +9840,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9798,7 +9854,7 @@
         <v>11946459</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9854,7 +9910,7 @@
         <f>C25</f>
         <v>-10341304.899857813</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10333174</v>
@@ -9909,7 +9965,7 @@
         <f>C4+C5</f>
         <v>1605154.1001421865</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>1613285</v>
@@ -9964,7 +10020,7 @@
         <f>C35</f>
         <v>-676714.25</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-646978</v>
@@ -10020,7 +10076,7 @@
         <v>928439.85014218651</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10076,7 +10132,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10131,7 +10187,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -10187,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10243,7 +10299,7 @@
         <f>C50</f>
         <v>4636.0957492890666</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>62139.423404708286</v>
@@ -10298,7 +10354,7 @@
         <f>SUM(C8:C12)</f>
         <v>933075.94589147554</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1028446.4234047083</v>
@@ -10353,7 +10409,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-233268.98647286888</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-316092</v>
@@ -10409,7 +10465,7 @@
         <v>-130645.02443131036</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10466,7 +10522,7 @@
         <v>569161.93498729635</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10523,8 +10579,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10548,8 +10604,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10574,7 +10630,7 @@
         <v>569161.93498729635</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10670,7 +10726,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10694,7 +10750,7 @@
         <v>-10241839</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10751,7 +10807,7 @@
         <v>-99465.899857813085</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10808,7 +10864,7 @@
         <v>-10341304.899857813</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10857,14 +10913,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10876,8 +10932,8 @@
         <v>0.85731169378306993</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10936,8 +10992,8 @@
         <v>8.3259733999683991E-3</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10994,7 +11050,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.86563766718303836</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.86495705547560164</v>
@@ -11042,14 +11098,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11060,8 +11116,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-676714.25</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11118,8 +11174,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11177,7 +11233,7 @@
         <v>-676714.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11226,14 +11282,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11246,7 +11302,7 @@
         <v>5.664559263962652E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11304,7 +11360,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11360,7 +11416,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>5.664559263962652E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>5.4156465945264617E-2</v>
@@ -11408,26 +11464,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11506,7 +11562,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11517,7 +11573,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-52759</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-52759</v>
@@ -11566,111 +11622,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>57395.095749289067</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>114898.42340470829</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>117143.83209497746</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>103032.2190187908</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>121976.64802985649</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>175374.64499999999</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>351080</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>357941</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>314822</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>372708</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11684,7 +11740,7 @@
         <f>C47+C48</f>
         <v>4636.0957492890666</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>62139.423404708286</v>
@@ -11732,14 +11788,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11752,8 +11808,8 @@
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11779,8 +11835,8 @@
         <f>G54</f>
         <v>2.4896608221132883E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11806,7 +11862,7 @@
         <f>-C8/C47</f>
         <v>17.597752992706202</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>18.315491195814932</v>
@@ -11854,14 +11910,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11875,7 +11931,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11930,7 +11986,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11985,7 +12041,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -12040,7 +12096,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -12091,11 +12147,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12151,7 +12207,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>202593</v>
@@ -12199,14 +12255,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12220,7 +12276,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12245,7 +12301,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12270,7 +12326,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12296,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12324,7 +12380,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12346,7 +12402,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12370,7 +12426,7 @@
         <v>0.86563766718303836</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12427,7 +12483,7 @@
         <v>0.13436233281696161</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12484,7 +12540,7 @@
         <v>5.664559263962652E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12541,7 +12597,7 @@
         <v>7.7716740177335097E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12598,7 +12654,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12655,8 +12711,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>453</v>
+      <c r="E78" s="295" t="s">
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12714,7 +12770,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12771,7 +12827,7 @@
         <v>3.8807279623937656E-4</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12828,7 +12884,7 @@
         <v>7.8104812973574481E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12885,7 +12941,7 @@
         <v>1.952620324339362E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12938,12 +12994,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.0935878525286059E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -13000,7 +13056,7 @@
         <v>4.7642731204894803E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13052,26 +13108,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13081,7 +13137,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13107,7 +13163,7 @@
         <v>4.7642731204894803E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13156,14 +13212,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13174,7 +13230,7 @@
       <c r="C90" s="114">
         <v>0.1</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.13091990644800003</v>
@@ -13230,7 +13286,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>461000</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>603540.76872528018</v>
@@ -13285,7 +13341,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.80996280963569622</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.9542170326314009</v>
@@ -13334,13 +13390,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>5.1282051282051287E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>6.713841356307694E-2</v>
@@ -13388,7 +13444,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13397,7 +13453,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13421,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13478,7 +13534,7 @@
         <v>-9.2732567630995688E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13556,7 +13612,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13571,7 +13627,7 @@
         <v>24075995</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13628,7 +13684,7 @@
         <v>103970</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13685,7 +13741,7 @@
         <v>1124718</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13742,7 +13798,7 @@
         <v>4569034</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13799,7 +13855,7 @@
         <v>19506961</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13848,7 +13904,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13857,7 +13913,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13883,7 +13939,7 @@
         <v>8.7029972647124972E-3</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13940,7 +13996,7 @@
         <v>9.4146558406972308E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13997,7 +14053,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -14016,63 +14072,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3226606227451485</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.65019430537408307</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.1911040666425015</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.7903285844398347</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6212457823006146</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.5133869677398846</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.3115161389526857</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>15.801640747079396</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-4.710466049773947</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.6060025550358761</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14080,58 +14136,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.4072044192682269</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.3921031576498697</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.5946029642834716</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4961201367772632</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.8985688487688246</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>3.3827126502118285</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.5849400500854394</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>4.3222093600132299</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-2.6897368713115899</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.2473106321529053</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14140,7 +14196,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14196,7 +14252,7 @@
         <f>C81</f>
         <v>7.8104812973574481E-2</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>8.6087971624454432E-2</v>
@@ -14250,7 +14306,7 @@
         <f>C4/C101</f>
         <v>0.49619793491400876</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.49619793491400876</v>
@@ -14305,7 +14361,7 @@
         <v>1.2342258232843137</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14362,7 +14418,7 @@
         <v>4.7595309702120517E-2</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14458,7 +14514,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14483,7 +14539,7 @@
         <v>0.13380541021228595</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14540,7 +14596,7 @@
         <v>6.8618159083223579E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14589,7 +14645,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15322,7 +15378,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15390,7 +15446,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15400,7 +15456,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15418,10 +15474,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15436,8 +15492,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15452,8 +15508,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15468,8 +15524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16814,7 +16870,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16845,12 +16901,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16865,6 +16921,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>461000</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>5762500</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>1.330700225807637</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>470220</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>435388.88888888882</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>479624.4</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>411200.61728395062</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>489216.88799999998</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>388356.13854595326</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>499001.22575999994</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>366780.79751562251</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>508981.2502752</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>346404.08654253243</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>519160.875280704</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>327159.41506794718</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>529544.09278631816</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>308983.89200861688</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>540134.9746420444</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>291818.12023036031</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>550937.67413488531</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>275606.00243978476</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>561956.42761758296</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>260294.55785979662</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>5877750</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>2722535.5245897528</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>6134528.040973207</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>6134528.040973207</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.01</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.02</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.03</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.03</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>5762499.9999999991</v>
+      </c>
+      <c r="C51" s="124">
+        <v>5854783.1286184937</v>
+      </c>
+      <c r="D51" s="124">
+        <v>5948428.4151420891</v>
+      </c>
+      <c r="E51" s="124">
+        <v>6043465.7040520106</v>
+      </c>
+      <c r="F51" s="124">
+        <v>6043465.7040520106</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>5762499.9999999981</v>
+      </c>
+      <c r="C52" s="124">
+        <v>5944113.7954056608</v>
+      </c>
+      <c r="D52" s="124">
+        <v>6134528.040973207</v>
+      </c>
+      <c r="E52" s="124">
+        <v>6334257.0299089691</v>
+      </c>
+      <c r="F52" s="124">
+        <v>6334257.0299089691</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>5762499.9999999972</v>
+      </c>
+      <c r="C53" s="124">
+        <v>6051936.6472844742</v>
+      </c>
+      <c r="D53" s="124">
+        <v>6364877.9285301566</v>
+      </c>
+      <c r="E53" s="124">
+        <v>6703552.7034878442</v>
+      </c>
+      <c r="F53" s="124">
+        <v>6703552.7034878442</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>5762499.9999999972</v>
+      </c>
+      <c r="C54" s="124">
+        <v>6158956.6852294384</v>
+      </c>
+      <c r="D54" s="124">
+        <v>6599567.5233050678</v>
+      </c>
+      <c r="E54" s="124">
+        <v>7090111.2456540884</v>
+      </c>
+      <c r="F54" s="124">
+        <v>7090111.2456540884</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>5762499.9999999963</v>
+      </c>
+      <c r="C55" s="124">
+        <v>6255853.7046263088</v>
+      </c>
+      <c r="D55" s="124">
+        <v>6817841.8693736047</v>
+      </c>
+      <c r="E55" s="124">
+        <v>7459884.3681094954</v>
+      </c>
+      <c r="F55" s="124">
+        <v>7459884.3681094954</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>5762499.9999999963</v>
+      </c>
+      <c r="C56" s="124">
+        <v>6339011.0014466001</v>
+      </c>
+      <c r="D56" s="124">
+        <v>7010390.2063529529</v>
+      </c>
+      <c r="E56" s="124">
+        <v>7795720.6027818955</v>
+      </c>
+      <c r="F56" s="124">
+        <v>7795720.6027818955</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.01</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.02</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.03</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.03</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>1.354717575</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>1.3547175749999998</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.376412599072097</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3984278555526914</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4207703606401749</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4207703606401749</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3547175749999996</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3974135230257707</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4421783863664597</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4891330712338364</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4891330712338364</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3547175749999993</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4227618115163305</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.496331799133952</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5759515249203897</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5759515249203897</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3547175749999993</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4479213648840024</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5515054422942469</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.6668283406842059</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.6668283406842059</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3547175749999991</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4707010777069189</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.6028199920193107</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7537590387758271</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7537590387758271</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.3547175749999991</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.4902506918486873</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.6480865631504074</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.8327114464864604</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.8327114464864604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.03</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>1.5759515249203897</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.03</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>1.4891330712338364</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.02</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>1.4421783863664597</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.01</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>1.3974135230257707</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>1.3547175749999993</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16885,19 +18392,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-1.95</v>
       </c>
@@ -16914,19 +18421,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -16940,13 +18447,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>3.2471362100207659</v>
       </c>
@@ -16963,15 +18470,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16988,12 +18495,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17010,37 +18517,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>449</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17054,12 +18561,12 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17072,12 +18579,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17090,8 +18597,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17107,7 +18614,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17117,25 +18624,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17145,23 +18652,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>3.0358093755934008</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17181,8 +18688,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17192,23 +18699,23 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>3.1437906437775509</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17218,8 +18725,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17239,8 +18746,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17250,23 +18757,23 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>3.0885228428265123</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17276,8 +18783,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17297,8 +18804,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17308,23 +18815,23 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>3.2017620522283852</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17335,8 +18842,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17398,8 +18905,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17409,23 +18916,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>3.0358093755934004</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17435,12 +18942,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17456,8 +18963,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17467,23 +18974,23 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>3.3089502498267458</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17493,8 +19000,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17509,16 +19016,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17527,10 +19034,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17542,8 +19049,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17554,8 +19061,8 @@
         <v>0.02</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17563,30 +19070,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>3.1437906437775509</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17594,38 +19101,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>0.43316896917239917</v>
       </c>
@@ -17645,10 +19152,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17669,12 +19176,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17718,7 +19225,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.5850806671299138</v>
       </c>
@@ -17728,14 +19235,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>1.95</v>
       </c>
@@ -17746,9 +19253,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.21725217049313983</v>
       </c>
@@ -17758,12 +19265,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17807,28 +19314,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.38060581781059921</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17840,7 +19347,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17852,23 +19359,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>2.7560078891212956</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.12428070944437752</v>
       </c>
@@ -17878,12 +19385,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17912,19 +19419,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>2.4970028993594653</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.20573499246785443</v>
       </c>
@@ -17933,33 +19440,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1F2B3A-4368-F54A-8DFA-6ADB2350ADD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2E9DA-DAF6-594C-B7BE-F782B4D7007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2540" yWindow="5180" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3877,6 +3877,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,9 +3915,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4223,7 +4223,7 @@
       <c r="C1" s="44">
         <v>45754</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>462</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4378,13 +4378,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>3.1471362100207658</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>1.3058076567131074</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>1.9493178590444624</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>2.7560078891212956</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4584,22 +4584,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4611,13 +4611,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4637,13 +4637,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4672,13 +4672,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4764,13 +4764,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4786,13 +4786,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4808,22 +4808,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8618159083223579E-2</v>
+        <v>6.8618159083223565E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4892,22 +4892,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4951,22 +4951,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6725676276535744</v>
+        <v>1.6725676276535739</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -5003,13 +5003,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5022,13 +5022,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C97" s="245">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49818907182721045</v>
+        <v>0.49818907182721034</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C105" s="245">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8490697771281697</v>
+        <v>1.8490697771281694</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5159,13 +5159,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>1.8309265451850749</v>
+        <v>1.8309265451850745</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5204,13 +5204,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>3.1471362100207658</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5353,13 +5353,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5372,22 +5372,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>1.146915528433224</v>
+        <v>1.1469155284332238</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>1.3058076567131074</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5850806671299138</v>
+        <v>0.58508066712991391</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.15">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>1.7442777766579687</v>
+        <v>1.7442777766579685</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>1.9493178590444624</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>2.4982981903965076</v>
+        <v>2.4982981903965071</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.15">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>2.7560078891212956</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20573499246785443</v>
+        <v>0.20573499246785421</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
@@ -5720,13 +5720,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5763,13 +5763,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5777,22 +5777,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -6508,43 +6508,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13091990644800003</v>
+        <v>0.130919906448</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22434123042000001</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19291178268</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.1679849793</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2366828560000008E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16256610900000001</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4188703000000006E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4188703000000005E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7911,43 +7911,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13091990644800003</v>
+        <v>0.130919906448</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22434123042000001</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19291178268</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.1679849793</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2366828560000008E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16256610900000001</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188703000000006E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188703000000005E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9265,11 +9265,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3276384168968809</v>
+        <v>4.32763841689688</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8309265451850749</v>
+        <v>1.8309265451850745</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9675,11 +9675,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2296651.6211234401</v>
+        <v>-2296651.6211234396</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49818907182721045</v>
+        <v>-0.49818907182721034</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9692,11 +9692,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8524211.6725608632</v>
+        <v>8524211.6725608613</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8490697771281699</v>
+        <v>1.8490697771281694</v>
       </c>
       <c r="E87" s="262" t="str">
         <f>Market_currency</f>
@@ -9709,11 +9709,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>56984.406565176003</v>
+        <v>56984.406565175988</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2361042638866811E-2</v>
+        <v>1.2361042638866809E-2</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9726,11 +9726,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6284544.458002599</v>
+        <v>6284544.458002598</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
-        <v>1.3632417479398262</v>
+        <v>1.3632417479398258</v>
       </c>
       <c r="E89" s="262" t="str">
         <f>Market_currency</f>
@@ -13246,43 +13246,43 @@
       <c r="E90" s="293"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.13091990644800003</v>
+        <v>0.130919906448</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22434123042000001</v>
+        <v>0.22434123041999995</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19291178268</v>
+        <v>0.19291178267999998</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.1679849793</v>
+        <v>0.16798497929999998</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2366828560000008E-2</v>
+        <v>8.2366828559999994E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16256610900000001</v>
+        <v>0.16256610899999999</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4188703000000006E-3</v>
+        <v>5.4188702999999998E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4188703000000005E-2</v>
+        <v>5.4188702999999998E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.670192480000001E-2</v>
+        <v>8.6701924799999996E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13302,43 +13302,43 @@
       <c r="E91" s="293"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603540.76872528018</v>
+        <v>603540.76872528007</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034213.0722362001</v>
+        <v>1034213.0722361997</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889323.3181548001</v>
+        <v>889323.31815479998</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774410.75457300013</v>
+        <v>774410.75457299978</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800007</v>
+        <v>399695.87332800002</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379711.07966160006</v>
+        <v>379711.0796616</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749429.76248999999</v>
+        <v>749429.76248999988</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24980.992083000005</v>
+        <v>24980.992083000001</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249809.92083000002</v>
+        <v>249809.92082999999</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800007</v>
+        <v>399695.87332800002</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13357,23 +13357,23 @@
       <c r="E92" s="293"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.9542170326314009</v>
+        <v>0.95421703263140079</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93269497678697022</v>
+        <v>0.93269497678697</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66190563508315703</v>
+        <v>0.66190563508315692</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.92130046033819624</v>
+        <v>0.92130046033819613</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91714805388673337</v>
+        <v>0.91714805388673326</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
@@ -13381,19 +13381,19 @@
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59260370943012197</v>
+        <v>0.59260370943012186</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3555970749640645E-2</v>
+        <v>6.3555970749640631E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60271554025101703</v>
+        <v>-0.60271554025101692</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66343418012332678</v>
+        <v>0.66343418012332667</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13412,43 +13412,43 @@
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.713841356307694E-2</v>
+        <v>6.7138413563076926E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11504678483076924</v>
+        <v>0.11504678483076922</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8929119323076922E-2</v>
+        <v>9.8929119323076908E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6146143230769232E-2</v>
+        <v>8.6146143230769218E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461542E-2</v>
+        <v>4.4462525538461535E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2239399261538468E-2</v>
+        <v>4.2239399261538461E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3367235384615393E-2</v>
+        <v>8.3367235384615379E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538464E-3</v>
+        <v>2.7789078461538459E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538465E-2</v>
+        <v>2.7789078461538462E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461542E-2</v>
+        <v>4.4462525538461535E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14549,50 +14549,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13380541021228595</v>
+        <v>0.13380541021228592</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14869531112297607</v>
+        <v>0.14869531112297604</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.26068029974306556</v>
+        <v>0.2606802997430655</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31586494336262133</v>
+        <v>0.31586494336262128</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19760954311055717</v>
+        <v>0.19760954311055715</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.1024537932039436</v>
+        <v>0.10245379320394359</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9407725719822131E-2</v>
+        <v>7.9407725719822117E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29730649532849029</v>
+        <v>0.29730649532849024</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2404080944316722E-2</v>
+        <v>9.2404080944316694E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.7439516213544478E-2</v>
+        <v>-9.743951621354445E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14163469393880695</v>
+        <v>0.14163469393880693</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14606,50 +14606,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8618159083223579E-2</v>
+        <v>6.8618159083223565E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.62540057040903E-2</v>
+        <v>7.6254005704090286E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13368220499644387</v>
+        <v>0.13368220499644384</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1619820222372417</v>
+        <v>0.16198202223724167</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10133822723618317</v>
+        <v>0.10133822723618316</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2540406771253129E-2</v>
+        <v>5.2540406771253122E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0721910625549813E-2</v>
+        <v>4.0721910625549806E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15246486939922579</v>
+        <v>0.15246486939922577</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.738670817657268E-2</v>
+        <v>4.7386708176572666E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9968982673612557E-2</v>
+        <v>-4.9968982673612543E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2633176378875369E-2</v>
+        <v>7.2633176378875355E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15487,10 +15487,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15505,8 +15505,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15521,8 +15521,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15537,8 +15537,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="C11" s="229">
         <f>Exchange_Rate</f>
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1437906437775509</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16564,23 +16564,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16591,23 +16591,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0625945857462655</v>
+        <v>3.0625945857462646</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0897751627044805</v>
+        <v>3.0897751627044796</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390906</v>
+        <v>3.1173597688390902</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390906</v>
+        <v>3.1173597688390902</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16618,23 +16618,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0885228428265123</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1437906437775509</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283852</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283852</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16645,23 +16645,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1198184630562373</v>
+        <v>3.1198184630562369</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.21064977869493</v>
+        <v>3.2106497786949295</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267458</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267458</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16672,23 +16672,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.150881066262659</v>
+        <v>3.1508810662626585</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2787685151405097</v>
+        <v>3.2787685151405088</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319894</v>
+        <v>3.4211490010319889</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319894</v>
+        <v>3.4211490010319889</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16699,23 +16699,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1790054598174233</v>
+        <v>3.1790054598174224</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3421227199442383</v>
+        <v>3.3421227199442374</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326923</v>
+        <v>3.5284757783326914</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326923</v>
+        <v>3.5284757783326914</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
@@ -16725,23 +16725,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2031418941193404</v>
+        <v>3.2031418941193395</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3980099416692164</v>
+        <v>3.398009941669216</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6259523621602194</v>
+        <v>3.625952362160219</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.6259523621602194</v>
+        <v>3.625952362160219</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3089502498267458</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.2017620522283852</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1437906437775509</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16844,7 +16844,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0885228428265123</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -17017,8 +17017,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18016,23 +18016,23 @@
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>1.354717575</v>
+        <v>1.3547175749999998</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -18043,23 +18043,23 @@
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.3547175749999998</v>
+        <v>1.3547175749999996</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>1.376412599072097</v>
+        <v>1.3764125990720966</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>1.3984278555526914</v>
+        <v>1.398427855552691</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4207703606401749</v>
+        <v>1.4207703606401747</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4207703606401749</v>
+        <v>1.4207703606401747</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -18070,23 +18070,23 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999996</v>
+        <v>1.3547175749999993</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>1.3974135230257707</v>
+        <v>1.3974135230257703</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4421783863664597</v>
+        <v>1.4421783863664595</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4891330712338364</v>
+        <v>1.4891330712338362</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4891330712338364</v>
+        <v>1.4891330712338362</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18097,23 +18097,23 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999993</v>
+        <v>1.3547175749999991</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>1.4227618115163305</v>
+        <v>1.4227618115163303</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>1.496331799133952</v>
+        <v>1.4963317991339515</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5759515249203897</v>
+        <v>1.5759515249203895</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5759515249203897</v>
+        <v>1.5759515249203895</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18124,23 +18124,23 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999993</v>
+        <v>1.3547175749999991</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>1.4479213648840024</v>
+        <v>1.4479213648840019</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>1.5515054422942469</v>
+        <v>1.5515054422942467</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>1.6668283406842059</v>
+        <v>1.6668283406842055</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>1.6668283406842059</v>
+        <v>1.6668283406842055</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18151,23 +18151,23 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999991</v>
+        <v>1.3547175749999989</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>1.4707010777069189</v>
+        <v>1.4707010777069185</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>1.6028199920193107</v>
+        <v>1.6028199920193102</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>1.7537590387758271</v>
+        <v>1.7537590387758266</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>1.7537590387758271</v>
+        <v>1.7537590387758266</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
@@ -18177,23 +18177,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999991</v>
+        <v>1.3547175749999989</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>1.4902506918486873</v>
+        <v>1.4902506918486869</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>1.6480865631504074</v>
+        <v>1.6480865631504069</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>1.8327114464864604</v>
+        <v>1.83271144648646</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>1.8327114464864604</v>
+        <v>1.83271144648646</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.5759515249203897</v>
+        <v>1.5759515249203895</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.4891330712338364</v>
+        <v>1.4891330712338362</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.4421783863664597</v>
+        <v>1.4421783863664595</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.3974135230257707</v>
+        <v>1.3974135230257703</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.3547175749999993</v>
+        <v>1.3547175749999991</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
@@ -18468,7 +18468,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>3.2471362100207659</v>
+        <v>3.2471362100207655</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18483,11 +18483,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18508,8 +18508,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18530,8 +18530,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18541,8 +18541,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18555,8 +18555,8 @@
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18574,8 +18574,8 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18592,8 +18592,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18610,8 +18610,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18637,21 +18637,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18665,8 +18665,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18674,14 +18674,14 @@
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.0358093755934008</v>
+        <v>3.0358093755933999</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18701,8 +18701,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18712,8 +18712,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18721,14 +18721,14 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.1437906437775509</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18738,8 +18738,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18759,8 +18759,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18770,8 +18770,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18779,14 +18779,14 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.0885228428265123</v>
+        <v>3.0885228428265115</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18796,8 +18796,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18817,8 +18817,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18828,8 +18828,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18837,14 +18837,14 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.2017620522283852</v>
+        <v>3.2017620522283843</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18855,8 +18855,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1443313652775102</v>
+        <v>3.1443313652775093</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18918,8 +18918,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18929,8 +18929,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18938,14 +18938,14 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.0358093755934004</v>
+        <v>3.0358093755933995</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18955,8 +18955,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18976,8 +18976,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18987,8 +18987,8 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18996,14 +18996,14 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.3089502498267458</v>
+        <v>3.3089502498267449</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -19013,8 +19013,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1471362100207658</v>
+        <v>3.1471362100207654</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.1437906437775509</v>
+        <v>3.14379064377755</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239917</v>
+        <v>0.43316896917239905</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.146915528433224</v>
+        <v>1.1469155284332238</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3058076567131074</v>
+        <v>1.3058076567131072</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.5850806671299138</v>
+        <v>0.58508066712991391</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.15">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.7442777766579687</v>
+        <v>1.7442777766579685</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.9493178590444624</v>
+        <v>1.9493178590444622</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4982981903965076</v>
+        <v>2.4982981903965071</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7560078891212956</v>
+        <v>2.7560078891212951</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19446,7 +19446,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.20573499246785443</v>
+        <v>0.20573499246785421</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.15">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2E9DA-DAF6-594C-B7BE-F782B4D7007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A48A21A-A871-443A-AE7D-ED52FE8F397E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="5180" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2505,7 +2494,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3918,7 +3907,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4207,7 +4196,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4216,7 +4205,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4222,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4247,7 +4236,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>417</v>
       </c>
@@ -4256,7 +4245,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4264,7 +4253,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4273,7 +4262,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4283,7 +4272,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4293,17 +4282,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>419</v>
       </c>
@@ -4315,7 +4304,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4325,7 +4314,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>418</v>
       </c>
@@ -4335,7 +4324,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>422</v>
       </c>
@@ -4349,7 +4338,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>421</v>
       </c>
@@ -4363,7 +4352,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4373,11 +4362,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4386,14 +4375,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4408,7 +4397,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4421,7 +4410,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>436</v>
       </c>
@@ -4429,7 +4418,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>437</v>
       </c>
@@ -4437,7 +4426,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4453,28 +4442,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>3.1471362100207654</v>
+        <v>3.2635759761825347</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21725217049313983</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.23107791371828346</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>435</v>
       </c>
@@ -4493,13 +4482,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>1.3058076567131072</v>
+        <v>1.4421853171775827</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4509,16 +4498,16 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>1.9493178590444622</v>
+        <v>2.0138537681635289</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4531,13 +4520,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>2.7560078891212951</v>
+        <v>2.8871025504129477</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4547,16 +4536,16 @@
         <v>438</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>2.4970028993594653</v>
+        <v>2.5804623119161265</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4569,11 +4558,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4583,7 +4572,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4592,7 +4581,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4601,7 +4590,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4610,7 +4599,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4619,7 +4608,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4632,11 +4621,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4645,7 +4634,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4658,7 +4647,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4671,7 +4660,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4680,7 +4669,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4693,7 +4682,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4702,7 +4691,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4717,7 +4706,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4732,7 +4721,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4745,12 +4734,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4763,7 +4752,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4772,7 +4761,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4785,7 +4774,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4794,7 +4783,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4807,7 +4796,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4816,7 +4805,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4825,7 +4814,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4838,7 +4827,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4851,7 +4840,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4861,7 +4850,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4877,7 +4866,7 @@
         <v>0.80996280963569622</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4887,10 +4876,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4900,7 +4889,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4909,21 +4898,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>432</v>
       </c>
@@ -4932,25 +4921,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4959,7 +4948,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4968,7 +4957,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4976,20 +4965,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6725676276535739</v>
+        <v>1.7840721361638123</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4999,10 +4988,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5011,17 +5000,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5030,7 +5019,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5043,7 +5032,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5056,7 +5045,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5065,7 +5054,7 @@
         <v>0.23422582328431374</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5074,7 +5063,7 @@
         <v>0.10863424600069688</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5083,12 +5072,12 @@
         <v>2.2824569622635926</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5101,7 +5090,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5114,7 +5103,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5127,12 +5116,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5145,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5158,7 +5147,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5167,20 +5156,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5203,7 +5192,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5212,7 +5201,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5229,7 +5218,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5244,14 +5233,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.31 HKD</v>
+        <v>3.43 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5266,14 +5255,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>3.2 HKD</v>
+        <v>3.32 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5288,14 +5277,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>3.14 HKD</v>
+        <v>3.26 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5310,14 +5299,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>3.09 HKD</v>
+        <v>3.2 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5332,27 +5321,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>3.04 HKD</v>
+        <v>3.15 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>3.1471362100207654</v>
+        <v>3.2635759761825347</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5361,7 +5350,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5371,7 +5360,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5380,7 +5369,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5389,12 +5378,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5403,16 +5392,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5425,7 +5414,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5438,49 +5427,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.15889212827988333</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.16572593193648588</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>1.1469155284332238</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.2764593852410968</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>1.3058076567131072</v>
+        <v>1.4421853171775827</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>418</v>
       </c>
@@ -5493,21 +5482,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58508066712991391</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.55809660087505186</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5516,7 +5505,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5526,30 +5515,30 @@
         <v>0.20504008238649371</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>1.7442777766579685</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>1.8088136857770354</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>1.9493178590444622</v>
+        <v>2.0138537681635289</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>418</v>
       </c>
@@ -5562,63 +5551,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38060581781059921</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.38293032463145815</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>0.25770969872478805</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.26005257398719595</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>2.4982981903965071</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>2.6270499764257518</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>2.7560078891212951</v>
+        <v>2.8871025504129477</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>418</v>
       </c>
@@ -5631,21 +5620,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12428070944437752</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.1153561089176649</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>425</v>
       </c>
@@ -5654,7 +5643,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5664,30 +5653,30 @@
         <v>0.24126031259386493</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>2.2557425867656002</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.3392019993222615</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>2.4970028993594653</v>
+        <v>2.5804623119161265</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>418</v>
       </c>
@@ -5700,16 +5689,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20573499246785421</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.20844420967210364</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5719,7 +5708,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5728,12 +5717,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5742,27 +5731,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5771,12 +5760,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5785,7 +5774,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5794,22 +5783,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5870,15 +5859,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5927,7 +5916,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5943,7 +5932,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5951,7 +5940,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5987,7 +5976,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6023,7 +6012,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6059,7 +6048,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6095,7 +6084,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6111,7 +6100,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6127,7 +6116,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6143,7 +6132,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6159,7 +6148,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6195,7 +6184,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6231,7 +6220,7 @@
       </c>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6267,7 +6256,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6303,7 +6292,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6339,13 +6328,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6361,7 +6350,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6377,7 +6366,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6393,7 +6382,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6429,7 +6418,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6465,7 +6454,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6501,7 +6490,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6548,7 +6537,7 @@
       </c>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6556,7 +6545,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6593,7 +6582,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6630,7 +6619,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6667,7 +6656,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6704,7 +6693,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6741,7 +6730,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6757,12 +6746,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6811,7 +6800,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6860,7 +6849,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6909,7 +6898,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6958,7 +6947,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7007,7 +6996,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7056,7 +7045,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7105,7 +7094,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7154,7 +7143,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7203,7 +7192,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7252,7 +7241,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7301,7 +7290,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7350,7 +7339,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7399,12 +7388,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7453,7 +7442,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7502,12 +7491,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7556,7 +7545,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7605,7 +7594,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7654,7 +7643,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7703,13 +7692,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7758,7 +7747,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7807,7 +7796,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7856,7 +7845,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7905,7 +7894,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7954,12 +7943,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8009,7 +7998,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8058,7 +8047,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8108,7 +8097,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8157,7 +8146,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8207,7 +8196,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8223,13 +8212,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8278,7 +8267,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8312,7 +8301,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8346,7 +8335,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8395,7 +8384,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8476,7 +8465,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8487,7 +8476,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8503,7 +8492,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8514,7 +8503,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8534,7 +8523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8557,7 +8546,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8579,7 +8568,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8600,7 +8589,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8621,7 +8610,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8642,7 +8631,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8664,7 +8653,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8676,7 +8665,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8688,7 +8677,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8712,12 +8701,12 @@
         <v>10520135.700000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8737,7 +8726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8757,7 +8746,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8777,7 +8766,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8797,7 +8786,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8817,7 +8806,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8839,7 +8828,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8859,7 +8848,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8879,7 +8868,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8891,7 +8880,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8903,7 +8892,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8927,7 +8916,7 @@
         <v>52579.6</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8944,7 +8933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8963,7 +8952,7 @@
         <v>8886812.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8978,7 +8967,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8997,7 +8986,7 @@
         <v>7788128.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9013,7 +9002,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9030,7 +9019,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9050,7 +9039,7 @@
         <v>13455846.25</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9061,7 +9050,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9074,7 +9063,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9093,7 +9082,7 @@
         <v>2883130.95</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9109,7 +9098,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9125,7 +9114,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9141,7 +9130,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9160,7 +9149,7 @@
         <v>773133.70000000007</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9180,7 +9169,7 @@
         <v>10572715.300000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9200,7 +9189,7 @@
         <v>10520135.700000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9219,7 +9208,7 @@
         <v>52579.6</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9230,7 +9219,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9244,7 +9233,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9258,7 +9247,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9273,10 +9262,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9289,7 +9278,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9303,7 +9292,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9314,10 +9303,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9329,7 +9318,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9343,7 +9332,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9357,10 +9346,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9372,7 +9361,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9383,7 +9372,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9394,10 +9383,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9409,7 +9398,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9425,7 +9414,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9436,7 +9425,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9450,7 +9439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9466,7 +9455,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9476,7 +9465,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9486,7 +9475,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9496,7 +9485,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9506,10 +9495,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9521,7 +9510,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9537,7 +9526,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9553,7 +9542,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9566,7 +9555,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9579,10 +9568,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9594,7 +9583,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9608,7 +9597,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9622,7 +9611,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9636,7 +9625,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9650,7 +9639,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9661,7 +9650,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9669,7 +9658,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9686,7 +9675,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9703,7 +9692,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9720,7 +9709,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9751,19 +9740,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9820,7 +9809,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9843,7 +9832,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9857,7 +9846,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9914,7 +9903,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9969,7 +9958,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10024,7 +10013,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10079,7 +10068,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10136,7 +10125,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10191,7 +10180,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10246,7 +10235,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10303,7 +10292,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10358,7 +10347,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10413,7 +10402,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10468,7 +10457,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10525,7 +10514,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10582,7 +10571,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10608,7 +10597,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10633,7 +10622,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10690,7 +10679,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10709,7 +10698,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10732,7 +10721,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10753,7 +10742,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10810,7 +10799,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10867,7 +10856,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10924,18 +10913,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10994,7 +10983,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11054,7 +11043,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11109,18 +11098,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11177,7 +11166,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11236,7 +11225,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11293,18 +11282,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11362,7 +11351,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11420,7 +11409,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11475,18 +11464,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11544,10 +11533,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11570,14 +11559,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11632,7 +11621,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11687,7 +11676,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11744,7 +11733,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11799,11 +11788,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11813,7 +11802,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11839,7 +11828,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11866,7 +11855,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11921,11 +11910,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11935,7 +11924,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11990,7 +11979,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12045,7 +12034,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12100,7 +12089,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12155,7 +12144,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12211,7 +12200,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12266,11 +12255,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12280,7 +12269,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12305,7 +12294,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12330,7 +12319,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12355,7 +12344,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12382,10 +12371,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12408,7 +12397,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12429,7 +12418,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12486,7 +12475,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12543,7 +12532,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12600,7 +12589,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12657,7 +12646,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12714,7 +12703,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12773,7 +12762,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12830,7 +12819,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12887,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12944,7 +12933,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13001,7 +12990,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13059,7 +13048,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13116,7 +13105,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13142,7 +13131,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13166,7 +13155,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13223,18 +13212,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13289,7 +13278,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13345,7 +13334,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13400,7 +13389,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13455,11 +13444,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13480,7 +13469,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13537,7 +13526,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13594,10 +13583,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13620,7 +13609,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13630,7 +13619,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13687,7 +13676,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13744,7 +13733,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13801,7 +13790,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13858,7 +13847,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13915,11 +13904,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13942,7 +13931,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13999,7 +13988,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14056,7 +14045,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14083,18 +14072,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14146,7 +14135,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14198,11 +14187,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14256,7 +14245,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14311,7 +14300,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14365,7 +14354,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14421,7 +14410,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14478,7 +14467,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14497,7 +14486,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14520,7 +14509,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14541,7 +14530,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14599,7 +14588,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14656,7 +14645,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14706,688 +14695,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15409,16 +15398,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15430,7 +15419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15443,7 +15432,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15464,24 +15453,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>7114524.1873412039</v>
+        <v>7588825.7998306183</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15493,7 +15482,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15509,7 +15498,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15525,7 +15514,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15541,13 +15530,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>12913283.070721932</v>
+        <v>13387584.683211347</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15555,7 +15544,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15569,13 +15558,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15583,10 +15572,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15596,13 +15585,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15612,7 +15601,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15622,13 +15611,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.14379064377755</v>
+        <v>3.2599879167672925</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15636,10 +15625,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15657,7 +15646,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15671,15 +15660,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>537541.82748800213</v>
+        <v>540042.022034458</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15693,15 +15682,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>507678.39262755762</v>
+        <v>512411.96509316022</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15715,15 +15704,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>479474.03748158208</v>
+        <v>486195.53897211479</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15737,15 +15726,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>452836.59095482749</v>
+        <v>461320.41837354144</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15759,15 +15748,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>427679.00256844825</v>
+        <v>437717.9783637324</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15781,15 +15770,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>403919.0579813121</v>
+        <v>415323.10505209956</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15803,15 +15792,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>381479.11031568371</v>
+        <v>394074.01595641079</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15825,15 +15814,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>360285.82640925673</v>
+        <v>373912.08955864079</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15847,15 +15836,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>340269.94716429804</v>
+        <v>354781.70358122204</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15869,15 +15858,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>321366.06121072592</v>
+        <v>336630.08153753169</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15899,7 +15888,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15921,7 +15910,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15943,7 +15932,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15965,7 +15954,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15987,7 +15976,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -16009,7 +15998,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16031,7 +16020,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16053,7 +16042,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16075,7 +16064,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16097,7 +16086,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16119,7 +16108,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16141,7 +16130,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16163,7 +16152,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16185,7 +16174,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16207,7 +16196,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16229,7 +16218,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16251,7 +16240,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16273,7 +16262,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16295,7 +16284,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16317,13 +16306,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>7256814.6710880287</v>
+        <v>7740602.3158272309</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16331,30 +16320,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3361309.2998853745</v>
+        <v>3755693.2450356269</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>7573839.1540870694</v>
+        <v>8068102.1635585381</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16364,10 +16353,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>7573839.1540870694</v>
+        <v>8068102.1635585381</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16391,141 +16380,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>7114524.187341203</v>
+        <v>7588825.7998306192</v>
       </c>
       <c r="C56" s="124">
-        <v>7228459.2069750074</v>
+        <v>7708291.1258954611</v>
       </c>
       <c r="D56" s="124">
-        <v>7344075.9802509518</v>
+        <v>7829471.2855157647</v>
       </c>
       <c r="E56" s="124">
-        <v>7461411.3538993616</v>
+        <v>7952403.9164119214</v>
       </c>
       <c r="F56" s="124">
-        <v>7461411.3538993616</v>
+        <v>7952403.9164119214</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>7114524.1873412021</v>
+        <v>7588825.7998306202</v>
       </c>
       <c r="C57" s="124">
-        <v>7338749.0446372405</v>
+        <v>7822832.2996255979</v>
       </c>
       <c r="D57" s="124">
-        <v>7573839.1540870694</v>
+        <v>8068102.1635585381</v>
       </c>
       <c r="E57" s="124">
-        <v>7820429.4747285768</v>
+        <v>8325295.7727201767</v>
       </c>
       <c r="F57" s="124">
-        <v>7820429.4747285768</v>
+        <v>8325295.7727201767</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>7114524.1873412021</v>
+        <v>7588825.7998306192</v>
       </c>
       <c r="C58" s="124">
-        <v>7471869.7886962304</v>
+        <v>7964249.5538186785</v>
       </c>
       <c r="D58" s="124">
-        <v>7858234.7890675925</v>
+        <v>8370236.8003636207</v>
       </c>
       <c r="E58" s="124">
-        <v>8276370.9935064297</v>
+        <v>8809700.3190522641</v>
       </c>
       <c r="F58" s="124">
-        <v>8276370.9935064297</v>
+        <v>8809700.3190522641</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>7114524.1873412011</v>
+        <v>7588825.7998306192</v>
       </c>
       <c r="C59" s="124">
-        <v>7603999.3589330409</v>
+        <v>8107875.5886692684</v>
       </c>
       <c r="D59" s="124">
-        <v>8147988.3332833685</v>
+        <v>8685217.0884205196</v>
       </c>
       <c r="E59" s="124">
-        <v>8753625.6742986385</v>
+        <v>9328532.7985863127</v>
       </c>
       <c r="F59" s="124">
-        <v>8753625.6742986385</v>
+        <v>9328532.7985863127</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>7114524.1873412021</v>
+        <v>7588825.7998306174</v>
       </c>
       <c r="C60" s="124">
-        <v>7723630.8015673673</v>
+        <v>8240951.9074817337</v>
       </c>
       <c r="D60" s="124">
-        <v>8417475.2078309935</v>
+        <v>8985005.625718208</v>
       </c>
       <c r="E60" s="124">
-        <v>9210156.6631988883</v>
+        <v>9836424.1410892401</v>
       </c>
       <c r="F60" s="124">
-        <v>9210156.6631988883</v>
+        <v>9836424.1410892401</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>7114524.187341203</v>
+        <v>7588825.7998306174</v>
       </c>
       <c r="C61" s="124">
-        <v>7826298.8448787555</v>
+        <v>8357830.033836456</v>
       </c>
       <c r="D61" s="124">
-        <v>8655200.1190104969</v>
+        <v>9255647.5660671927</v>
       </c>
       <c r="E61" s="124">
-        <v>9624788.3360079788</v>
+        <v>10308494.572138546</v>
       </c>
       <c r="F61" s="124">
-        <v>9624788.3360079788</v>
+        <v>10308494.572138546</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16535,7 +16524,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16558,193 +16547,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0625945857462646</v>
+        <v>3.1753992249840111</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.0897751627044796</v>
+        <v>3.2038877094922853</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390902</v>
+        <v>3.2327881859549339</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1173597688390902</v>
+        <v>3.2327881859549339</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.0885228428265115</v>
+        <v>3.2023269371078023</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.14379064377755</v>
+        <v>3.2599879167672925</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283843</v>
+        <v>3.3204520733848977</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2017620522283843</v>
+        <v>3.3204520733848977</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1198184630562369</v>
+        <v>3.2355730003899903</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2106497786949295</v>
+        <v>3.3310173488707346</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267449</v>
+        <v>3.4343317006865863</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3089502498267449</v>
+        <v>3.4343317006865863</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1508810662626585</v>
+        <v>3.2693383303057657</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2787685151405088</v>
+        <v>3.4050666906510809</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319889</v>
+        <v>3.5563050592125047</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4211490010319889</v>
+        <v>3.5563050592125047</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036379</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1790054598174224</v>
+        <v>3.300623506516013</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.3421227199442374</v>
+        <v>3.4755445735596653</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326914</v>
+        <v>3.6757062440939037</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.5284757783326914</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>3.6757062440939037</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036379</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.2031418941193395</v>
+        <v>3.3281006174758065</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.398009941669216</v>
+        <v>3.5391703250777344</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.625952362160219</v>
+        <v>3.7866862197260631</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.625952362160219</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>3.7866862197260631</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16761,7 +16750,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16776,14 +16765,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.3089502498267449</v>
+        <v>3.4343317006865863</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16798,7 +16787,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.2017620522283843</v>
+        <v>3.3204520733848977</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16806,7 +16795,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16821,7 +16810,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.14379064377755</v>
+        <v>3.2599879167672925</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16829,7 +16818,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16844,7 +16833,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0885228428265115</v>
+        <v>3.2023269371078023</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16852,7 +16841,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16867,21 +16856,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16889,23 +16878,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16939,16 +16928,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>445</v>
       </c>
@@ -16960,7 +16949,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>444</v>
       </c>
@@ -16973,7 +16962,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>442</v>
       </c>
@@ -16994,24 +16983,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>443</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>5762500</v>
+        <v>6146666.666666667</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17021,13 +17010,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>446</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17035,10 +17024,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17048,13 +17037,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17064,7 +17053,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17074,13 +17063,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>1.330700225807637</v>
+        <v>1.4175407151461414</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17088,10 +17077,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17109,7 +17098,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17123,15 +17112,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>435388.88888888882</v>
+        <v>437413.95348837209</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17145,15 +17134,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>411200.61728395062</v>
+        <v>415034.63493780425</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17167,15 +17156,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>388356.13854595326</v>
+        <v>393800.30477819568</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17189,15 +17178,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>366780.79751562251</v>
+        <v>373652.38220814842</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17211,15 +17200,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>346404.08654253243</v>
+        <v>354535.28358354548</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17233,15 +17222,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>327159.41506794718</v>
+        <v>336396.26907461998</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17255,15 +17244,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>308983.89200861688</v>
+        <v>319185.29716847668</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17277,15 +17266,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>291818.12023036031</v>
+        <v>302854.88661567081</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17299,15 +17288,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>275606.00243978476</v>
+        <v>287359.98543998535</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17321,15 +17310,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>260294.55785979662</v>
+        <v>272657.84665003262</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17351,7 +17340,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17373,7 +17362,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17395,7 +17384,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17417,7 +17406,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17439,7 +17428,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17461,7 +17450,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17483,7 +17472,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17505,7 +17494,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17527,7 +17516,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17549,7 +17538,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17571,7 +17560,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17593,7 +17582,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17615,7 +17604,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17637,7 +17626,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17659,7 +17648,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17681,7 +17670,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17703,7 +17692,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17725,7 +17714,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17747,7 +17736,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17769,13 +17758,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>5877750</v>
+        <v>6269600</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17783,30 +17772,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2722535.5245897528</v>
+        <v>3041971.8528788611</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>6134528.040973207</v>
+        <v>6534862.6968237124</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17816,10 +17805,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>6134528.040973207</v>
+        <v>6534862.6968237124</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17843,141 +17832,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>5762499.9999999991</v>
+        <v>6146666.666666667</v>
       </c>
       <c r="C51" s="124">
-        <v>5854783.1286184937</v>
+        <v>6243429.1378201917</v>
       </c>
       <c r="D51" s="124">
-        <v>5948428.4151420891</v>
+        <v>6341580.560378354</v>
       </c>
       <c r="E51" s="124">
-        <v>6043465.7040520106</v>
+        <v>6441151.4194949139</v>
       </c>
       <c r="F51" s="124">
-        <v>6043465.7040520106</v>
+        <v>6441151.4194949139</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>5762499.9999999981</v>
+        <v>6146666.6666666679</v>
       </c>
       <c r="C52" s="124">
-        <v>5944113.7954056608</v>
+        <v>6336203.2287136232</v>
       </c>
       <c r="D52" s="124">
-        <v>6134528.040973207</v>
+        <v>6534862.6968237124</v>
       </c>
       <c r="E52" s="124">
-        <v>6334257.0299089691</v>
+        <v>6743179.9551206185</v>
       </c>
       <c r="F52" s="124">
-        <v>6334257.0299089691</v>
+        <v>6743179.9551206185</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>5762499.9999999972</v>
+        <v>6146666.6666666679</v>
       </c>
       <c r="C53" s="124">
-        <v>6051936.6472844742</v>
+        <v>6450745.9452508166</v>
       </c>
       <c r="D53" s="124">
-        <v>6364877.9285301566</v>
+        <v>6779580.5161386179</v>
       </c>
       <c r="E53" s="124">
-        <v>6703552.7034878442</v>
+        <v>7135529.622468059</v>
       </c>
       <c r="F53" s="124">
-        <v>6703552.7034878442</v>
+        <v>7135529.622468059</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>5762499.9999999972</v>
+        <v>6146666.6666666679</v>
       </c>
       <c r="C54" s="124">
-        <v>6158956.6852294384</v>
+        <v>6567077.6919752341</v>
       </c>
       <c r="D54" s="124">
-        <v>6599567.5233050678</v>
+        <v>7034702.8352330457</v>
       </c>
       <c r="E54" s="124">
-        <v>7090111.2456540884</v>
+        <v>7555764.6353217121</v>
       </c>
       <c r="F54" s="124">
-        <v>7090111.2456540884</v>
+        <v>7555764.6353217121</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>5762499.9999999963</v>
+        <v>6146666.6666666688</v>
       </c>
       <c r="C55" s="124">
-        <v>6255853.7046263088</v>
+        <v>6674864.5610565552</v>
       </c>
       <c r="D55" s="124">
-        <v>6817841.8693736047</v>
+        <v>7277520.401199257</v>
       </c>
       <c r="E55" s="124">
-        <v>7459884.3681094954</v>
+        <v>7967137.7340850271</v>
       </c>
       <c r="F55" s="124">
-        <v>7459884.3681094954</v>
+        <v>7967137.7340850271</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>5762499.9999999963</v>
+        <v>6146666.6666666688</v>
       </c>
       <c r="C56" s="124">
-        <v>6339011.0014466001</v>
+        <v>6769531.4966637818</v>
       </c>
       <c r="D56" s="124">
-        <v>7010390.2063529529</v>
+        <v>7496730.3076095767</v>
       </c>
       <c r="E56" s="124">
-        <v>7795720.6027818955</v>
+        <v>8349497.2267636582</v>
       </c>
       <c r="F56" s="124">
-        <v>7795720.6027818955</v>
+        <v>8349497.2267636582</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17987,7 +17976,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -18010,193 +17999,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>1.3547175749999998</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.3547175749999996</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>1.3764125990720966</v>
+        <v>1.4677801616090429</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>1.398427855552691</v>
+        <v>1.4908547745636276</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4207703606401747</v>
+        <v>1.5142630856791246</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4207703606401747</v>
+        <v>1.5142630856791246</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999993</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>1.3974135230257703</v>
+        <v>1.4895906069778897</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4421783863664595</v>
+        <v>1.536293856069237</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4891330712338362</v>
+        <v>1.5852675742454856</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4891330712338362</v>
+        <v>1.5852675742454856</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999991</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>1.4227618115163303</v>
+        <v>1.516518681803257</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>1.4963317991339515</v>
+        <v>1.5938250544625694</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5759515249203895</v>
+        <v>1.6775058371350271</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5759515249203895</v>
+        <v>1.6775058371350271</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999991</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>1.4479213648840019</v>
+        <v>1.5438673432901144</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>1.5515054422942467</v>
+        <v>1.6538022673826525</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>1.6668283406842055</v>
+        <v>1.7762997213073819</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>1.6668283406842055</v>
+        <v>1.7762997213073819</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999989</v>
+        <v>1.4450320800000003</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>1.4707010777069185</v>
+        <v>1.5692071725133143</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>1.6028199920193102</v>
+        <v>1.7108867314404654</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>1.7537590387758266</v>
+        <v>1.8730102404877502</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>1.7537590387758266</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>1.8730102404877502</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>1.3547175749999989</v>
+        <v>1.4450320800000003</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>1.4902506918486869</v>
+        <v>1.5914626105069811</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>1.6480865631504069</v>
+        <v>1.762421223905223</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>1.83271144648646</v>
+        <v>1.9628998933640758</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>1.83271144648646</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>1.9628998933640758</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18213,7 +18202,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18228,14 +18217,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.5759515249203895</v>
+        <v>1.6775058371350271</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18250,7 +18239,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.4891330712338362</v>
+        <v>1.5852675742454856</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18258,7 +18247,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18273,7 +18262,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.4421783863664595</v>
+        <v>1.536293856069237</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18281,7 +18270,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18296,7 +18285,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.3974135230257703</v>
+        <v>1.4895906069778897</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18304,7 +18293,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18319,21 +18308,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.3547175749999991</v>
+        <v>1.4450320800000001</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18341,23 +18330,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18387,7 +18376,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18397,7 +18386,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18410,7 +18399,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18422,7 +18411,7 @@
         <v>-1.95</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18442,7 +18431,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18451,7 +18440,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18468,10 +18457,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>3.2471362100207655</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3.3635759761825348</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18496,7 +18485,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18518,7 +18507,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18540,7 +18529,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18551,7 +18540,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
@@ -18565,7 +18554,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18584,7 +18573,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18602,7 +18591,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18613,7 +18602,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18622,7 +18611,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18630,7 +18619,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18642,18 +18631,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18668,13 +18657,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.0358093755933999</v>
+        <v>3.1473138841036388</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18683,7 +18672,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18692,7 +18681,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18704,7 +18693,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18715,13 +18704,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.14379064377755</v>
+        <v>3.2599879167672925</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18730,7 +18719,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18741,7 +18730,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18750,7 +18739,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18762,7 +18751,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18773,13 +18762,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.0885228428265115</v>
+        <v>3.2023269371078023</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18788,7 +18777,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18799,7 +18788,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18808,7 +18797,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18820,7 +18809,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18831,13 +18820,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.2017620522283843</v>
+        <v>3.3204520733848977</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18846,7 +18835,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18858,20 +18847,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.1443313652775093</v>
+        <v>3.2605485521589155</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18880,12 +18869,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18895,12 +18884,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18909,7 +18898,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18921,7 +18910,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18932,13 +18921,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.0358093755933995</v>
+        <v>3.1473138841036383</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18947,7 +18936,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18958,7 +18947,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18967,7 +18956,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18979,7 +18968,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18990,13 +18979,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.3089502498267449</v>
+        <v>3.4343317006865863</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19005,7 +18994,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -19016,13 +19005,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.1471362100207654</v>
+        <v>3.2635759761825347</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19036,7 +19025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -19045,7 +19034,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19053,7 +19042,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19066,7 +19055,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19078,13 +19067,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.14379064377755</v>
+        <v>3.2599879167672925</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19094,7 +19083,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19102,7 +19091,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19112,7 +19101,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19124,7 +19113,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19134,7 +19123,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19147,10 +19136,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.43316896917239905</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.41771411417681625</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19159,12 +19148,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19174,7 +19163,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19187,49 +19176,49 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.15889212827988333</v>
+        <v>0.16572593193648588</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.1469155284332238</v>
+        <v>1.2764593852410968</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.3058076567131072</v>
+        <v>1.4421853171775827</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19240,18 +19229,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.58508066712991391</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.55809660087505186</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19264,24 +19253,24 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21725217049313983</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.23107791371828346</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19290,7 +19279,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19302,23 +19291,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.7442777766579685</v>
+        <v>1.8088136857770354</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.9493178590444622</v>
+        <v>2.0138537681635289</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19329,58 +19318,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.38060581781059921</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.38293032463145815</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.25770969872478805</v>
+        <v>0.26005257398719595</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.4982981903965071</v>
+        <v>2.6270499764257518</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.7560078891212951</v>
+        <v>2.8871025504129477</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19390,18 +19379,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.12428070944437752</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1153561089176649</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>423</v>
       </c>
@@ -19410,7 +19399,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19420,23 +19409,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>2.2557425867656002</v>
+        <v>2.3392019993222615</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>2.4970028993594653</v>
+        <v>2.5804623119161265</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19446,19 +19435,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.20573499246785421</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.20844420967210364</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19466,7 +19455,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19474,7 +19463,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A48A21A-A871-443A-AE7D-ED52FE8F397E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C159776-F9E9-4889-BA67-FF7A9DCAEA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3869,29 +3869,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4309,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8989.5</v>
+        <v>9127.7999999999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4357,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0843026500000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4367,13 +4367,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4449,14 +4449,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>3.2635759761825347</v>
+        <v>3.2651677227364719</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23107791371828346</v>
+        <v>0.22476237737510796</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>1.4421853171775827</v>
+        <v>1.442807885747313</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>2.0138537681635289</v>
+        <v>2.0147359823273976</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>2.8871025504129477</v>
+        <v>2.8883838436255198</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>2.5804623119161265</v>
+        <v>2.5816032128017068</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4573,22 +4573,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4600,13 +4600,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4626,13 +4626,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4661,13 +4661,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4753,13 +4753,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4775,7 +4775,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4797,22 +4797,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8618159083223565E-2</v>
+        <v>6.7611450117865554E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.1282051282051287E-2</v>
+        <v>5.0505050505050511E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4940,22 +4940,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7840721361638123</v>
+        <v>1.7849422831116506</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4992,13 +4992,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5011,13 +5011,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C97" s="245">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49818907182721034</v>
+        <v>0.49843205398668117</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C105" s="245">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8490697771281694</v>
+        <v>1.8499716254280749</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C109" s="245">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2361042638866811E-2</v>
+        <v>1.2367071500203906E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>1.8309265451850745</v>
+        <v>1.8318195444717706</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5193,13 +5193,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.43 HKD</v>
+        <v>3.44 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>3.2635759761825347</v>
+        <v>3.2651677227364719</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5342,13 +5342,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5361,22 +5361,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>1.2764593852410968</v>
+        <v>1.2770819538108271</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>1.4421853171775827</v>
+        <v>1.442807885747313</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55809660087505186</v>
+        <v>0.55812135600246449</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>1.8088136857770354</v>
+        <v>1.8096958999409041</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>2.0138537681635289</v>
+        <v>2.0147359823273976</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38293032463145815</v>
+        <v>0.38296095226652327</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>2.6270499764257518</v>
+        <v>2.6283312696383239</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>2.8871025504129477</v>
+        <v>2.8883838436255198</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1153561089176649</v>
+        <v>0.11539495398269373</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>2.3392019993222615</v>
+        <v>2.3403429002078417</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>2.5804623119161265</v>
+        <v>2.5816032128017068</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20844420967210364</v>
+        <v>0.20848028732861767</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5709,13 +5709,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5752,13 +5752,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5766,22 +5766,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5805,17 +5805,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5832,6 +5821,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6497,43 +6497,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.130919906448</v>
+        <v>0.13098376012000001</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22434123041999995</v>
+        <v>0.22445064855000002</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19291178267999998</v>
+        <v>0.19300587170000003</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16798497929999998</v>
+        <v>0.16806691075000002</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2407001400000013E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16256610899999999</v>
+        <v>0.16264539750000001</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4215132500000009E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4215132500000013E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7900,43 +7900,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.130919906448</v>
+        <v>0.13098376012000001</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22434123041999995</v>
+        <v>0.22445064855000002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19291178267999998</v>
+        <v>0.19300587170000003</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16798497929999998</v>
+        <v>0.16806691075000002</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2407001400000013E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16256610899999999</v>
+        <v>0.16264539750000001</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4215132500000009E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4215132500000013E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9254,11 +9254,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.32763841689688</v>
+        <v>4.3297491394867791</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8309265451850745</v>
+        <v>1.8318195444717706</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="C73" s="76">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965307.73072710668</v>
+        <v>-965332.26117943332</v>
       </c>
       <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="C74" s="280">
         <f>-$C$66/C73</f>
-        <v>12.111829862994474</v>
+        <v>12.111522084339404</v>
       </c>
       <c r="D74" s="280">
         <f>-$C$66/D73</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2296651.6211234396</v>
+        <v>-2297771.7688786001</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49818907182721034</v>
+        <v>-0.49843205398668117</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8524211.6725608613</v>
+        <v>8528369.1932234261</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8490697771281694</v>
+        <v>1.8499716254280749</v>
       </c>
       <c r="E87" s="262" t="str">
         <f>Market_currency</f>
@@ -9698,11 +9698,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>56984.406565175988</v>
+        <v>57012.199615940008</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2361042638866809E-2</v>
+        <v>1.2367071500203906E-2</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9715,11 +9715,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>6284544.458002598</v>
+        <v>6287609.6239607669</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
-        <v>1.3632417479398258</v>
+        <v>1.3639066429415978</v>
       </c>
       <c r="E89" s="262" t="str">
         <f>Market_currency</f>
@@ -13235,43 +13235,43 @@
       <c r="E90" s="293"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.130919906448</v>
+        <v>0.13098376012000001</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0.22434123041999995</v>
+        <v>0.22445064855000002</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>0.19291178267999998</v>
+        <v>0.19300587170000003</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>0.16798497929999998</v>
+        <v>0.16806691075000002</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="L90" s="113">
         <f>Data!H65</f>
-        <v>8.2366828559999994E-2</v>
+        <v>8.2407001400000013E-2</v>
       </c>
       <c r="M90" s="113">
         <f>Data!I65</f>
-        <v>0.16256610899999999</v>
+        <v>0.16264539750000001</v>
       </c>
       <c r="N90" s="113">
         <f>Data!J65</f>
-        <v>5.4188702999999998E-3</v>
+        <v>5.4215132500000009E-3</v>
       </c>
       <c r="O90" s="113">
         <f>Data!K65</f>
-        <v>5.4188702999999998E-2</v>
+        <v>5.4215132500000013E-2</v>
       </c>
       <c r="P90" s="113">
         <f>Data!L65</f>
-        <v>8.6701924799999996E-2</v>
+        <v>8.6744212000000015E-2</v>
       </c>
       <c r="Q90" s="113" t="str">
         <f>Data!M65</f>
@@ -13291,43 +13291,43 @@
       <c r="E91" s="293"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603540.76872528007</v>
+        <v>603835.13415320008</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034213.0722361997</v>
+        <v>1034717.4898155001</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889323.31815479998</v>
+        <v>889757.0685370001</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774410.75457299978</v>
+        <v>774788.45855750015</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800002</v>
+        <v>399890.81732000003</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379711.0796616</v>
+        <v>379896.27645400004</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749429.76248999988</v>
+        <v>749795.28247500001</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24980.992083000001</v>
+        <v>24993.176082500002</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249809.92082999999</v>
+        <v>249931.76082500003</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399695.87332800002</v>
+        <v>399890.81732000003</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13346,43 +13346,43 @@
       <c r="E92" s="293"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95421703263140079</v>
+        <v>0.95468243367751804</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.93269497678697</v>
+        <v>0.93314988086336026</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66190563508315692</v>
+        <v>0.66222846685461378</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.92130046033819613</v>
+        <v>0.9217498069578508</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.91714805388673326</v>
+        <v>0.91759537524982637</v>
       </c>
       <c r="L92" s="171">
         <f t="shared" si="38"/>
-        <v>1.1241605446900729</v>
+        <v>1.1247088324229588</v>
       </c>
       <c r="M92" s="171">
         <f t="shared" si="38"/>
-        <v>0.59260370943012186</v>
+        <v>0.59289274051725438</v>
       </c>
       <c r="N92" s="171">
         <f t="shared" si="38"/>
-        <v>6.3555970749640631E-2</v>
+        <v>6.3586968954726444E-2</v>
       </c>
       <c r="O92" s="171">
         <f t="shared" si="38"/>
-        <v>-0.60271554025101692</v>
+        <v>-0.60300950318958502</v>
       </c>
       <c r="P92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66343418012332667</v>
+        <v>0.6637577574132939</v>
       </c>
       <c r="Q92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13396,48 +13396,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.1282051282051287E-2</v>
+        <v>5.0505050505050511E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7138413563076926E-2</v>
+        <v>6.6153414202020214E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11504678483076922</v>
+        <v>0.11335891340909092</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8929119323076908E-2</v>
+        <v>9.7477712979797987E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6146143230769218E-2</v>
+        <v>8.4882278156565669E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461535E-2</v>
+        <v>4.3810208080808086E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2239399261538461E-2</v>
+        <v>4.1619697676767681E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3367235384615379E-2</v>
+        <v>8.2144140151515152E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538459E-3</v>
+        <v>2.7381380050505054E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7789078461538462E-2</v>
+        <v>2.7381380050505059E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4462525538461535E-2</v>
+        <v>4.3810208080808086E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14538,50 +14538,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13380541021228592</v>
+        <v>0.13387067123337382</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14869531112297604</v>
+        <v>0.14876783440749397</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.2606802997430655</v>
+        <v>0.26080744155677643</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.31586494336262128</v>
+        <v>0.31601900042725717</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19760954311055715</v>
+        <v>0.19770592337305656</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.10245379320394359</v>
+        <v>0.10250376307547723</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>7.9407725719822117E-2</v>
+        <v>7.9446455314197417E-2</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.29730649532849024</v>
+        <v>0.29745150086623651</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>9.2404080944316694E-2</v>
+        <v>9.2449149261550997E-2</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.743951621354445E-2</v>
+        <v>-9.7487040467700667E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>0.14163469393880693</v>
+        <v>0.14170377354278743</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14595,50 +14595,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8618159083223565E-2</v>
+        <v>6.7611450117865554E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.6254005704090286E-2</v>
+        <v>7.5135269902774734E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13368220499644384</v>
+        <v>0.13172093007918001</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16198202223724167</v>
+        <v>0.159605555771342</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10133822723618316</v>
+        <v>9.9851476451038673E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2540406771253122E-2</v>
+        <v>5.1769577310847088E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0721910625549806E-2</v>
+        <v>4.0124472380907786E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15246486939922577</v>
+        <v>0.15022803074052349</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.7386708176572666E-2</v>
+        <v>4.6691489526035856E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9968982673612543E-2</v>
+        <v>-4.9235879024091246E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.2633176378875355E-2</v>
+        <v>7.1567562395347187E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14652,43 +14652,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12805261694198788</v>
+        <v>0.12611242577620019</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.26409677957617222</v>
+        <v>0.26009531321895746</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20009255242227042</v>
+        <v>0.19706084708253907</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18259469380944435</v>
+        <v>0.17982810753960429</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6674119806440852E-2</v>
+        <v>8.5360875566949324E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3985538684020242E-2</v>
+        <v>8.2713030522141157E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1700083430669114</v>
+        <v>0.16743245908104909</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1959730797040992E-2</v>
+        <v>1.1778522754661583E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.6327381945603204E-2</v>
+        <v>-2.5928482219154669E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3780632960676347E-2</v>
+        <v>9.2359714279453969E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C11" s="229">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0843026500000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.2599879167672925</v>
+        <v>3.2615779133141047</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16553,23 +16553,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16580,23 +16580,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>3.1753992249840111</v>
+        <v>3.1769479650196741</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>3.2038877094922853</v>
+        <v>3.2054503442395696</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.2327881859549339</v>
+        <v>3.2343649163550086</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>3.2327881859549339</v>
+        <v>3.2343649163550086</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16607,23 +16607,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2023269371078023</v>
+        <v>3.2038888106183072</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>3.2599879167672925</v>
+        <v>3.2615779133141047</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>3.3204520733848977</v>
+        <v>3.3220715601637854</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>3.3204520733848977</v>
+        <v>3.3220715601637854</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16634,23 +16634,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>3.2355730003899903</v>
+        <v>3.2371510890298651</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>3.3310173488707346</v>
+        <v>3.3326419886599918</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>3.4343317006865863</v>
+        <v>3.4360067300683257</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>3.4343317006865863</v>
+        <v>3.4360067300683257</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16661,23 +16661,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>3.2693383303057657</v>
+        <v>3.270932887337346</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>3.4050666906510809</v>
+        <v>3.4067274465857746</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5563050592125047</v>
+        <v>3.5580395787591805</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>3.5563050592125047</v>
+        <v>3.5580395787591805</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16688,23 +16688,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>3.1473138841036379</v>
+        <v>3.148848926053248</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>3.300623506516013</v>
+        <v>3.3022333222919231</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>3.4755445735596653</v>
+        <v>3.4772397037292682</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>3.6757062440939037</v>
+        <v>3.6774989992771809</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>3.6757062440939037</v>
+        <v>3.6774989992771809</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16714,23 +16714,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>3.1473138841036379</v>
+        <v>3.148848926053248</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>3.3281006174758065</v>
+        <v>3.3297238346852982</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>3.5391703250777344</v>
+        <v>3.5408964874866538</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>3.7866862197260631</v>
+        <v>3.788533103262735</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>3.7866862197260631</v>
+        <v>3.788533103262735</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.4343317006865863</v>
+        <v>3.4360067300683257</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3204520733848977</v>
+        <v>3.3220715601637854</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.2599879167672925</v>
+        <v>3.2615779133141047</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.2023269371078023</v>
+        <v>3.2038888106183072</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18005,23 +18005,23 @@
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -18032,23 +18032,23 @@
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4677801616090429</v>
+        <v>1.4684960432159762</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>1.4908547745636276</v>
+        <v>1.4915819103702246</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>1.5142630856791246</v>
+        <v>1.5150016384402598</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>1.5142630856791246</v>
+        <v>1.5150016384402598</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -18059,23 +18059,23 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>1.4895906069778897</v>
+        <v>1.4903171262110062</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>1.536293856069237</v>
+        <v>1.5370431539158564</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>1.5852675742454856</v>
+        <v>1.5860407580833336</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>1.5852675742454856</v>
+        <v>1.5860407580833336</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18086,23 +18086,23 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>1.516518681803257</v>
+        <v>1.5172583346881163</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5938250544625694</v>
+        <v>1.594602412047174</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>1.6775058371350271</v>
+        <v>1.6783240084155353</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>1.6775058371350271</v>
+        <v>1.6783240084155353</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18113,23 +18113,23 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>1.5438673432901144</v>
+        <v>1.5446203349597898</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>1.6538022673826525</v>
+        <v>1.6546088777018884</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>1.7762997213073819</v>
+        <v>1.7771660774090277</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>1.7762997213073819</v>
+        <v>1.7771660774090277</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18140,23 +18140,23 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>1.4450320800000003</v>
+        <v>1.4457368666666672</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>1.5692071725133143</v>
+        <v>1.5699725231984187</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>1.7108867314404654</v>
+        <v>1.7117211836115873</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>1.8730102404877502</v>
+        <v>1.8739237652892389</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>1.8730102404877502</v>
+        <v>1.8739237652892389</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18166,23 +18166,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>1.4450320800000003</v>
+        <v>1.4457368666666672</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>1.5914626105069811</v>
+        <v>1.5922388158548819</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>1.762421223905223</v>
+        <v>1.7632808110360911</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>1.9628998933640758</v>
+        <v>1.9638572601187607</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>1.9628998933640758</v>
+        <v>1.9638572601187607</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.6775058371350271</v>
+        <v>1.6783240084155353</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.5852675742454856</v>
+        <v>1.5860407580833336</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.536293856069237</v>
+        <v>1.5370431539158564</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.4895906069778897</v>
+        <v>1.4903171262110062</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.4450320800000001</v>
+        <v>1.445736866666667</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-1.95</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>3.3635759761825348</v>
+        <v>3.365167722736472</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1473138841036388</v>
+        <v>3.1488489260532488</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.2599879167672925</v>
+        <v>3.2615779133141047</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.2023269371078023</v>
+        <v>3.2038888106183072</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.3204520733848977</v>
+        <v>3.3220715601637854</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.2605485521589155</v>
+        <v>3.2621388221448817</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.1473138841036383</v>
+        <v>3.1488489260532484</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.4343317006865863</v>
+        <v>3.4360067300683257</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.2635759761825347</v>
+        <v>3.2651677227364719</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.2599879167672925</v>
+        <v>3.2615779133141047</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19208,7 +19208,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2764593852410968</v>
+        <v>1.2770819538108271</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>1.4421853171775827</v>
+        <v>1.442807885747313</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.55809660087505186</v>
+        <v>0.55812135600246449</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23107791371828346</v>
+        <v>0.22476237737510796</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8088136857770354</v>
+        <v>1.8096958999409041</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>2.0138537681635289</v>
+        <v>2.0147359823273976</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.38293032463145815</v>
+        <v>0.38296095226652327</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>2.6270499764257518</v>
+        <v>2.6283312696383239</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>2.8871025504129477</v>
+        <v>2.8883838436255198</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.1153561089176649</v>
+        <v>0.11539495398269373</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>2.3392019993222615</v>
+        <v>2.3403429002078417</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>2.5804623119161265</v>
+        <v>2.5816032128017068</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19435,7 +19435,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.20844420967210364</v>
+        <v>0.20848028732861767</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886B5BD4-3A02-4695-AAE2-E9782B6742E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05185DA0-A252-422F-8CBF-108C638D520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9127.7999999999993</v>
+        <v>9312.2000000000007</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0843026499999999</v>
+        <v>1.0877953499999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="C26" s="307">
         <f>C127</f>
-        <v>3.2651677227364715</v>
+        <v>3.2756853132866759</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22476237737510796</v>
+        <v>0.21751806401088669</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C29" s="313">
         <f>C144</f>
-        <v>1.4428078857473128</v>
+        <v>1.4469215565384661</v>
       </c>
       <c r="D29" s="313" t="str">
         <f>D144</f>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C30" s="314">
         <f>C152</f>
-        <v>2.0147359823273976</v>
+        <v>2.020565281803631</v>
       </c>
       <c r="D30" s="314" t="str">
         <f>D152</f>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C31" s="314">
         <f>C160</f>
-        <v>2.8883838436255198</v>
+        <v>2.8968500893046811</v>
       </c>
       <c r="D31" s="314" t="str">
         <f>D160</f>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C32" s="314">
         <f>C168</f>
-        <v>2.5816032128017063</v>
+        <v>2.5891418051380395</v>
       </c>
       <c r="D32" s="314" t="str">
         <f>D168</f>
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.761145011786554E-2</v>
+        <v>6.6486083447110586E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0505050505050511E-2</v>
+        <v>4.9504950495049507E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C87" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7849422831116502</v>
+        <v>1.7906918475088454</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C97" s="223">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49843205398668106</v>
+        <v>0.50003757771657265</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C105" s="223">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8499716254280745</v>
+        <v>1.8559306590024485</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="C109" s="223">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2367071500203905E-2</v>
+        <v>1.2406907675674619E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C113" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C114" s="223">
         <f>BS!D47</f>
-        <v>1.8318195444717704</v>
+        <v>1.8377201074953657</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="E121" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.44 HKD</v>
+        <v>3.45 HKD</v>
       </c>
       <c r="F121" s="232">
         <f>DCF!F74</f>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="E122" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>3.32 HKD</v>
+        <v>3.33 HKD</v>
       </c>
       <c r="F122" s="221">
         <f>DCF!F75</f>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E123" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>3.26 HKD</v>
+        <v>3.27 HKD</v>
       </c>
       <c r="F123" s="221">
         <f>DCF!F76</f>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="E124" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>3.2 HKD</v>
+        <v>3.21 HKD</v>
       </c>
       <c r="F124" s="221">
         <f>DCF!F77</f>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E125" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>3.15 HKD</v>
+        <v>3.16 HKD</v>
       </c>
       <c r="F125" s="221">
         <f>DCF!F78</f>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C127" s="217">
         <f>Scenarios!C60</f>
-        <v>3.2651677227364715</v>
+        <v>3.2756853132866759</v>
       </c>
       <c r="D127" s="212" t="str">
         <f>Market_currency</f>
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C143" s="216">
         <f>Scenarios!C82</f>
-        <v>1.2770819538108269</v>
+        <v>1.2811956246019802</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C144" s="215">
         <f>Scenarios!C83</f>
-        <v>1.4428078857473128</v>
+        <v>1.4469215565384661</v>
       </c>
       <c r="D144" s="303" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55812135600246449</v>
+        <v>0.55828432277376183</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="C151" s="216">
         <f>Scenarios!C92</f>
-        <v>1.8096958999409039</v>
+        <v>1.8155251994171373</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C152" s="215">
         <f>Scenarios!C93</f>
-        <v>2.0147359823273976</v>
+        <v>2.020565281803631</v>
       </c>
       <c r="D152" s="303" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38296095226652316</v>
+        <v>0.38316257864944714</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C159" s="216">
         <f>Scenarios!C98</f>
-        <v>2.6283312696383239</v>
+        <v>2.6367975153174852</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C160" s="215">
         <f>Scenarios!C99</f>
-        <v>2.8883838436255198</v>
+        <v>2.8968500893046811</v>
       </c>
       <c r="D160" s="303" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11539495398269362</v>
+        <v>0.11565067695769848</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C167" s="216">
         <f>Scenarios!C104</f>
-        <v>2.3403429002078413</v>
+        <v>2.3478814925441744</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C168" s="215">
         <f>Scenarios!C105</f>
-        <v>2.5816032128017063</v>
+        <v>2.5891418051380395</v>
       </c>
       <c r="D168" s="303" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20848028732861767</v>
+        <v>0.20871779203219298</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,6 +5804,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5820,17 +5831,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6499,43 +6499,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13098376011999999</v>
+        <v>0.13140567827999999</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22445064854999996</v>
+        <v>0.22517363744999996</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19300587169999997</v>
+        <v>0.19362757229999997</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16806691074999999</v>
+        <v>0.16860827924999999</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2407001399999999E-2</v>
+        <v>8.2672446599999991E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16264539749999998</v>
+        <v>0.16316930249999997</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4215132500000001E-3</v>
+        <v>5.4389767499999995E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4215132499999999E-2</v>
+        <v>5.4389767499999998E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7902,43 +7902,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13098376011999999</v>
+        <v>0.13140567827999999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22445064854999996</v>
+        <v>0.22517363744999996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19300587169999997</v>
+        <v>0.19362757229999997</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16806691074999999</v>
+        <v>0.16860827924999999</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2407001399999999E-2</v>
+        <v>8.2672446599999991E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16264539749999998</v>
+        <v>0.16316930249999997</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4215132500000001E-3</v>
+        <v>5.4389767499999995E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4215132499999999E-2</v>
+        <v>5.4389767499999998E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9256,11 +9256,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3297491394867782</v>
+        <v>4.3436959050134378</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8318195444717704</v>
+        <v>1.8377201074953657</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="C73" s="76">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965332.26117943332</v>
+        <v>-965494.34807256667</v>
       </c>
       <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>12.111522084339404</v>
+        <v>12.109488805750372</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
@@ -9666,11 +9666,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2297771.7688785996</v>
+        <v>-2305173.2332734</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49843205398668106</v>
+        <v>-0.50003757771657265</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9683,11 +9683,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8528369.1932234243</v>
+        <v>8555840.3380012885</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8499716254280747</v>
+        <v>1.8559306590024487</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9700,11 +9700,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>57012.199615939993</v>
+        <v>57195.844384859993</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2367071500203903E-2</v>
+        <v>1.2406907675674619E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9717,11 +9717,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>6287609.6239607651</v>
+        <v>6307862.9491127487</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>1.3639066429415976</v>
+        <v>1.3682999889615506</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13237,43 +13237,43 @@
       <c r="E90" s="270"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.13098376011999999</v>
+        <v>0.13140567827999999</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.22445064854999996</v>
+        <v>0.22517363744999996</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.19300587169999997</v>
+        <v>0.19362757229999997</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.16806691074999999</v>
+        <v>0.16860827924999999</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="L90" s="112">
         <f>Data!H65</f>
-        <v>8.2407001399999999E-2</v>
+        <v>8.2672446599999991E-2</v>
       </c>
       <c r="M90" s="112">
         <f>Data!I65</f>
-        <v>0.16264539749999998</v>
+        <v>0.16316930249999997</v>
       </c>
       <c r="N90" s="112">
         <f>Data!J65</f>
-        <v>5.4215132500000001E-3</v>
+        <v>5.4389767499999995E-3</v>
       </c>
       <c r="O90" s="112">
         <f>Data!K65</f>
-        <v>5.4215132499999999E-2</v>
+        <v>5.4389767499999998E-2</v>
       </c>
       <c r="P90" s="112">
         <f>Data!L65</f>
-        <v>8.6744212000000001E-2</v>
+        <v>8.7023627999999992E-2</v>
       </c>
       <c r="Q90" s="112" t="str">
         <f>Data!M65</f>
@@ -13293,43 +13293,43 @@
       <c r="E91" s="270"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>603835.13415319996</v>
+        <v>605780.17687079997</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1034717.4898154997</v>
+        <v>1038050.4686444998</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>889757.06853699987</v>
+        <v>892623.10830299987</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>774788.45855750004</v>
+        <v>777284.16734249995</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>399890.81731999997</v>
+        <v>401178.92507999996</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>379896.27645399998</v>
+        <v>381119.97882599995</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>749795.2824749999</v>
+        <v>752210.48452499986</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>24993.176082499998</v>
+        <v>25073.682817499997</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>249931.76082499998</v>
+        <v>250736.82817499997</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>399890.81731999997</v>
+        <v>401178.92507999996</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13348,43 +13348,43 @@
       <c r="E92" s="270"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95468243367751782</v>
+        <v>0.95775760769475871</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.93314988086336004</v>
+        <v>0.93615569532751497</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66222846685461356</v>
+        <v>0.66436160317608539</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92174980695785069</v>
+        <v>0.92471890008951618</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
-        <v>0.91759537524982626</v>
+        <v>0.9205510863394698</v>
       </c>
       <c r="L92" s="170">
         <f t="shared" si="38"/>
-        <v>1.1247088324229586</v>
+        <v>1.1283316867422795</v>
       </c>
       <c r="M92" s="170">
         <f t="shared" si="38"/>
-        <v>0.59289274051725427</v>
+        <v>0.59480253615853995</v>
       </c>
       <c r="N92" s="170">
         <f t="shared" si="38"/>
-        <v>6.3586968954726431E-2</v>
+        <v>6.3791792032921596E-2</v>
       </c>
       <c r="O92" s="170">
         <f t="shared" si="38"/>
-        <v>-0.60300950318958491</v>
+        <v>-0.60495188642713416</v>
       </c>
       <c r="P92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66375775741329379</v>
+        <v>0.66589581980695967</v>
       </c>
       <c r="Q92" s="170" t="str">
         <f t="shared" si="38"/>
@@ -13398,48 +13398,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0505050505050511E-2</v>
+        <v>4.9504950495049507E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.61534142020202E-2</v>
+        <v>6.5052315980198019E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11335891340909089</v>
+        <v>0.11147209774752473</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.7477712979797959E-2</v>
+        <v>9.5855233811881171E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4882278156565655E-2</v>
+        <v>8.346944517326732E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3810208080808079E-2</v>
+        <v>4.3081003960396033E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1619697676767674E-2</v>
+        <v>4.0926953762376234E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2144140151515138E-2</v>
+        <v>8.0776882425742561E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7381380050505049E-3</v>
+        <v>2.6925627475247521E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7381380050505052E-2</v>
+        <v>2.6925627475247522E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3810208080808079E-2</v>
+        <v>4.3081003960396033E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14540,50 +14540,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13387067123337379</v>
+        <v>0.13430188856316339</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="267"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14876783440749394</v>
+        <v>0.14924703771409387</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.26080744155677638</v>
+        <v>0.26164754109091043</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>0.31601900042725711</v>
+        <v>0.31703694459883347</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.19770592337305654</v>
+        <v>0.19834276353808339</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.10250376307547722</v>
+        <v>0.10283394293189804</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>7.9446455314197389E-2</v>
+        <v>7.970236415521692E-2</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.29745150086623645</v>
+        <v>0.2984096363619631</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>9.244914926155097E-2</v>
+        <v>9.2746941712418651E-2</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>-9.7487040467700639E-2</v>
+        <v>-9.7801060714945764E-2</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>0.1417037735427874</v>
+        <v>0.14216022245938176</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14597,50 +14597,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.761145011786554E-2</v>
+        <v>6.6486083447110586E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.5135269902774721E-2</v>
+        <v>7.3884672135690027E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13172093007917998</v>
+        <v>0.12952848568856951</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15960555577134197</v>
+        <v>0.15694898247467004</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.9851476451038659E-2</v>
+        <v>9.8189486900041284E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.1769577310847081E-2</v>
+        <v>5.0907892540543585E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0124472380907772E-2</v>
+        <v>3.9456615918424219E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15022803074052346</v>
+        <v>0.14772754275344707</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.6691489526035843E-2</v>
+        <v>4.591432758040527E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9235879024091232E-2</v>
+        <v>-4.841636669056721E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.1567562395347173E-2</v>
+        <v>7.037634775216918E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14654,43 +14654,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12611242577620019</v>
+        <v>0.12361515001825563</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.26009531321895746</v>
+        <v>0.2549449109769979</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19706084708253907</v>
+        <v>0.1931586520908056</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17982810753960429</v>
+        <v>0.17626715491505768</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5360875566949324E-2</v>
+        <v>8.3670561199286952E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2713030522141157E-2</v>
+        <v>8.10751487296235E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16743245908104909</v>
+        <v>0.1641169648418204</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1778522754661583E-2</v>
+        <v>1.154528468031185E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.5928482219154669E-2</v>
+        <v>-2.5415046927686261E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2359714279453969E-2</v>
+        <v>9.0530809046197466E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0843026499999999</v>
+        <v>1.0877953499999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.2615779133141038</v>
+        <v>3.272083940554591</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16555,23 +16555,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16582,23 +16582,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.1769479650196737</v>
+        <v>3.1871813866178078</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2054503442395692</v>
+        <v>3.2157755762375961</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2343649163550081</v>
+        <v>3.2447832864875106</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2343649163550081</v>
+        <v>3.2447832864875106</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16609,23 +16609,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2038888106183068</v>
+        <v>3.2142090126844427</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2615779133141043</v>
+        <v>3.272083940554591</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3220715601637849</v>
+        <v>3.3327724464321937</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3220715601637849</v>
+        <v>3.3327724464321937</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16636,23 +16636,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>3.2371510890298643</v>
+        <v>3.2475784338386728</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>3.332641988659991</v>
+        <v>3.343376923849712</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4360067300683248</v>
+        <v>3.4470746184536476</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4360067300683248</v>
+        <v>3.4470746184536476</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16663,23 +16663,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>3.2709328873373451</v>
+        <v>3.2814690483396292</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>3.4067274465857738</v>
+        <v>3.4177010220470994</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5580395787591796</v>
+        <v>3.5695005530883783</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5580395787591796</v>
+        <v>3.5695005530883783</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16690,23 +16690,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>3.1488489260532471</v>
+        <v>3.1589918364703951</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>3.3022333222919227</v>
+        <v>3.3128703066475071</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>3.4772397037292673</v>
+        <v>3.4884404096513779</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6774989992771805</v>
+        <v>3.6893447701556115</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6774989992771805</v>
+        <v>3.6893447701556115</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16716,23 +16716,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>3.1488489260532471</v>
+        <v>3.1589918364703951</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>3.3297238346852973</v>
+        <v>3.3404493700673288</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>3.5408964874866529</v>
+        <v>3.552302241370815</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7885331032627345</v>
+        <v>3.8007365314935568</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7885331032627345</v>
+        <v>3.8007365314935568</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.4360067300683248</v>
+        <v>3.4470746184536476</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3220715601637849</v>
+        <v>3.3327724464321937</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.2615779133141043</v>
+        <v>3.272083940554591</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.2038888106183068</v>
+        <v>3.2142090126844427</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18007,23 +18007,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18034,23 +18034,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4684960432159757</v>
+        <v>1.4732262872397643</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4915819103702241</v>
+        <v>1.4963865174034636</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5150016384402594</v>
+        <v>1.5198816838985827</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5150016384402594</v>
+        <v>1.5198816838985827</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18061,23 +18061,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>1.490317126211006</v>
+        <v>1.4951176591864783</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5370431539158562</v>
+        <v>1.5419941983716472</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5860407580833333</v>
+        <v>1.5911496311048625</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5860407580833333</v>
+        <v>1.5911496311048625</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18088,23 +18088,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5172583346881161</v>
+        <v>1.5221456493004755</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5946024120471738</v>
+        <v>1.5997388634286742</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6783240084155349</v>
+        <v>1.6837301395028221</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6783240084155349</v>
+        <v>1.6837301395028221</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18115,23 +18115,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>1.5446203349597893</v>
+        <v>1.5495957866419503</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>1.6546088777018881</v>
+        <v>1.6599386188282697</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7771660774090272</v>
+        <v>1.7828905934918446</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7771660774090272</v>
+        <v>1.7828905934918446</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18142,23 +18142,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>1.445736866666667</v>
+        <v>1.4503938000000003</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>1.5699725231984183</v>
+        <v>1.5750296380470956</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>1.7117211836115871</v>
+        <v>1.7172348919641398</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>1.8739237652892384</v>
+        <v>1.87995995226621</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>1.8739237652892384</v>
+        <v>1.87995995226621</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18168,23 +18168,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>1.445736866666667</v>
+        <v>1.4503938000000003</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>1.5922388158548817</v>
+        <v>1.5973676537417358</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>1.7632808110360907</v>
+        <v>1.7689606006120968</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9638572601187603</v>
+        <v>1.9701831362497619</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9638572601187603</v>
+        <v>1.9701831362497619</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.6783240084155349</v>
+        <v>1.6837301395028221</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18241,7 +18241,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.5860407580833333</v>
+        <v>1.5911496311048625</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.5370431539158562</v>
+        <v>1.5419941983716472</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.490317126211006</v>
+        <v>1.4951176591864783</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.4457368666666668</v>
+        <v>1.4503938000000001</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.98</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>3.3651677227364716</v>
+        <v>3.375685313286676</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.148848926053248</v>
+        <v>3.1589918364703964</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.2615779133141043</v>
+        <v>3.272083940554591</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.2038888106183068</v>
+        <v>3.2142090126844427</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.3220715601637849</v>
+        <v>3.3327724464321937</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.2621388221448813</v>
+        <v>3.2726466561560823</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.1488489260532475</v>
+        <v>3.1589918364703959</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.4360067300683248</v>
+        <v>3.4470746184536476</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.2651677227364715</v>
+        <v>3.2756853132866759</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.2615779133141038</v>
+        <v>3.272083940554591</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2770819538108269</v>
+        <v>1.2811956246019802</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19220,7 +19220,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>1.4428078857473128</v>
+        <v>1.4469215565384661</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="F83" s="293">
         <f>(1-C83/C60)</f>
-        <v>0.55812135600246449</v>
+        <v>0.55828432277376183</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22476237737510796</v>
+        <v>0.21751806401088669</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8096958999409039</v>
+        <v>1.8155251994171373</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>2.0147359823273976</v>
+        <v>2.020565281803631</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19320,7 +19320,7 @@
       </c>
       <c r="F93" s="293">
         <f>(1-C93/C60)</f>
-        <v>0.38296095226652316</v>
+        <v>0.38316257864944714</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>2.6283312696383239</v>
+        <v>2.6367975153174852</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>2.8883838436255198</v>
+        <v>2.8968500893046811</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="F99" s="293">
         <f>(1-C99/C60)</f>
-        <v>0.11539495398269362</v>
+        <v>0.11565067695769848</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>2.3403429002078413</v>
+        <v>2.3478814925441744</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>2.5816032128017063</v>
+        <v>2.5891418051380395</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19437,7 +19437,7 @@
       </c>
       <c r="F105" s="293">
         <f>(1-C105/C66)</f>
-        <v>0.20848028732861767</v>
+        <v>0.20871779203219298</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A06EE2-B18F-4D14-8DA9-21F04F9DFED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC6E67C-230E-403A-B6A2-5FF9AC4CDA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9312.2000000000007</v>
+        <v>9266.0999999999985</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4370,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0877953499999999</v>
+        <v>1.0859573200000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4462,14 +4462,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>3.2756853132866759</v>
+        <v>3.2701504414227913</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21751806401088669</v>
+        <v>0.21897211796497307</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>1.4469215565384661</v>
+        <v>1.4447567412596667</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>2.020565281803631</v>
+        <v>2.0174976185871221</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>2.8968500893046811</v>
+        <v>2.8923947356969659</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>2.5891418051380395</v>
+        <v>2.585174628205595</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6486083447110586E-2</v>
+        <v>6.6703960626889283E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.9504950495049507E-2</v>
+        <v>4.9751243781094537E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7906918475088454</v>
+        <v>1.7876661448006324</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.50003757771657265</v>
+        <v>0.49919267240513671</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8559306590024485</v>
+        <v>1.8527947233421556</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2406907675674619E-2</v>
+        <v>1.23859439268269E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>1.8377201074953657</v>
+        <v>1.8346149419059199</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.45 HKD</v>
+        <v>3.44 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>3.16 HKD</v>
+        <v>3.15 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>3.2756853132866759</v>
+        <v>3.2701504414227913</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.2811956246019802</v>
+        <v>1.2790308093231808</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>1.4469215565384661</v>
+        <v>1.4447567412596667</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55828432277376183</v>
+        <v>0.55819869234178854</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>1.8155251994171373</v>
+        <v>1.8124575362006285</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>2.020565281803631</v>
+        <v>2.0174976185871221</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38316257864944714</v>
+        <v>0.38305663463319428</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>2.6367975153174852</v>
+        <v>2.63234216170977</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>2.8968500893046811</v>
+        <v>2.8923947356969659</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11565067695769848</v>
+        <v>0.11551630803917079</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>2.3478814925441744</v>
+        <v>2.3439143156117299</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>2.5891418051380395</v>
+        <v>2.585174628205595</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20871779203219298</v>
+        <v>0.20859299585318691</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6570,43 +6570,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13140567827999999</v>
+        <v>0.13118364425600001</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22517363744999996</v>
+        <v>0.22479316524000001</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19362757229999997</v>
+        <v>0.19330040296000001</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16860827924999999</v>
+        <v>0.16832338460000001</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2672446599999991E-2</v>
+        <v>8.2532756320000011E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16316930249999997</v>
+        <v>0.162893598</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4389767499999995E-3</v>
+        <v>5.4297866000000009E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4389767499999998E-2</v>
+        <v>5.4297866000000007E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7973,43 +7973,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13140567827999999</v>
+        <v>0.13118364425600001</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22517363744999996</v>
+        <v>0.22479316524000001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19362757229999997</v>
+        <v>0.19330040296000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16860827924999999</v>
+        <v>0.16832338460000001</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2672446599999991E-2</v>
+        <v>8.2532756320000011E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16316930249999997</v>
+        <v>0.162893598</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4389767499999995E-3</v>
+        <v>5.4297866000000009E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4389767499999998E-2</v>
+        <v>5.4297866000000007E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9327,11 +9327,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3436959050134378</v>
+        <v>4.3363564331318099</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8377201074953657</v>
+        <v>1.8346149419059199</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C73" s="76">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965494.34807256667</v>
+        <v>-965409.05000168004</v>
       </c>
       <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>12.109488805750372</v>
+        <v>12.110558731534217</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
@@ -9737,11 +9737,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2305173.2332734</v>
+        <v>-2301278.2197876801</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.50003757771657265</v>
+        <v>-0.49919267240513671</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9754,11 +9754,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8555840.3380012885</v>
+        <v>8541383.6746073365</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8559306590024487</v>
+        <v>1.8527947233421553</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9771,11 +9771,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>57195.844384859993</v>
+        <v>57099.201502672004</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2406907675674619E-2</v>
+        <v>1.2385943926826898E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>6307862.9491127487</v>
+        <v>6297204.6563223293</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>1.3682999889615506</v>
+        <v>1.3659879948638454</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13308,43 +13308,43 @@
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.13140567827999999</v>
+        <v>0.13118364425600001</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.22517363744999996</v>
+        <v>0.22479316524000001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.19362757229999997</v>
+        <v>0.19330040296000001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.16860827924999999</v>
+        <v>0.16832338460000001</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="L90" s="112">
         <f>Data!H65</f>
-        <v>8.2672446599999991E-2</v>
+        <v>8.2532756320000011E-2</v>
       </c>
       <c r="M90" s="112">
         <f>Data!I65</f>
-        <v>0.16316930249999997</v>
+        <v>0.162893598</v>
       </c>
       <c r="N90" s="112">
         <f>Data!J65</f>
-        <v>5.4389767499999995E-3</v>
+        <v>5.4297866000000009E-3</v>
       </c>
       <c r="O90" s="112">
         <f>Data!K65</f>
-        <v>5.4389767499999998E-2</v>
+        <v>5.4297866000000007E-2</v>
       </c>
       <c r="P90" s="112">
         <f>Data!L65</f>
-        <v>8.7023627999999992E-2</v>
+        <v>8.6876585600000014E-2</v>
       </c>
       <c r="Q90" s="112" t="str">
         <f>Data!M65</f>
@@ -13364,43 +13364,43 @@
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>605780.17687079997</v>
+        <v>604756.60002016008</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1038050.4686444998</v>
+        <v>1036296.4917564</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>892623.10830299987</v>
+        <v>891114.8576456001</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>777284.16734249995</v>
+        <v>775970.803006</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>401178.92507999996</v>
+        <v>400501.05961600004</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>381119.97882599995</v>
+        <v>380476.0066352</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>752210.48452499986</v>
+        <v>750939.48677999992</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>25073.682817499997</v>
+        <v>25031.316226000003</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>250736.82817499997</v>
+        <v>250313.16226000001</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>401178.92507999996</v>
+        <v>400501.05961600004</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13419,43 +13419,43 @@
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95775760769475871</v>
+        <v>0.95613930033973005</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.93615569532751497</v>
+        <v>0.93457388837027555</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66436160317608539</v>
+        <v>0.66323904224816299</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92471890008951618</v>
+        <v>0.92315641769801537</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
-        <v>0.9205510863394698</v>
+        <v>0.91899564623465213</v>
       </c>
       <c r="L92" s="170">
         <f t="shared" si="38"/>
-        <v>1.1283316867422795</v>
+        <v>1.1264251631575053</v>
       </c>
       <c r="M92" s="170">
         <f t="shared" si="38"/>
-        <v>0.59480253615853995</v>
+        <v>0.59379750804775111</v>
       </c>
       <c r="N92" s="170">
         <f t="shared" si="38"/>
-        <v>6.3791792032921596E-2</v>
+        <v>6.3684004085942172E-2</v>
       </c>
       <c r="O92" s="170">
         <f t="shared" si="38"/>
-        <v>-0.60495188642713416</v>
+        <v>-0.60392970912530108</v>
       </c>
       <c r="P92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66589581980695967</v>
+        <v>0.6647706665383053</v>
       </c>
       <c r="Q92" s="170" t="str">
         <f t="shared" si="38"/>
@@ -13469,48 +13469,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.9504950495049507E-2</v>
+        <v>4.9751243781094537E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5052315980198019E-2</v>
+        <v>6.5265494654726378E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11147209774752473</v>
+        <v>0.11183739564179106</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.5855233811881171E-2</v>
+        <v>9.6169354706467675E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.346944517326732E-2</v>
+        <v>8.3742977412935335E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3081003960396033E-2</v>
+        <v>4.3222181890547273E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.0926953762376234E-2</v>
+        <v>4.1061072796019914E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.0776882425742561E-2</v>
+        <v>8.1041591044776123E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6925627475247521E-3</v>
+        <v>2.7013863681592046E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6925627475247522E-2</v>
+        <v>2.7013863681592046E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3081003960396033E-2</v>
+        <v>4.3222181890547273E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14611,50 +14611,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13430188856316339</v>
+        <v>0.13407496086004744</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14924703771409387</v>
+        <v>0.1489948574370504</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.26164754109091043</v>
+        <v>0.26120543952286157</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>0.31703694459883347</v>
+        <v>0.31650125246218208</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.19834276353808339</v>
+        <v>0.19800762701661742</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.10283394293189804</v>
+        <v>0.10266018610150977</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>7.970236415521692E-2</v>
+        <v>7.9567692374915414E-2</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.2984096363619631</v>
+        <v>0.29790541848318441</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>9.2746941712418651E-2</v>
+        <v>9.2590228722906745E-2</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>-9.7801060714945764E-2</v>
+        <v>-9.7635807863271154E-2</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>0.14216022245938176</v>
+        <v>0.14192001665809112</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14668,50 +14668,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6486083447110586E-2</v>
+        <v>6.6703960626889283E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.3884672135690027E-2</v>
+        <v>7.4126794744801203E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12952848568856951</v>
+        <v>0.12995295498649831</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15694898247467004</v>
+        <v>0.15746330968267766</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8189486900041284E-2</v>
+        <v>9.8511257222197737E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.0907892540543585E-2</v>
+        <v>5.1074719453487454E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9456615918424219E-2</v>
+        <v>3.9585916604435535E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.14772754275344707</v>
+        <v>0.14821165098665892</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.591432758040527E-2</v>
+        <v>4.6064790409406343E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.841636669056721E-2</v>
+        <v>-4.8575028787697094E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.037634775216918E-2</v>
+        <v>7.0606973461736888E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14725,43 +14725,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12361515001825563</v>
+        <v>0.12423015076461513</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2549449109769979</v>
+        <v>0.25621329361867456</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1931586520908056</v>
+        <v>0.19411964040966537</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17626715491505768</v>
+        <v>0.17714410593453561</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3670561199286952E-2</v>
+        <v>8.408683264803965E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.10751487296235E-2</v>
+        <v>8.1478507678527115E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1641169648418204</v>
+        <v>0.1649334671544663</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.154528468031185E-2</v>
+        <v>1.1602723907577085E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.5415046927686261E-2</v>
+        <v>-2.5541489947226995E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0530809046197466E-2</v>
+        <v>9.0981211081253191E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0877953499999999</v>
+        <v>1.0859573200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.272083940554591</v>
+        <v>3.2665551538712716</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16626,23 +16626,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16653,23 +16653,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.1871813866178078</v>
+        <v>3.1817960583903573</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2157755762375961</v>
+        <v>3.2103419328759184</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2447832864875106</v>
+        <v>3.2393006292725648</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2447832864875106</v>
+        <v>3.2393006292725648</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16680,23 +16680,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2142090126844427</v>
+        <v>3.2087780163195623</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>3.272083940554591</v>
+        <v>3.2665551538712716</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3327724464321937</v>
+        <v>3.3271411153737227</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3327724464321937</v>
+        <v>3.3271411153737227</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16707,23 +16707,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>3.2475784338386728</v>
+        <v>3.2420910537089931</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>3.343376923849712</v>
+        <v>3.3377276745793019</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4470746184536476</v>
+        <v>3.4412501528857851</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4470746184536476</v>
+        <v>3.4412501528857851</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16734,23 +16734,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>3.2814690483396292</v>
+        <v>3.2759244037932822</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>3.4177010220470994</v>
+        <v>3.4119261885643559</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5695005530883783</v>
+        <v>3.5634692264223906</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5695005530883783</v>
+        <v>3.5634692264223906</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16761,23 +16761,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>3.1589918364703951</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>3.3128703066475071</v>
+        <v>3.3072726039089115</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>3.4884404096513779</v>
+        <v>3.4825460489831226</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6893447701556115</v>
+        <v>3.6831109446774195</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6893447701556115</v>
+        <v>3.6831109446774195</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16787,23 +16787,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>3.1589918364703951</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>3.3404493700673288</v>
+        <v>3.3348050674366325</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>3.552302241370815</v>
+        <v>3.5462999744106685</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>3.8007365314935568</v>
+        <v>3.7943144891792739</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>3.8007365314935568</v>
+        <v>3.7943144891792739</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.4470746184536476</v>
+        <v>3.4412501528857851</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3327724464321937</v>
+        <v>3.3271411153737227</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.272083940554591</v>
+        <v>3.2665551538712716</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16906,7 +16906,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.2142090126844427</v>
+        <v>3.2087780163195623</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18078,23 +18078,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18105,23 +18105,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4732262872397643</v>
+        <v>1.470737000893086</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4963865174034636</v>
+        <v>1.4938580975949189</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5198816838985827</v>
+        <v>1.5173135646917337</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5198816838985827</v>
+        <v>1.5173135646917337</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18132,23 +18132,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4951176591864783</v>
+        <v>1.4925913833468967</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5419941983716472</v>
+        <v>1.5393887160109874</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5911496311048625</v>
+        <v>1.588461091613993</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5911496311048625</v>
+        <v>1.588461091613993</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18159,23 +18159,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5221456493004755</v>
+        <v>1.5195737047083393</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5997388634286742</v>
+        <v>1.5970358108525187</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6837301395028221</v>
+        <v>1.6808851682420882</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6837301395028221</v>
+        <v>1.6808851682420882</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18186,23 +18186,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>1.5495957866419503</v>
+        <v>1.5469774600019981</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>1.6599386188282697</v>
+        <v>1.6571338477106465</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7828905934918446</v>
+        <v>1.7798780724348688</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7828905934918446</v>
+        <v>1.7798780724348688</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18213,23 +18213,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>1.4503938000000003</v>
+        <v>1.4479430933333339</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>1.5750296380470956</v>
+        <v>1.5723683362446752</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>1.7172348919641398</v>
+        <v>1.714333308271512</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>1.87995995226621</v>
+        <v>1.8767834147023534</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>1.87995995226621</v>
+        <v>1.8767834147023534</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18239,23 +18239,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>1.4503938000000003</v>
+        <v>1.4479430933333339</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>1.5973676537417358</v>
+        <v>1.5946686077597809</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>1.7689606006120968</v>
+        <v>1.765971616836111</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9701831362497619</v>
+        <v>1.9668541500485239</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9701831362497619</v>
+        <v>1.9668541500485239</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.6837301395028221</v>
+        <v>1.6808851682420882</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.5911496311048625</v>
+        <v>1.588461091613993</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.5419941983716472</v>
+        <v>1.5393887160109874</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.4951176591864783</v>
+        <v>1.4925913833468967</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.4503938000000001</v>
+        <v>1.4479430933333337</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.02</v>
+        <v>-2.0099999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>3.375685313286676</v>
+        <v>3.3701504414227914</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1589918364703964</v>
+        <v>3.1536541396644786</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.272083940554591</v>
+        <v>3.2665551538712716</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.2142090126844427</v>
+        <v>3.2087780163195623</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.3327724464321937</v>
+        <v>3.3271411153737227</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.2726466561560823</v>
+        <v>3.2671169186614204</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.1589918364703959</v>
+        <v>3.1536541396644782</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.4470746184536476</v>
+        <v>3.4412501528857851</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.2756853132866759</v>
+        <v>3.2701504414227913</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.272083940554591</v>
+        <v>3.2665551538712716</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.41771411417681625</v>
+        <v>0.41771411417681609</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2811956246019802</v>
+        <v>1.2790308093231808</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>1.4469215565384661</v>
+        <v>1.4447567412596667</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55828432277376183</v>
+        <v>0.55819869234178854</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21751806401088669</v>
+        <v>0.21897211796497307</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8155251994171373</v>
+        <v>1.8124575362006285</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>2.020565281803631</v>
+        <v>2.0174976185871221</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.38316257864944714</v>
+        <v>0.38305663463319428</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>2.6367975153174852</v>
+        <v>2.63234216170977</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>2.8968500893046811</v>
+        <v>2.8923947356969659</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.11565067695769848</v>
+        <v>0.11551630803917079</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>2.3478814925441744</v>
+        <v>2.3439143156117299</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>2.5891418051380395</v>
+        <v>2.585174628205595</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.20871779203219298</v>
+        <v>0.20859299585318691</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC6E67C-230E-403A-B6A2-5FF9AC4CDA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF162F0-A557-4359-B9B9-E1CF9B89E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4370,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0859573200000001</v>
+        <v>1.0859573199999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4462,7 +4478,7 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>3.2701504414227913</v>
+        <v>3.27015044142279</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
@@ -4501,7 +4517,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>1.4447567412596667</v>
+        <v>1.4447567412596662</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4520,7 +4536,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>2.0174976185871221</v>
+        <v>2.0174976185871216</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4539,7 +4555,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>2.8923947356969659</v>
+        <v>2.8923947356969646</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4558,7 +4574,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>2.585174628205595</v>
+        <v>2.5851746282055941</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>928439.85014218651</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>57395.095749289067</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-52759</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>4636.0957492890666</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-130645.02443131036</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-233268.98647286888</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>632498.42340470827</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>569161.93498729635</v>
       </c>
@@ -4859,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6703960626889283E-2</v>
+        <v>6.6703960626889269E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>452</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>454</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>455</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>7.8104812973574481E-2</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>8.6087971624454432E-2</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.49619793491400876</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.49619793491400876</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.2342258232843137</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.2342258232843137</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5050,7 +5066,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7876661448006324</v>
+        <v>1.7876661448006319</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>2119124</v>
       </c>
@@ -5117,7 +5133,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49919267240513671</v>
+        <v>0.49919267240513659</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.10863424600069688</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>2.2824569622635926</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>11691643</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>7865303.2833807282</v>
       </c>
@@ -5179,7 +5195,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8527947233421556</v>
+        <v>1.8527947233421551</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>52579.6</v>
       </c>
@@ -5210,7 +5226,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.23859439268269E-2</v>
+        <v>1.2385943926826896E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5232,7 +5248,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5245,7 +5261,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>1.8346149419059199</v>
+        <v>1.8346149419059194</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5404,7 +5420,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>3.2701504414227913</v>
+        <v>3.27015044142279</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5523,7 +5539,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.2790308093231808</v>
+        <v>1.2790308093231804</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5532,7 +5548,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>1.4447567412596667</v>
+        <v>1.4447567412596662</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5592,7 +5608,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>1.8124575362006285</v>
+        <v>1.8124575362006279</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5601,7 +5617,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>2.0174976185871221</v>
+        <v>2.0174976185871216</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5627,7 +5643,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38305663463319428</v>
+        <v>0.38305663463319417</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5661,7 +5677,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>2.63234216170977</v>
+        <v>2.6323421617097686</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5670,7 +5686,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>2.8923947356969659</v>
+        <v>2.8923947356969646</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5730,7 +5746,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>2.3439143156117299</v>
+        <v>2.343914315611729</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5739,7 +5755,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>2.585174628205595</v>
+        <v>2.5851746282055941</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5765,7 +5781,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20859299585318691</v>
+        <v>0.20859299585318714</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,389 +6033,389 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>11946459</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>12989832</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>14279054</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>13398008</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>10417493</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>10858435</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>11259591</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>9799678</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>8503792</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>10671841</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>10241839</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>10928762</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>11742407</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>10461599</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>8825812</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>8937079</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>8501281</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>8114588</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>8204309</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>8925894</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>738313</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>745298</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>638514</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>1023256</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>847748</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>907717</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>732380</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>852198</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>806857</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>842048</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>91335</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>114839</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>113843</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>118507</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>441079</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>440918</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>418466</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>385743</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>344473</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>409408</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>52759</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>34185</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>29394</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>50559</v>
       </c>
-      <c r="G12" s="334">
-        <v>0</v>
-      </c>
-      <c r="H12" s="334">
-        <v>0</v>
-      </c>
-      <c r="I12" s="334">
-        <v>0</v>
-      </c>
-      <c r="J12" s="334">
-        <v>0</v>
-      </c>
-      <c r="K12" s="334">
-        <v>0</v>
-      </c>
-      <c r="L12" s="334">
-        <v>0</v>
-      </c>
-      <c r="M12" s="334"/>
+      <c r="G12" s="321">
+        <v>0</v>
+      </c>
+      <c r="H12" s="321">
+        <v>0</v>
+      </c>
+      <c r="I12" s="321">
+        <v>0</v>
+      </c>
+      <c r="J12" s="321">
+        <v>0</v>
+      </c>
+      <c r="K12" s="321">
+        <v>0</v>
+      </c>
+      <c r="L12" s="321">
+        <v>0</v>
+      </c>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>351080</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>357941</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>314822</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>372708</v>
       </c>
-      <c r="G13" s="334">
-        <v>0</v>
-      </c>
-      <c r="H13" s="334">
-        <v>0</v>
-      </c>
-      <c r="I13" s="334">
-        <v>0</v>
-      </c>
-      <c r="J13" s="334">
-        <v>0</v>
-      </c>
-      <c r="K13" s="334">
-        <v>0</v>
-      </c>
-      <c r="L13" s="334">
-        <v>0</v>
-      </c>
-      <c r="M13" s="334"/>
+      <c r="G13" s="321">
+        <v>0</v>
+      </c>
+      <c r="H13" s="321">
+        <v>0</v>
+      </c>
+      <c r="I13" s="321">
+        <v>0</v>
+      </c>
+      <c r="J13" s="321">
+        <v>0</v>
+      </c>
+      <c r="K13" s="321">
+        <v>0</v>
+      </c>
+      <c r="L13" s="321">
+        <v>0</v>
+      </c>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>316092</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>289887</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>472037</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>1000171</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>274458</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>624095</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>611891</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>382557</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>-92900</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>288050</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>1151129</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>2374098</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>1798732</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>1641435</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>779157</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>754988</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>1528290</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>107512</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>-236670</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>843041</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>79856</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>-7583</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>156154</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>143837</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>33672</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>51771</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>149400</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>57280</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-21166</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>13384</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6411,157 +6427,157 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1522553</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>1543625</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>2142477</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>2938708</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>1263205</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>1142589</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>2004377</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>1698866</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>1114826</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>1353926</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-379005</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-691134</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-2353697</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-3662736</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>1111135</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-2689670</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-4539377</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-249652</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-274490</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-298988</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-1061021</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-784057</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>65370</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-1366718</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-415861</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-1030192</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-691303</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-493789</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-482886</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-1271043</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6570,43 +6586,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13118364425600001</v>
+        <v>0.13118364425599999</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22479316524000001</v>
+        <v>0.22479316523999995</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19330040296000001</v>
+        <v>0.19330040295999998</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16832338460000001</v>
+        <v>0.16832338459999999</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2532756320000011E-2</v>
+        <v>8.2532756319999984E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.162893598</v>
+        <v>0.16289359799999997</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4297866000000009E-3</v>
+        <v>5.4297865999999992E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4297866000000007E-2</v>
+        <v>5.4297866E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -6622,186 +6638,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>103970</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>263657</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>421401</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>212262</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>635876</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>365962</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>155306</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>298566</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>595460</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>783912</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>1124718</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>974450</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>1189994</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1231545</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>1001505</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>1110767</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>1286322</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>1210432</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>1279001</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>1406243</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>4569034</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>4910188</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>5721069</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>4516904</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>5119631</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>4302483</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>4821570</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>5001063</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>5352833</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>5330337</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>19506961</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>19407158</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>17776590</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>16914674</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>15628137</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>15117089</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>15127638</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>14247929</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>14313860</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>14881574</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>1098684</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>1106088</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>1029450</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>1087573</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>928375</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>806640</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>916956</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>1092459</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>997219</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>1026493</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6828,47 +6844,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>11946459</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>12989832</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>14279054</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>13398008</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>10417493</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>10858435</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>11259591</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>9799678</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>8503792</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>10671841</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6877,47 +6893,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-10241839</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-10928762</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-11742407</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-10461599</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-8825812</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-8937079</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-8501281</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-8114588</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-8204309</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-8925894</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6926,47 +6942,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>1704620</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>2061070</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>2536647</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>2936409</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>1591681</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>1921356</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>2758310</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>1685090</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>299483</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>1745947</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6975,47 +6991,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-738313</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-745298</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-638514</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-1023256</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-847748</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-907717</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-732380</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-852198</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-806857</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-842048</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7024,47 +7040,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-91335</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-114839</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-113843</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-118507</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-441079</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-440918</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-418466</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-385743</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-344473</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-409408</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7073,47 +7089,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-646978</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-630459</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-524671</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-904749</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-406669</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-466799</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-313914</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-466455</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-462384</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-432640</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7122,47 +7138,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7171,47 +7187,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>966307</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1315772</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1898133</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>1913153</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>743933</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>1013639</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>2025930</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>832892</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>-507374</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>903899</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7318,47 +7334,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-316092</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-289887</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-472037</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-1000171</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-274458</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-624095</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-611891</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-382557</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>92900</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-288050</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7367,47 +7383,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>1151129</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>2374098</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>1798732</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>1641435</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>779157</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>754988</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>1528290</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>107512</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>-236670</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>843041</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7416,47 +7432,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-79856</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-156154</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-143837</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-33672</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-51771</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-149400</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-57280</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-13384</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7470,47 +7486,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-52759</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-34185</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-29394</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-50559</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7519,47 +7535,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>351080</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>357941</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>314822</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>372708</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7775,47 +7791,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7824,47 +7840,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7873,47 +7889,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7922,47 +7938,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>82527</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>68434</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>-145850</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>-2090746</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>1958479</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>-2577273</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>-3226303</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>955425</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>357450</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>-216105</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -7973,43 +7989,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13118364425600001</v>
+        <v>0.13118364425599999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22479316524000001</v>
+        <v>0.22479316523999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19330040296000001</v>
+        <v>0.19330040295999998</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16832338460000001</v>
+        <v>0.16832338459999999</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2532756320000011E-2</v>
+        <v>8.2532756319999984E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.162893598</v>
+        <v>0.16289359799999997</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4297866000000009E-3</v>
+        <v>5.4297865999999992E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4297866000000007E-2</v>
+        <v>5.4297866E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8344,115 +8360,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>103970</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>263657</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>421401</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>212262</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>635876</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>365962</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>1124718</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>974450</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>1189994</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1231545</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>1001505</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>1110767</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>4569034</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>4910188</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>5721069</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>4516904</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>5119631</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>4302483</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>4821570</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>5001063</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>5352833</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>5330337</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8461,47 +8477,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>19506961</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>19407158</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>17776590</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>16914674</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>15628137</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>15117089</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>15127638</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>14247929</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>14313860</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>14881574</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9327,11 +9343,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3363564331318099</v>
+        <v>4.336356433131809</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8346149419059199</v>
+        <v>1.8346149419059194</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9587,11 +9603,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965409.05000168004</v>
-      </c>
-      <c r="D73" s="76">
+        <v>-965409.05000167992</v>
+      </c>
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-956584.92915481783</v>
       </c>
@@ -9605,7 +9621,7 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>12.110558731534217</v>
+        <v>12.110558731534219</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
@@ -9619,8 +9635,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>3826339.7166192713</v>
       </c>
@@ -9737,11 +9753,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2301278.2197876801</v>
+        <v>-2301278.2197876796</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49919267240513671</v>
+        <v>-0.49919267240513659</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9754,11 +9770,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8541383.6746073365</v>
+        <v>8541383.6746073347</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8527947233421553</v>
+        <v>1.8527947233421551</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9771,11 +9787,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>57099.201502672004</v>
+        <v>57099.201502671989</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2385943926826898E-2</v>
+        <v>1.2385943926826895E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9788,7 +9804,7 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>6297204.6563223293</v>
+        <v>6297204.6563223274</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
@@ -9924,54 +9940,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>G4</f>
         <v>11946459</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>11946459</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>12989832</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>14279054</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>13398008</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>10417493</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>10858435</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>11259591</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>9799678</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>8503792</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>10671841</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9981,52 +9997,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-10341304.899857813</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10333174</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-11043601</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-11856250</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-10580106</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-9266891</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-9377997</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-8919747</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-8500331</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-8548782</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-9335302</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10036,52 +10052,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>1605154.1001421865</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>1613285</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>1946231</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>2422804</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>2817902</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>1150602</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>1480438</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>2339844</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>1299347</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>-44990</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>1336539</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10091,52 +10107,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-676714.25</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-646978</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-630459</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-524671</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-904749</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-406669</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-466799</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-313914</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-466455</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-462384</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-432640</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10146,54 +10162,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>928439.85014218651</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>966307</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1315772</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1898133</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>1913153</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>743933</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>1013639</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>2025930</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>832892</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>-507374</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>903899</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10203,52 +10219,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10258,52 +10274,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10313,54 +10329,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10370,52 +10386,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>4636.0957492890666</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>62139.423404708286</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>82958.832094977464</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>73638.219018790798</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>71417.648029856486</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10425,52 +10441,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>933075.94589147554</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1028446.4234047083</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1398730.8320949774</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1971771.2190187909</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>1984570.6480298564</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>743933</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>1013639</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>2025930</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>832892</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>-507374</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>903899</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10480,52 +10496,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-233268.98647286888</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-316092</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-289887</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-472037</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-1000171</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-274458</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-624095</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-611891</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-382557</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>92900</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-288050</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10535,54 +10551,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-130645.02443131036</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-79856</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-156154</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-143837</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-33672</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-51771</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-149400</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-57280</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-13384</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10592,54 +10608,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>569161.93498729635</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>632498.42340470827</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>1108843.8320949774</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>1343580.2190187909</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>840562.64802985638</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>435803</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>337773</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>1264639</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>393055</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>-414474</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>602465</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10649,7 +10665,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10658,24 +10674,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10683,71 +10699,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>569161.93498729635</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>632498.42340470827</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>1108843.8320949774</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>1343580.2190187909</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>840562.64802985638</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>435803</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>337773</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>1264639</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>393055</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>-414474</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>602465</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10820,54 +10836,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-10241839</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-10241839</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-10928762</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-11742407</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-10461599</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-8825812</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-8937079</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-8501281</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-8114588</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-8204309</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-8925894</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10877,54 +10893,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-99465.899857813085</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-91335</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-114839</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-113843</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-118507</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-441079</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-440918</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-418466</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-385743</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-344473</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-409408</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10934,54 +10950,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-10341304.899857813</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-10333174</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-11043601</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-11856250</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-10580106</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-9266891</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-9377997</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-8919747</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-8500331</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-8548782</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-9335302</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11187,54 +11203,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-676714.25</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-646978</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-630459</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-524671</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-904749</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-406669</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-466799</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-313914</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-466455</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-462384</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-432640</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11244,7 +11260,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11253,47 +11269,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11303,54 +11319,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-676714.25</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-646978</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-630459</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-524671</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-904749</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-406669</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-466799</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-313914</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-466455</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-462384</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-432640</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11644,52 +11660,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-52759</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-52759</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-34185</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-29394</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-50559</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>0</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>0</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>0</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11699,52 +11715,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>57395.095749289067</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>114898.42340470829</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>117143.83209497746</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>103032.2190187908</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>121976.64802985649</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11754,54 +11770,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>175374.64499999999</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>351080</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>357941</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>314822</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>372708</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11811,52 +11827,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>4636.0957492890666</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>62139.423404708286</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>82958.832094977464</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>73638.219018790798</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>71417.648029856486</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -12002,52 +12018,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12057,52 +12073,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12112,52 +12128,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12167,52 +12183,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12222,53 +12238,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>202593</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>1024457</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>87208</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>406304</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>309682</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>365444</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>114251</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-342823</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>177804</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>227192</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12278,52 +12294,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>202593</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>1024457</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>87208</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>406304</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>309682</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>365444</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>114251</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-342823</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>177804</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>227192</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13308,43 +13324,43 @@
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.13118364425600001</v>
+        <v>0.13118364425599999</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.22479316524000001</v>
+        <v>0.22479316523999995</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.19330040296000001</v>
+        <v>0.19330040295999998</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.16832338460000001</v>
+        <v>0.16832338459999999</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="L90" s="112">
         <f>Data!H65</f>
-        <v>8.2532756320000011E-2</v>
+        <v>8.2532756319999984E-2</v>
       </c>
       <c r="M90" s="112">
         <f>Data!I65</f>
-        <v>0.162893598</v>
+        <v>0.16289359799999997</v>
       </c>
       <c r="N90" s="112">
         <f>Data!J65</f>
-        <v>5.4297866000000009E-3</v>
+        <v>5.4297865999999992E-3</v>
       </c>
       <c r="O90" s="112">
         <f>Data!K65</f>
-        <v>5.4297866000000007E-2</v>
+        <v>5.4297866E-2</v>
       </c>
       <c r="P90" s="112">
         <f>Data!L65</f>
-        <v>8.6876585600000014E-2</v>
+        <v>8.6876585599999986E-2</v>
       </c>
       <c r="Q90" s="112" t="str">
         <f>Data!M65</f>
@@ -13364,43 +13380,43 @@
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>604756.60002016008</v>
+        <v>604756.60002015997</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1036296.4917564</v>
+        <v>1036296.4917563997</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>891114.8576456001</v>
+        <v>891114.85764559987</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>775970.803006</v>
+        <v>775970.80300599989</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>400501.05961600004</v>
+        <v>400501.05961599993</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>380476.0066352</v>
+        <v>380476.00663519988</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>750939.48677999992</v>
+        <v>750939.4867799998</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>25031.316226000003</v>
+        <v>25031.316225999995</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>250313.16226000001</v>
+        <v>250313.16225999998</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>400501.05961600004</v>
+        <v>400501.05961599993</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13419,27 +13435,27 @@
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95613930033973005</v>
+        <v>0.95613930033972983</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.93457388837027555</v>
+        <v>0.93457388837027533</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66323904224816299</v>
+        <v>0.66323904224816288</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92315641769801537</v>
+        <v>0.92315641769801526</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
-        <v>0.91899564623465213</v>
+        <v>0.9189956462346518</v>
       </c>
       <c r="L92" s="170">
         <f t="shared" si="38"/>
-        <v>1.1264251631575053</v>
+        <v>1.1264251631575048</v>
       </c>
       <c r="M92" s="170">
         <f t="shared" si="38"/>
@@ -13447,15 +13463,15 @@
       </c>
       <c r="N92" s="170">
         <f t="shared" si="38"/>
-        <v>6.3684004085942172E-2</v>
+        <v>6.3684004085942159E-2</v>
       </c>
       <c r="O92" s="170">
         <f t="shared" si="38"/>
-        <v>-0.60392970912530108</v>
+        <v>-0.60392970912530097</v>
       </c>
       <c r="P92" s="170">
         <f t="shared" si="38"/>
-        <v>0.6647706665383053</v>
+        <v>0.66477066653830508</v>
       </c>
       <c r="Q92" s="170" t="str">
         <f t="shared" si="38"/>
@@ -13474,43 +13490,43 @@
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5265494654726378E-2</v>
+        <v>6.5265494654726364E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11183739564179106</v>
+        <v>0.11183739564179103</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.6169354706467675E-2</v>
+        <v>9.6169354706467661E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3742977412935335E-2</v>
+        <v>8.3742977412935321E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3222181890547273E-2</v>
+        <v>4.3222181890547259E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1061072796019914E-2</v>
+        <v>4.10610727960199E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1041591044776123E-2</v>
+        <v>8.104159104477611E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7013863681592046E-3</v>
+        <v>2.7013863681592037E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7013863681592046E-2</v>
+        <v>2.7013863681592042E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3222181890547273E-2</v>
+        <v>4.3222181890547259E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13697,54 +13713,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>24075995</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>24075995</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>24317346</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>23497659</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>21431578</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>20747768</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>19419572</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>19949208</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>19248992</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>19666693</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>20211911</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13754,54 +13770,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>103970</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>263657</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>421401</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>212262</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>635876</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>365962</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13811,54 +13827,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>1124718</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>974450</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>1189994</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1231545</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1001505</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1110767</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13868,54 +13884,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>4569034</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>4569034</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>4910188</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>5721069</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>4516904</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>5119631</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>4302483</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>4821570</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>5001063</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>5352833</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>5330337</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13925,54 +13941,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>19506961</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>19506961</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>19407158</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>17776590</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>16914674</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>15628137</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>15117089</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>15127638</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>14247929</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>14313860</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>14881574</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -14611,50 +14627,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13407496086004744</v>
+        <v>0.13407496086004742</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.1489948574370504</v>
+        <v>0.14899485743705035</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.26120543952286157</v>
+        <v>0.26120543952286152</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>0.31650125246218208</v>
+        <v>0.31650125246218203</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.19800762701661742</v>
+        <v>0.19800762701661739</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.10266018610150977</v>
+        <v>0.10266018610150975</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>7.9567692374915414E-2</v>
+        <v>7.95676923749154E-2</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.29790541848318441</v>
+        <v>0.29790541848318436</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>9.2590228722906745E-2</v>
+        <v>9.2590228722906717E-2</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>-9.7635807863271154E-2</v>
+        <v>-9.763580786327114E-2</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>0.14192001665809112</v>
+        <v>0.14192001665809109</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14668,50 +14684,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6703960626889283E-2</v>
+        <v>6.6703960626889269E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.4126794744801203E-2</v>
+        <v>7.4126794744801175E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12995295498649831</v>
+        <v>0.12995295498649828</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15746330968267766</v>
+        <v>0.15746330968267763</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8511257222197737E-2</v>
+        <v>9.8511257222197723E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.1074719453487454E-2</v>
+        <v>5.107471945348744E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9585916604435535E-2</v>
+        <v>3.9585916604435528E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.14821165098665892</v>
+        <v>0.14821165098665889</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.6064790409406343E-2</v>
+        <v>4.606479040940633E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.8575028787697094E-2</v>
+        <v>-4.8575028787697087E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.0606973461736888E-2</v>
+        <v>7.0606973461736874E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15470,7 +15486,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15509,7 +15525,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>569161.93498729635</v>
       </c>
@@ -15541,7 +15557,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>7588825.7998306183</v>
       </c>
@@ -15549,17 +15565,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>2119124</v>
       </c>
@@ -15567,15 +15583,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>7865303.2833807282</v>
       </c>
@@ -15583,15 +15599,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>52579.6</v>
       </c>
@@ -15599,15 +15615,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>13387584.683211347</v>
       </c>
@@ -15623,7 +15639,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0859573200000001</v>
+        <v>1.0859573199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15637,7 +15653,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15674,7 +15690,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15684,13 +15700,13 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.2665551538712716</v>
+        <v>3.2665551538712712</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15698,10 +15714,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15719,7 +15735,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15741,7 +15757,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15763,7 +15779,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15783,9 +15799,19 @@
         <f t="shared" si="1"/>
         <v>486195.53897211479</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15805,9 +15831,19 @@
         <f t="shared" si="1"/>
         <v>461320.41837354144</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15827,9 +15863,19 @@
         <f t="shared" si="1"/>
         <v>437717.9783637324</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15851,7 +15897,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15873,7 +15919,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15895,7 +15941,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15917,7 +15963,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15939,7 +15985,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15961,7 +16007,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15983,11 +16029,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16003,13 +16049,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16025,13 +16081,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16047,9 +16113,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16071,7 +16147,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16093,7 +16169,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16115,7 +16191,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16137,7 +16213,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16159,7 +16235,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16181,7 +16257,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16203,7 +16279,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16225,7 +16301,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16247,7 +16323,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16269,7 +16345,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16291,11 +16367,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16311,13 +16387,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16333,13 +16419,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16355,13 +16451,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16377,9 +16483,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16401,7 +16517,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16412,11 +16528,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16426,7 +16542,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>8068102.1635585381</v>
@@ -16453,7 +16569,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16475,7 +16591,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16496,14 +16612,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>7588825.7998306192</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>7964249.5538186785</v>
       </c>
       <c r="D58" s="123">
@@ -16515,16 +16631,26 @@
       <c r="F58" s="123">
         <v>8809700.3190522641</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>7588825.7998306192</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>8107875.5886692684</v>
       </c>
       <c r="D59" s="123">
@@ -16536,16 +16662,26 @@
       <c r="F59" s="123">
         <v>9328532.7985863127</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>7588825.7998306174</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>8240951.9074817337</v>
       </c>
       <c r="D60" s="123">
@@ -16557,16 +16693,26 @@
       <c r="F60" s="123">
         <v>9836424.1410892401</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>7588825.7998306174</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>8357830.033836456</v>
       </c>
       <c r="D61" s="123">
@@ -16578,26 +16724,56 @@
       <c r="F61" s="123">
         <v>10308494.572138546</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16626,23 +16802,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16653,23 +16829,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.1817960583903573</v>
+        <v>3.1817960583903564</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2103419328759184</v>
+        <v>3.2103419328759175</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2393006292725648</v>
+        <v>3.2393006292725639</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2393006292725648</v>
+        <v>3.2393006292725639</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16680,23 +16856,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2087780163195623</v>
+        <v>3.2087780163195614</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2665551538712716</v>
+        <v>3.2665551538712707</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3271411153737227</v>
+        <v>3.3271411153737218</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3271411153737227</v>
+        <v>3.3271411153737218</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16707,23 +16883,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>3.2420910537089931</v>
+        <v>3.2420910537089922</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>3.3377276745793019</v>
+        <v>3.3377276745793014</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4412501528857851</v>
+        <v>3.4412501528857846</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4412501528857851</v>
+        <v>3.4412501528857846</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16734,23 +16910,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>3.2759244037932822</v>
+        <v>3.2759244037932818</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>3.4119261885643559</v>
+        <v>3.411926188564355</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5634692264223906</v>
+        <v>3.5634692264223902</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5634692264223906</v>
+        <v>3.5634692264223902</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16761,23 +16937,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644777</v>
+        <v>3.1536541396644768</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>3.3072726039089115</v>
+        <v>3.3072726039089106</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>3.4825460489831226</v>
+        <v>3.4825460489831221</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6831109446774195</v>
+        <v>3.6831109446774186</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6831109446774195</v>
+        <v>3.6831109446774186</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16787,23 +16963,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644777</v>
+        <v>3.1536541396644768</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>3.3348050674366325</v>
+        <v>3.3348050674366316</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>3.5462999744106685</v>
+        <v>3.5462999744106676</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7943144891792739</v>
+        <v>3.7943144891792731</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7943144891792739</v>
+        <v>3.7943144891792731</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16838,7 +17014,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.4412501528857851</v>
+        <v>3.4412501528857846</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16860,7 +17036,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3271411153737227</v>
+        <v>3.3271411153737218</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16883,7 +17059,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.2665551538712716</v>
+        <v>3.2665551538712707</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16906,7 +17082,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.2087780163195623</v>
+        <v>3.2087780163195614</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16929,7 +17105,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -16969,6 +17145,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17071,7 +17317,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>6146666.666666667</v>
       </c>
@@ -17079,8 +17325,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17089,7 +17335,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18078,23 +18324,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18105,23 +18351,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>1.470737000893086</v>
+        <v>1.4707370008930858</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4938580975949189</v>
+        <v>1.4938580975949185</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5173135646917337</v>
+        <v>1.5173135646917335</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5173135646917337</v>
+        <v>1.5173135646917335</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18132,23 +18378,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4925913833468967</v>
+        <v>1.4925913833468964</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5393887160109874</v>
+        <v>1.5393887160109869</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>1.588461091613993</v>
+        <v>1.5884610916139925</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>1.588461091613993</v>
+        <v>1.5884610916139925</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18159,23 +18405,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5195737047083393</v>
+        <v>1.5195737047083391</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5970358108525187</v>
+        <v>1.5970358108525184</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6808851682420882</v>
+        <v>1.6808851682420878</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6808851682420882</v>
+        <v>1.6808851682420878</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18186,23 +18432,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>1.5469774600019981</v>
+        <v>1.5469774600019977</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>1.6571338477106465</v>
+        <v>1.6571338477106461</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7798780724348688</v>
+        <v>1.7798780724348684</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7798780724348688</v>
+        <v>1.7798780724348684</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18213,23 +18459,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333339</v>
+        <v>1.4479430933333335</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>1.5723683362446752</v>
+        <v>1.572368336244675</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>1.714333308271512</v>
+        <v>1.7143333082715115</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>1.8767834147023534</v>
+        <v>1.876783414702353</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>1.8767834147023534</v>
+        <v>1.876783414702353</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18239,23 +18485,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333339</v>
+        <v>1.4479430933333335</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>1.5946686077597809</v>
+        <v>1.5946686077597807</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>1.765971616836111</v>
+        <v>1.7659716168361108</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9668541500485239</v>
+        <v>1.9668541500485235</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9668541500485239</v>
+        <v>1.9668541500485235</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18290,7 +18536,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.6808851682420882</v>
+        <v>1.6808851682420878</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18312,7 +18558,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.588461091613993</v>
+        <v>1.5884610916139925</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18335,7 +18581,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.5393887160109874</v>
+        <v>1.5393887160109869</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18358,7 +18604,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.4925913833468967</v>
+        <v>1.4925913833468964</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18381,7 +18627,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.4479430933333337</v>
+        <v>1.4479430933333333</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18530,14 +18776,14 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>3.3701504414227914</v>
+        <v>3.3701504414227901</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>966307</v>
       </c>
@@ -18545,11 +18791,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中海石油化学(3983.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18562,7 +18808,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>632498.42340470827</v>
       </c>
@@ -18570,8 +18816,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18584,7 +18830,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>569161.93498729635</v>
       </c>
@@ -18592,8 +18838,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18603,8 +18849,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18617,8 +18863,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18636,8 +18882,8 @@
         <v>-3.750240119526338E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18654,8 +18900,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.20361731775539216</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18672,8 +18918,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0443280496378065E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18699,21 +18945,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18727,8 +18973,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18736,14 +18982,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1536541396644786</v>
+        <v>3.1536541396644777</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18763,8 +19009,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18774,8 +19020,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18783,14 +19029,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.2665551538712716</v>
+        <v>3.2665551538712707</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18800,8 +19046,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18821,8 +19067,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18832,8 +19078,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18841,14 +19087,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.2087780163195623</v>
+        <v>3.2087780163195614</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18858,8 +19104,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18879,8 +19125,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18890,8 +19136,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18899,14 +19145,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.3271411153737227</v>
+        <v>3.3271411153737218</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18917,8 +19163,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18926,7 +19172,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.2671169186614204</v>
+        <v>3.2671169186614191</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18980,8 +19226,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18991,8 +19237,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19000,14 +19246,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.1536541396644782</v>
+        <v>3.1536541396644773</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19017,8 +19263,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19038,8 +19284,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19049,8 +19295,8 @@
         <v>0.03</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19058,14 +19304,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.4412501528857851</v>
+        <v>3.4412501528857846</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19075,8 +19321,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19084,7 +19330,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.2701504414227913</v>
+        <v>3.27015044142279</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19146,7 +19392,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.2665551538712716</v>
+        <v>3.2665551538712712</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19209,7 +19455,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.41771411417681609</v>
+        <v>0.41771411417681625</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19281,7 +19527,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2790308093231808</v>
+        <v>1.2790308093231804</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19291,7 +19537,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>1.4447567412596667</v>
+        <v>1.4447567412596662</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19370,7 +19616,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8124575362006285</v>
+        <v>1.8124575362006279</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19380,7 +19626,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>2.0174976185871221</v>
+        <v>2.0174976185871216</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19391,7 +19637,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.38305663463319428</v>
+        <v>0.38305663463319417</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19430,7 +19676,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>2.63234216170977</v>
+        <v>2.6323421617097686</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19442,7 +19688,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>2.8923947356969659</v>
+        <v>2.8923947356969646</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19488,7 +19734,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>2.3439143156117299</v>
+        <v>2.343914315611729</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19498,7 +19744,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>2.585174628205595</v>
+        <v>2.5851746282055941</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19508,7 +19754,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.20859299585318691</v>
+        <v>0.20859299585318714</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF162F0-A557-4359-B9B9-E1CF9B89E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAE99E1-0C9B-49C9-B8EB-FB3BF960BD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9266.0999999999985</v>
+        <v>9220</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4386,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0859573199999999</v>
+        <v>1.0910393900000002</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>3.27015044142279</v>
+        <v>3.2854541123385519</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21897211796497307</v>
+        <v>0.22285790267459293</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>1.4447567412596662</v>
+        <v>1.4507423578077803</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>2.0174976185871216</v>
+        <v>2.0259795689376197</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>2.8923947356969646</v>
+        <v>2.9047135873529037</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>2.5851746282055941</v>
+        <v>2.5961436933857449</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6703960626889269E-2</v>
+        <v>6.7351202858976097E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.9751243781094537E-2</v>
+        <v>0.05</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7876661448006319</v>
+        <v>1.7960320762393625</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.49919267240513659</v>
+        <v>0.50152879746081569</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8527947233421551</v>
+        <v>1.8614654439185916</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2385943926826896E-2</v>
+        <v>1.244390774630022E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>1.8346149419059194</v>
+        <v>1.8432005846251125</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.44 HKD</v>
+        <v>3.46 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>3.33 HKD</v>
+        <v>3.34 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>3.27 HKD</v>
+        <v>3.28 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>3.21 HKD</v>
+        <v>3.22 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>3.15 HKD</v>
+        <v>3.17 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>3.27015044142279</v>
+        <v>3.2854541123385519</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.2790308093231804</v>
+        <v>1.2850164258712944</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>1.4447567412596662</v>
+        <v>1.4507423578077803</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55819869234178854</v>
+        <v>0.55843475263906295</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>1.8124575362006279</v>
+        <v>1.8209394865511259</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>2.0174976185871216</v>
+        <v>2.0259795689376197</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.38305663463319417</v>
+        <v>0.38334869407275074</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>2.6323421617097686</v>
+        <v>2.6446610133657078</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>2.8923947356969646</v>
+        <v>2.9047135873529037</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11551630803917079</v>
+        <v>0.11588672736465067</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>2.343914315611729</v>
+        <v>2.3548833807918799</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>2.5851746282055941</v>
+        <v>2.5961436933857449</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20859299585318714</v>
+        <v>0.20893702568505856</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6586,43 +6586,43 @@
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13118364425599999</v>
+        <v>0.13179755831200002</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22479316523999995</v>
+        <v>0.22584515373000003</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19330040295999998</v>
+        <v>0.19420501142000002</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16832338459999999</v>
+        <v>0.16911110545000002</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.2532756319999984E-2</v>
+        <v>8.2918993640000008E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16289359799999997</v>
+        <v>0.16365590850000003</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.4297865999999992E-3</v>
+        <v>5.4551969500000012E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4297866E-2</v>
+        <v>5.4551969500000012E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
@@ -7989,43 +7989,43 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13118364425599999</v>
+        <v>0.13179755831200002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22479316523999995</v>
+        <v>0.22584515373000003</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19330040295999998</v>
+        <v>0.19420501142000002</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16832338459999999</v>
+        <v>0.16911110545000002</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.2532756319999984E-2</v>
+        <v>8.2918993640000008E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16289359799999997</v>
+        <v>0.16365590850000003</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4297865999999992E-3</v>
+        <v>5.4551969500000012E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4297866E-2</v>
+        <v>5.4551969500000012E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9343,11 +9343,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.336356433131809</v>
+        <v>4.356649741655322</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8346149419059194</v>
+        <v>1.8432005846251125</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965409.05000167992</v>
+        <v>-965644.89531819336</v>
       </c>
       <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>12.110558731534219</v>
+        <v>12.107600896235715</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
@@ -9753,11 +9753,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2301278.2197876796</v>
+        <v>-2312047.7562943604</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.49919267240513659</v>
+        <v>-0.50152879746081569</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9770,11 +9770,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8541383.6746073347</v>
+        <v>8581355.6964647081</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8527947233421551</v>
+        <v>1.8614654439185918</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9787,11 +9787,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>57099.201502671989</v>
+        <v>57366.414710444005</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2385943926826895E-2</v>
+        <v>1.2443907746300218E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9804,11 +9804,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>6297204.6563223274</v>
+        <v>6326674.3548807921</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>1.3659879948638454</v>
+        <v>1.3723805542040761</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13324,43 +13324,43 @@
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.13118364425599999</v>
+        <v>0.13179755831200002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.22479316523999995</v>
+        <v>0.22584515373000003</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.19330040295999998</v>
+        <v>0.19420501142000002</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.16832338459999999</v>
+        <v>0.16911110545000002</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="L90" s="112">
         <f>Data!H65</f>
-        <v>8.2532756319999984E-2</v>
+        <v>8.2918993640000008E-2</v>
       </c>
       <c r="M90" s="112">
         <f>Data!I65</f>
-        <v>0.16289359799999997</v>
+        <v>0.16365590850000003</v>
       </c>
       <c r="N90" s="112">
         <f>Data!J65</f>
-        <v>5.4297865999999992E-3</v>
+        <v>5.4551969500000012E-3</v>
       </c>
       <c r="O90" s="112">
         <f>Data!K65</f>
-        <v>5.4297866E-2</v>
+        <v>5.4551969500000012E-2</v>
       </c>
       <c r="P90" s="112">
         <f>Data!L65</f>
-        <v>8.6876585599999986E-2</v>
+        <v>8.728315120000002E-2</v>
       </c>
       <c r="Q90" s="112" t="str">
         <f>Data!M65</f>
@@ -13380,43 +13380,43 @@
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>604756.60002015997</v>
+        <v>607586.74381831998</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1036296.4917563997</v>
+        <v>1041146.1586953001</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>891114.85764559987</v>
+        <v>895285.1026462001</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>775970.80300599989</v>
+        <v>779602.19612450013</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>400501.05961599993</v>
+        <v>402375.32703200006</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>380476.00663519988</v>
+        <v>382256.5606804</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>750939.4867799998</v>
+        <v>754453.73818500014</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>25031.316225999995</v>
+        <v>25148.457939500004</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>250313.16225999998</v>
+        <v>251484.57939500007</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>400501.05961599993</v>
+        <v>402375.32703200006</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13435,43 +13435,43 @@
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.95613930033972983</v>
+        <v>0.9606138471424327</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.93457388837027533</v>
+        <v>0.93894751322034797</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66323904224816288</v>
+        <v>0.6663428725528735</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92315641769801526</v>
+        <v>0.92747661099593481</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
-        <v>0.9189956462346518</v>
+        <v>0.92329636792771075</v>
       </c>
       <c r="L92" s="170">
         <f t="shared" si="38"/>
-        <v>1.1264251631575048</v>
+        <v>1.1316966148283019</v>
       </c>
       <c r="M92" s="170">
         <f t="shared" si="38"/>
-        <v>0.59379750804775111</v>
+        <v>0.59657636541732473</v>
       </c>
       <c r="N92" s="170">
         <f t="shared" si="38"/>
-        <v>6.3684004085942159E-2</v>
+        <v>6.3982032894887492E-2</v>
       </c>
       <c r="O92" s="170">
         <f t="shared" si="38"/>
-        <v>-0.60392970912530097</v>
+        <v>-0.60675598323417168</v>
       </c>
       <c r="P92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66477066653830508</v>
+        <v>0.66788166454814824</v>
       </c>
       <c r="Q92" s="170" t="str">
         <f t="shared" si="38"/>
@@ -13485,48 +13485,48 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.9751243781094537E-2</v>
+        <v>0.05</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5265494654726364E-2</v>
+        <v>6.5898779156000009E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.11183739564179103</v>
+        <v>0.11292257686500001</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.6169354706467661E-2</v>
+        <v>9.7102505710000009E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3742977412935321E-2</v>
+        <v>8.4555552725000011E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3222181890547259E-2</v>
+        <v>4.364157560000001E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.10610727960199E-2</v>
+        <v>4.1459496820000004E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.104159104477611E-2</v>
+        <v>8.1827954250000015E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7013863681592037E-3</v>
+        <v>2.7275984750000006E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7013863681592042E-2</v>
+        <v>2.7275984750000006E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3222181890547259E-2</v>
+        <v>4.364157560000001E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14627,50 +14627,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13407496086004742</v>
+        <v>0.13470240571795219</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14899485743705035</v>
+        <v>0.14969212452222011</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.26120543952286152</v>
+        <v>0.26242783040654377</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>0.31650125246218203</v>
+        <v>0.31798241704432284</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.19800762701661739</v>
+        <v>0.19893426437381334</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.10266018610150975</v>
+        <v>0.10314061589591542</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>7.95676923749154E-2</v>
+        <v>7.9940053769733205E-2</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.29790541848318436</v>
+        <v>0.2992995581627354</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>9.2590228722906717E-2</v>
+        <v>9.3023533066475067E-2</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>-9.763580786327114E-2</v>
+        <v>-9.8092724540316714E-2</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>0.14192001665809109</v>
+        <v>0.14258417485821043</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14684,50 +14684,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6703960626889269E-2</v>
+        <v>6.7351202858976097E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.4126794744801175E-2</v>
+        <v>7.4846062261110055E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12995295498649828</v>
+        <v>0.13121391520327189</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15746330968267763</v>
+        <v>0.15899120852216142</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8511257222197723E-2</v>
+        <v>9.946713218690667E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.107471945348744E-2</v>
+        <v>5.1570307947957708E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9585916604435528E-2</v>
+        <v>3.9970026884866602E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.14821165098665889</v>
+        <v>0.1496497790813677</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.606479040940633E-2</v>
+        <v>4.6511766533237534E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.8575028787697087E-2</v>
+        <v>-4.9046362270158357E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.0606973461736874E-2</v>
+        <v>7.1292087429105214E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14741,43 +14741,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12423015076461513</v>
+        <v>0.12485130151843818</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25621329361867456</v>
+        <v>0.2574943600867679</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19411964040966537</v>
+        <v>0.19509023861171368</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17714410593453561</v>
+        <v>0.17802982646420823</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.408683264803965E-2</v>
+        <v>8.4507266811279833E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1478507678527115E-2</v>
+        <v>8.1885900216919744E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1649334671544663</v>
+        <v>0.1657581344902386</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1602723907577085E-2</v>
+        <v>1.1660737527114967E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.5541489947226995E-2</v>
+        <v>-2.5669197396963123E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0981211081253191E-2</v>
+        <v>9.1436117136659431E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0859573199999999</v>
+        <v>1.0910393900000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.2665551538712712</v>
+        <v>3.2818419995373933</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16802,23 +16802,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16829,23 +16829,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.1817960583903564</v>
+        <v>3.1966862479002582</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2103419328759175</v>
+        <v>3.2253657115515026</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2393006292725639</v>
+        <v>3.2544599290404483</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>3.2393006292725639</v>
+        <v>3.2544599290404483</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16856,23 +16856,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2087780163195614</v>
+        <v>3.2237944761684605</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>3.2665551538712707</v>
+        <v>3.2818419995373929</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3271411153737218</v>
+        <v>3.3427114916093261</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>3.3271411153737218</v>
+        <v>3.3427114916093261</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16883,23 +16883,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>3.2420910537089922</v>
+        <v>3.2572634121229709</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>3.3377276745793014</v>
+        <v>3.3533475938622712</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4412501528857846</v>
+        <v>3.4573545373237264</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>3.4412501528857846</v>
+        <v>3.4573545373237264</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16910,23 +16910,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>3.2759244037932818</v>
+        <v>3.2912550957350115</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>3.411926188564355</v>
+        <v>3.4278933425268314</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5634692264223902</v>
+        <v>3.5801455724610403</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>3.5634692264223902</v>
+        <v>3.5801455724610403</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16937,23 +16937,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644768</v>
+        <v>3.1684126304434383</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>3.3072726039089106</v>
+        <v>3.322749999357701</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>3.4825460489831221</v>
+        <v>3.4988436902192959</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6831109446774186</v>
+        <v>3.7003471907930745</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6831109446774186</v>
+        <v>3.7003471907930745</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16963,23 +16963,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>3.1536541396644768</v>
+        <v>3.1684126304434383</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>3.3348050674366316</v>
+        <v>3.3504113094840342</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>3.5462999744106676</v>
+        <v>3.5628959716741275</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7943144891792731</v>
+        <v>3.8120711463525256</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>3.7943144891792731</v>
+        <v>3.8120711463525256</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.4412501528857846</v>
+        <v>3.4573545373237264</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3271411153737218</v>
+        <v>3.3427114916093261</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.2665551538712707</v>
+        <v>3.2818419995373929</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.2087780163195614</v>
+        <v>3.2237944761684605</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18324,23 +18324,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18351,23 +18351,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4707370008930858</v>
+        <v>1.4776197653005572</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>1.4938580975949185</v>
+        <v>1.5008490642583641</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5173135646917335</v>
+        <v>1.5244142983998623</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>1.5173135646917335</v>
+        <v>1.5244142983998623</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18378,23 +18378,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>1.4925913833468964</v>
+        <v>1.499576422032916</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5393887160109869</v>
+        <v>1.5465927571532101</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5884610916139925</v>
+        <v>1.595894781972891</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>1.5884610916139925</v>
+        <v>1.595894781972891</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18405,23 +18405,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5195737047083391</v>
+        <v>1.5266850154341487</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>1.5970358108525184</v>
+        <v>1.6045096292372591</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6808851682420878</v>
+        <v>1.6887513853849203</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>1.6808851682420878</v>
+        <v>1.6887513853849203</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18432,23 +18432,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>1.5469774600019977</v>
+        <v>1.5542170149968042</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>1.6571338477106461</v>
+        <v>1.6648889132720031</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7798780724348684</v>
+        <v>1.7882075572028144</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>1.7798780724348684</v>
+        <v>1.7882075572028144</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18459,23 +18459,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333335</v>
+        <v>1.4547191866666673</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>1.572368336244675</v>
+        <v>1.5797267156242434</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>1.7143333082715115</v>
+        <v>1.7223560562336211</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>1.876783414702353</v>
+        <v>1.8855663977097854</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>1.876783414702353</v>
+        <v>1.8855663977097854</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18485,23 +18485,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>1.4479430933333335</v>
+        <v>1.4547191866666673</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>1.5946686077597807</v>
+        <v>1.6021313480923733</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>1.7659716168361108</v>
+        <v>1.7742360220843527</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9668541500485235</v>
+        <v>1.976058646658333</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>1.9668541500485235</v>
+        <v>1.976058646658333</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>1.6808851682420878</v>
+        <v>1.6887513853849203</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.5884610916139925</v>
+        <v>1.595894781972891</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.5393887160109869</v>
+        <v>1.5465927571532101</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.4925913833468964</v>
+        <v>1.499576422032916</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.4479430933333333</v>
+        <v>1.4547191866666671</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.0099999999999998</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>3.3701504414227901</v>
+        <v>3.385454112338552</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18982,7 +18982,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1536541396644777</v>
+        <v>3.1684126304434392</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>3.2665551538712707</v>
+        <v>3.2818419995373929</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>3.2087780163195614</v>
+        <v>3.2237944761684605</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>3.3271411153737218</v>
+        <v>3.3427114916093261</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>3.2671169186614191</v>
+        <v>3.2824063932779932</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>3.1536541396644773</v>
+        <v>3.1684126304434388</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>3.4412501528857846</v>
+        <v>3.4573545373237264</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>3.27015044142279</v>
+        <v>3.2854541123385519</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>3.2665551538712712</v>
+        <v>3.2818419995373933</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19455,7 +19455,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.41771411417681625</v>
+        <v>0.4177141141768162</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.2790308093231804</v>
+        <v>1.2850164258712944</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>1.4447567412596662</v>
+        <v>1.4507423578077803</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19548,7 +19548,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55819869234178854</v>
+        <v>0.55843475263906295</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21897211796497307</v>
+        <v>0.22285790267459293</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>1.8124575362006279</v>
+        <v>1.8209394865511259</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>2.0174976185871216</v>
+        <v>2.0259795689376197</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.38305663463319417</v>
+        <v>0.38334869407275074</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>2.6323421617097686</v>
+        <v>2.6446610133657078</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>2.8923947356969646</v>
+        <v>2.9047135873529037</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.11551630803917079</v>
+        <v>0.11588672736465067</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>2.343914315611729</v>
+        <v>2.3548833807918799</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>2.5851746282055941</v>
+        <v>2.5961436933857449</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.20859299585318714</v>
+        <v>0.20893702568505856</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/3983.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3983.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DEA81B-8D7C-40B8-B269-9F9D6D2B2DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516066D8-021E-FF4A-8A53-4322AC390303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9127.7999999999993</v>
+        <v>9312.2000000000007</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,37 +4388,37 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0907712000000001</v>
+        <v>1.0889065499999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,28 +4478,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>3.2846465100223896</v>
+        <v>3.2790314771769</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22703220937277968</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.2179052458704549</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,13 +4518,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>1.4504264860267857</v>
+        <v>1.4482303179503047</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4526,13 +4537,13 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>2.0255319611194467</v>
+        <v>2.0224198692511615</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4545,13 +4556,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>2.9040634993325485</v>
+        <v>2.8995436192954283</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4564,13 +4575,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>2.5955648360322128</v>
+        <v>2.5915402028830887</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4583,11 +4594,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8014795111682472E-2</v>
+        <v>6.6554000023446774E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0505050505050511E-2</v>
+        <v>4.9504950495049507E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>0.80996280963569622</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>452</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>5.2722021815940899E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>8.6087971624454432E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.49619793491400876</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.2342258232843137</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,20 +5067,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7955905909484173</v>
+        <v>1.7925210672981666</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,20 +5134,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.50140551592815619</v>
+        <v>0.50054837393973961</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>0.10863424600069688</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>2.2824569622635926</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,25 +5196,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8610078743551273</v>
+        <v>1.857826521260256</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,55 +5227,55 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2440848891002169E-2</v>
+        <v>1.2419581526329717E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>3.1676337982663911</v>
+        <v>3.1622187961450132</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>1.8427475047736226</v>
+        <v>1.8395973673893788</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5315,14 +5326,14 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>3.46 HKD</v>
+        <v>3.45 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5403,36 +5414,36 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>3.17 HKD</v>
+        <v>3.16 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>3.2846465100223896</v>
+        <v>3.2790314771769</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,7 +5485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5483,7 +5494,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,7 +5520,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5518,7 +5529,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5528,30 +5539,30 @@
         <v>0.16572593193648588</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.2847005540902998</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
+        <v>1.2825043860138188</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>1.4504264860267857</v>
+        <v>1.4482303179503047</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,21 +5575,21 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55842235028910348</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
+        <v>0.55833595132268554</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,30 +5608,30 @@
         <v>0.20504008238649371</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>1.8204918787329532</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
+        <v>1.8173797868646679</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>2.0255319611194467</v>
+        <v>2.0224198692511615</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,21 +5644,21 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3833333495890735</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
+        <v>0.38322645472364458</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,30 +5677,30 @@
         <v>0.26005257398719595</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>2.6440109253453525</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
+        <v>2.6394910453082323</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>2.9040634993325485</v>
+        <v>2.8995436192954283</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,21 +5713,21 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11586726593822938</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
+        <v>0.1157316910565902</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,30 +5746,30 @@
         <v>0.24126031259386493</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>2.3543045234383477</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
+        <v>2.3502798902892237</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>2.5955648360322128</v>
+        <v>2.5915402028830887</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,16 +5782,16 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20891895073378253</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="13.9">
+        <v>0.20879303450714981</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6185,7 +6196,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6201,7 +6212,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6217,7 +6228,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6233,7 +6244,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6269,7 +6280,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6305,7 +6316,7 @@
       </c>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6341,7 +6352,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6377,7 +6388,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6413,13 +6424,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6435,7 +6446,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6451,7 +6462,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6467,7 +6478,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6503,7 +6514,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6539,7 +6550,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6575,54 +6586,54 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
         <f>0.1208*Exchange_Rate</f>
-        <v>0.13176516096000002</v>
+        <v>0.13153991124</v>
       </c>
       <c r="D25" s="39">
         <f>0.207*Exchange_Rate</f>
-        <v>0.22578963839999999</v>
+        <v>0.22540365584999997</v>
       </c>
       <c r="E25" s="39">
         <f>0.178*Exchange_Rate</f>
-        <v>0.19415727360000001</v>
+        <v>0.19382536589999996</v>
       </c>
       <c r="F25" s="39">
         <f>0.155*Exchange_Rate</f>
-        <v>0.16906953600000002</v>
+        <v>0.16878051524999999</v>
       </c>
       <c r="G25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="H25" s="39">
         <f>0.076*Exchange_Rate</f>
-        <v>8.28986112E-2</v>
+        <v>8.2756897799999993E-2</v>
       </c>
       <c r="I25" s="39">
         <f>0.15*Exchange_Rate</f>
-        <v>0.16361568000000001</v>
+        <v>0.16333598249999998</v>
       </c>
       <c r="J25" s="39">
         <f>0.005*Exchange_Rate</f>
-        <v>5.453856E-3</v>
+        <v>5.4445327499999998E-3</v>
       </c>
       <c r="K25" s="39">
         <f>0.05*Exchange_Rate</f>
-        <v>5.4538560000000007E-2</v>
+        <v>5.4445327500000001E-2</v>
       </c>
       <c r="L25" s="39">
         <f>0.08*Exchange_Rate</f>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6630,7 +6641,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6667,7 +6678,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6704,7 +6715,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6741,7 +6752,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6778,7 +6789,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6815,7 +6826,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6831,12 +6842,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6885,7 +6896,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6934,7 +6945,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6983,7 +6994,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7032,7 +7043,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7081,7 +7092,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7130,7 +7141,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7179,7 +7190,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7228,7 +7239,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7277,7 +7288,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7326,7 +7337,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7375,7 +7386,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7424,7 +7435,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7473,12 +7484,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7527,7 +7538,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7576,12 +7587,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7630,7 +7641,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7679,7 +7690,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7728,7 +7739,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7777,13 +7788,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7832,7 +7843,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7881,7 +7892,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7930,7 +7941,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7979,61 +7990,61 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.13176516096000002</v>
+        <v>0.13153991124</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.22578963839999999</v>
+        <v>0.22540365584999997</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.19415727360000001</v>
+        <v>0.19382536589999996</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16906953600000002</v>
+        <v>0.16878051524999999</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="H65" s="73">
         <f t="shared" si="33"/>
-        <v>8.28986112E-2</v>
+        <v>8.2756897799999993E-2</v>
       </c>
       <c r="I65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16361568000000001</v>
+        <v>0.16333598249999998</v>
       </c>
       <c r="J65" s="73">
         <f t="shared" si="33"/>
-        <v>5.453856E-3</v>
+        <v>5.4445327499999998E-3</v>
       </c>
       <c r="K65" s="73">
         <f t="shared" si="33"/>
-        <v>5.4538560000000007E-2</v>
+        <v>5.4445327500000001E-2</v>
       </c>
       <c r="L65" s="73">
         <f t="shared" si="33"/>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="M65" s="73" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8083,7 +8094,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8132,7 +8143,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8182,7 +8193,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8231,7 +8242,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8281,7 +8292,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8297,13 +8308,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8352,7 +8363,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8386,7 +8397,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8420,7 +8431,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8469,7 +8480,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8550,18 +8561,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8577,7 +8588,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8588,7 +8599,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8608,7 +8619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8631,7 +8642,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8653,7 +8664,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8716,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8738,7 +8749,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8750,7 +8761,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8762,7 +8773,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8786,12 +8797,12 @@
         <v>10520135.700000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8811,7 +8822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>455</v>
       </c>
@@ -8831,7 +8842,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8851,7 +8862,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8871,7 +8882,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8891,7 +8902,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8913,7 +8924,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8933,7 +8944,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8953,7 +8964,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8965,7 +8976,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8977,7 +8988,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9001,7 +9012,7 @@
         <v>52579.6</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9018,7 +9029,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9037,7 +9048,7 @@
         <v>8886812.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9052,7 +9063,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9071,7 +9082,7 @@
         <v>7788128.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9087,7 +9098,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9104,7 +9115,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9124,7 +9135,7 @@
         <v>13455846.25</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9135,7 +9146,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9148,7 +9159,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9167,7 +9178,7 @@
         <v>2883130.95</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9183,7 +9194,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9199,7 +9210,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9215,7 +9226,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9234,7 +9245,7 @@
         <v>773133.70000000007</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9254,7 +9265,7 @@
         <v>10572715.300000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9274,7 +9285,7 @@
         <v>10520135.700000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9293,7 +9304,7 @@
         <v>52579.6</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9304,7 +9315,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9318,7 +9329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9332,25 +9343,25 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.3555788271632103</v>
+        <v>4.3481330584629827</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8427475047736226</v>
+        <v>1.8395973673893788</v>
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9363,7 +9374,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9377,7 +9388,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9388,10 +9399,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9403,7 +9414,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9417,7 +9428,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9431,10 +9442,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9446,7 +9457,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9457,7 +9468,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9468,10 +9479,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9483,7 +9494,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9499,7 +9510,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9510,7 +9521,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9524,7 +9535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9540,7 +9551,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9550,7 +9561,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9560,7 +9571,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9570,7 +9581,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9580,10 +9591,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9595,13 +9606,13 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-965632.4493354666</v>
+        <v>-965545.91590136662</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
@@ -9611,13 +9622,13 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>12.10775695042768</v>
+        <v>12.108842062767666</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
@@ -9627,7 +9638,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9640,7 +9651,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9653,10 +9664,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9668,7 +9679,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9682,7 +9693,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9696,7 +9707,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9710,7 +9721,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9724,7 +9735,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9735,7 +9746,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9743,68 +9754,68 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2311479.4284288003</v>
+        <v>-2307528.0038621998</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.50140551592815619</v>
+        <v>-0.50054837393973961</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>8579246.3007771373</v>
+        <v>8564580.263009781</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8610078743551275</v>
+        <v>1.857826521260256</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>57352.31338752</v>
+        <v>57254.270836379997</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2440848891002169E-2</v>
+        <v>1.2419581526329717E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>6325119.1857358562</v>
+        <v>6314306.529983961</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>1.3720432073179736</v>
+        <v>1.3696977288468462</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9825,19 +9836,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9894,7 +9905,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9917,7 +9928,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9931,7 +9942,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9988,7 +9999,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10043,7 +10054,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10098,7 +10109,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10153,7 +10164,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10210,7 +10221,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10265,7 +10276,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10320,7 +10331,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10377,7 +10388,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10432,7 +10443,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10487,7 +10498,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10542,7 +10553,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10599,7 +10610,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10656,7 +10667,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10682,7 +10693,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10707,7 +10718,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10764,7 +10775,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10783,7 +10794,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10806,7 +10817,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10827,7 +10838,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10884,7 +10895,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10941,7 +10952,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10998,18 +11009,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11068,7 +11079,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11128,7 +11139,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11183,18 +11194,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11251,7 +11262,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11310,7 +11321,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11367,18 +11378,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11436,7 +11447,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11494,7 +11505,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11549,18 +11560,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11618,10 +11629,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11644,14 +11655,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11706,7 +11717,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11761,7 +11772,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11818,7 +11829,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11873,11 +11884,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11887,7 +11898,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11913,7 +11924,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11940,7 +11951,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11995,11 +12006,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12009,7 +12020,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12064,7 +12075,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12119,7 +12130,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12174,7 +12185,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12229,7 +12240,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12285,7 +12296,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12340,11 +12351,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12354,7 +12365,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12379,7 +12390,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12404,7 +12415,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12429,7 +12440,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12456,10 +12467,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12482,7 +12493,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12503,7 +12514,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12560,7 +12571,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12617,7 +12628,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12674,7 +12685,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12731,7 +12742,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12788,7 +12799,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12847,7 +12858,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12904,7 +12915,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12961,7 +12972,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13018,7 +13029,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13075,7 +13086,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13133,7 +13144,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13190,7 +13201,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13216,7 +13227,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13240,7 +13251,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13297,18 +13308,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13320,50 +13331,50 @@
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.13176516096000002</v>
+        <v>0.13153991124</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.22578963839999999</v>
+        <v>0.22540365584999997</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.19415727360000001</v>
+        <v>0.19382536589999996</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.16906953600000002</v>
+        <v>0.16878051524999999</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="L90" s="112">
         <f>Data!H65</f>
-        <v>8.28986112E-2</v>
+        <v>8.2756897799999993E-2</v>
       </c>
       <c r="M90" s="112">
         <f>Data!I65</f>
-        <v>0.16361568000000001</v>
+        <v>0.16333598249999998</v>
       </c>
       <c r="N90" s="112">
         <f>Data!J65</f>
-        <v>5.453856E-3</v>
+        <v>5.4445327499999998E-3</v>
       </c>
       <c r="O90" s="112">
         <f>Data!K65</f>
-        <v>5.4538560000000007E-2</v>
+        <v>5.4445327500000001E-2</v>
       </c>
       <c r="P90" s="112">
         <f>Data!L65</f>
-        <v>8.7261696E-2</v>
+        <v>8.7112523999999997E-2</v>
       </c>
       <c r="Q90" s="112" t="str">
         <f>Data!M65</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13376,50 +13387,50 @@
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>607437.39202560007</v>
+        <v>606398.99081640004</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1040890.233024</v>
+        <v>1039110.8534684998</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>895065.031296</v>
+        <v>893534.93679899978</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>779410.56096000003</v>
+        <v>778078.17530249991</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>402276.41856000002</v>
+        <v>401588.73563999997</v>
       </c>
       <c r="L91" s="74">
         <f t="shared" si="37"/>
-        <v>382162.59763199999</v>
+        <v>381509.29885799997</v>
       </c>
       <c r="M91" s="74">
         <f t="shared" si="37"/>
-        <v>754268.28480000002</v>
+        <v>752978.87932499987</v>
       </c>
       <c r="N91" s="74">
         <f t="shared" si="37"/>
-        <v>25142.276160000001</v>
+        <v>25099.295977499998</v>
       </c>
       <c r="O91" s="74">
         <f t="shared" si="37"/>
-        <v>251422.76160000003</v>
+        <v>250992.959775</v>
       </c>
       <c r="P91" s="74">
         <f t="shared" si="37"/>
-        <v>402276.41856000002</v>
+        <v>401588.73563999997</v>
       </c>
       <c r="Q91" s="74" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13431,109 +13442,109 @@
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.96037771723729226</v>
+        <v>0.95873597210279793</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.93871670914867211</v>
+        <v>0.93711199304348514</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66617907782957753</v>
+        <v>0.66504025896685448</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92724862660363627</v>
+        <v>0.92566351493989163</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
-        <v>0.92306941108711971</v>
+        <v>0.92149144370277392</v>
       </c>
       <c r="L92" s="170">
         <f t="shared" si="38"/>
-        <v>1.1314184308159621</v>
+        <v>1.1294842952456234</v>
       </c>
       <c r="M92" s="170">
         <f t="shared" si="38"/>
-        <v>0.59642972010194217</v>
+        <v>0.59541013627209016</v>
       </c>
       <c r="N92" s="170">
         <f t="shared" si="38"/>
-        <v>6.3966305377110066E-2</v>
+        <v>6.385695634834819E-2</v>
       </c>
       <c r="O92" s="170">
         <f t="shared" si="38"/>
-        <v>-0.60660683565193485</v>
+        <v>-0.60556985426106347</v>
       </c>
       <c r="P92" s="170">
         <f t="shared" si="38"/>
-        <v>0.66771749157212457</v>
+        <v>0.66657604282406446</v>
       </c>
       <c r="Q92" s="170" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0505050505050511E-2</v>
+        <v>4.9504950495049507E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.6548061090909105E-2</v>
+        <v>6.5118767940594055E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.1140351709090909</v>
+        <v>0.11158596824257425</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>9.8059229090909097E-2</v>
+        <v>9.5953151435643549E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>8.5388654545454551E-2</v>
+        <v>8.355471051980197E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4071563636363636E-2</v>
+        <v>4.3125011881188113E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1867985454545453E-2</v>
+        <v>4.0968761287128709E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2634181818181829E-2</v>
+        <v>8.0859397277227713E-2</v>
       </c>
       <c r="N93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7544727272727273E-3</v>
+        <v>2.6953132425742571E-3</v>
       </c>
       <c r="O93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7544727272727276E-2</v>
+        <v>2.6953132425742574E-2</v>
       </c>
       <c r="P93" s="23">
         <f t="shared" si="39"/>
-        <v>4.4071563636363636E-2</v>
+        <v>4.3125011881188113E-2</v>
       </c>
       <c r="Q93" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13554,7 +13565,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13611,7 +13622,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13668,10 +13679,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13694,7 +13705,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13704,7 +13715,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13761,7 +13772,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13818,7 +13829,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13875,7 +13886,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13932,7 +13943,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13989,11 +14000,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14016,7 +14027,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14073,7 +14084,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14130,7 +14141,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14157,18 +14168,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14220,7 +14231,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14272,11 +14283,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14330,7 +14341,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14385,7 +14396,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14439,7 +14450,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14495,7 +14506,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14552,7 +14563,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14571,7 +14582,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14594,7 +14605,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14615,7 +14626,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14623,845 +14634,845 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.13466929432113128</v>
+        <v>0.13443908004736249</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.14965532848053401</v>
+        <v>0.14939949590239915</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.26236332263488876</v>
+        <v>0.26191481815516726</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>0.31790425331787192</v>
+        <v>0.31736080280694057</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.19888536404917662</v>
+        <v>0.19854537377983844</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.10311526274915402</v>
+        <v>0.10293898941640997</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>7.9920403587331892E-2</v>
+        <v>7.9783781369446846E-2</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.29922598689735358</v>
+        <v>0.29871446648274402</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>9.3000666814750554E-2</v>
+        <v>9.2841684167082425E-2</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>-9.8068612223167026E-2</v>
+        <v>-9.7900966031388273E-2</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>0.14254912603210412</v>
+        <v>0.14230544135482645</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8014795111682472E-2</v>
+        <v>6.6554000023446774E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.5583499232592929E-2</v>
+        <v>7.3960146486336212E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13250672860347917</v>
+        <v>0.12966080106691449</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16055770369589492</v>
+        <v>0.15710930832026759</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10044715356019021</v>
+        <v>9.8289788999920025E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2078415529875764E-2</v>
+        <v>5.0959895750698002E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.0363840195622169E-2</v>
+        <v>3.9496921470023191E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15112423580674422</v>
+        <v>0.14787844875383369</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.697003374482351E-2</v>
+        <v>4.5961229785684371E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-4.9529602132912638E-2</v>
+        <v>-4.8465824768013997E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.1994508097022292E-2</v>
+        <v>7.0448238294468543E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12611242577620019</v>
+        <v>0.12361515001825563</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.26009531321895746</v>
+        <v>0.2549449109769979</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19706084708253907</v>
+        <v>0.1931586520908056</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17982810753960429</v>
+        <v>0.17626715491505768</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5360875566949324E-2</v>
+        <v>8.3670561199286952E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2713030522141157E-2</v>
+        <v>8.10751487296235E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16743245908104909</v>
+        <v>0.1641169648418204</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1778522754661583E-2</v>
+        <v>1.154528468031185E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.5928482219154669E-2</v>
+        <v>-2.5415046927686261E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2359714279453969E-2</v>
+        <v>9.0530809046197466E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453"